--- a/imports/Inscription.xlsx
+++ b/imports/Inscription.xlsx
@@ -9,6 +9,7 @@
     <sheet name="A" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">A!$A$1:$G$246</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">A!$A$1:$G$246</definedName>
   </definedNames>
   <calcPr/>
@@ -786,12 +787,9 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -811,7 +809,13 @@
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1328,7 +1332,7 @@
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
@@ -1345,5679 +1349,5760 @@
       </c>
     </row>
     <row r="2" ht="13.5" customHeight="1">
-      <c r="A2" s="4">
+      <c r="A2" s="3">
         <v>1682</v>
       </c>
-      <c r="B2" s="5">
-        <v>9</v>
-      </c>
-      <c r="C2" s="5">
-        <v>1</v>
-      </c>
-      <c r="D2" s="5">
-        <v>2</v>
-      </c>
-      <c r="E2" s="5" t="s">
+      <c r="B2" s="4">
+        <v>9</v>
+      </c>
+      <c r="C2" s="4">
+        <v>1</v>
+      </c>
+      <c r="D2" s="4">
+        <v>2</v>
+      </c>
+      <c r="E2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="6">
+      <c r="F2" s="5">
         <v>46263</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="G2" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="3" ht="13.5" customHeight="1">
-      <c r="A3" s="4">
+      <c r="A3" s="3">
         <v>1787</v>
       </c>
-      <c r="B3" s="5">
-        <v>9</v>
-      </c>
-      <c r="C3" s="5">
-        <v>1</v>
-      </c>
-      <c r="D3" s="5">
+      <c r="B3" s="4">
+        <v>9</v>
+      </c>
+      <c r="C3" s="4">
+        <v>1</v>
+      </c>
+      <c r="D3" s="4">
         <v>3</v>
       </c>
-      <c r="E3" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" s="6">
+      <c r="E3" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" s="5">
         <v>46263</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="G3" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="4" ht="13.5" customHeight="1">
-      <c r="A4" s="4">
+      <c r="A4" s="3">
         <v>1707</v>
       </c>
-      <c r="B4" s="5">
-        <v>9</v>
-      </c>
-      <c r="C4" s="5">
-        <v>1</v>
-      </c>
-      <c r="D4" s="5">
-        <v>2</v>
-      </c>
-      <c r="E4" s="5" t="s">
+      <c r="B4" s="4">
+        <v>9</v>
+      </c>
+      <c r="C4" s="4">
+        <v>1</v>
+      </c>
+      <c r="D4" s="4">
+        <v>2</v>
+      </c>
+      <c r="E4" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F4" s="6">
+      <c r="F4" s="5">
         <v>46263</v>
       </c>
-      <c r="G4" s="5" t="s">
+      <c r="G4" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="5" ht="13.5" customHeight="1">
-      <c r="A5" s="4">
+      <c r="A5" s="3">
         <v>1726</v>
       </c>
-      <c r="B5" s="5">
-        <v>9</v>
-      </c>
-      <c r="C5" s="5">
-        <v>2</v>
-      </c>
-      <c r="D5" s="5">
+      <c r="B5" s="4">
+        <v>9</v>
+      </c>
+      <c r="C5" s="4">
+        <v>2</v>
+      </c>
+      <c r="D5" s="4">
         <v>7</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E5" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="F5" s="6">
+      <c r="F5" s="5">
         <v>46262</v>
       </c>
-      <c r="G5" s="5" t="s">
+      <c r="G5" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="6" ht="13.5" customHeight="1">
-      <c r="A6" s="4">
+      <c r="A6" s="3">
         <v>1727</v>
       </c>
-      <c r="B6" s="5">
-        <v>9</v>
-      </c>
-      <c r="C6" s="5">
-        <v>2</v>
-      </c>
-      <c r="D6" s="5">
-        <v>8</v>
-      </c>
-      <c r="E6" s="5" t="s">
+      <c r="B6" s="4">
+        <v>9</v>
+      </c>
+      <c r="C6" s="4">
+        <v>2</v>
+      </c>
+      <c r="D6" s="4">
+        <v>8</v>
+      </c>
+      <c r="E6" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="F6" s="6">
+      <c r="F6" s="5">
         <v>46261</v>
       </c>
-      <c r="G6" s="5" t="s">
+      <c r="G6" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="7" ht="13.5" customHeight="1">
-      <c r="A7" s="4">
+      <c r="A7" s="3">
         <v>1733</v>
       </c>
-      <c r="B7" s="5">
-        <v>9</v>
-      </c>
-      <c r="C7" s="5">
-        <v>1</v>
-      </c>
-      <c r="D7" s="5">
-        <v>2</v>
-      </c>
-      <c r="E7" s="5" t="s">
+      <c r="B7" s="4">
+        <v>9</v>
+      </c>
+      <c r="C7" s="4">
+        <v>1</v>
+      </c>
+      <c r="D7" s="4">
+        <v>2</v>
+      </c>
+      <c r="E7" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="F7" s="6">
+      <c r="F7" s="5">
         <v>46263</v>
       </c>
-      <c r="G7" s="5" t="s">
+      <c r="G7" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="8" ht="13.5" customHeight="1">
-      <c r="A8" s="4">
+      <c r="A8" s="3">
         <v>1739</v>
       </c>
-      <c r="B8" s="5">
-        <v>9</v>
-      </c>
-      <c r="C8" s="5">
-        <v>1</v>
-      </c>
-      <c r="D8" s="5">
-        <v>2</v>
-      </c>
-      <c r="E8" s="5" t="s">
+      <c r="B8" s="4">
+        <v>9</v>
+      </c>
+      <c r="C8" s="4">
+        <v>1</v>
+      </c>
+      <c r="D8" s="4">
+        <v>2</v>
+      </c>
+      <c r="E8" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="F8" s="6">
+      <c r="F8" s="5">
         <v>46274</v>
       </c>
-      <c r="G8" s="5" t="s">
+      <c r="G8" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="9" ht="13.5" customHeight="1">
-      <c r="A9" s="4">
+      <c r="A9" s="3">
         <v>1741</v>
       </c>
-      <c r="B9" s="5">
-        <v>9</v>
-      </c>
-      <c r="C9" s="5">
-        <v>1</v>
-      </c>
-      <c r="D9" s="5">
-        <v>2</v>
-      </c>
-      <c r="E9" s="5" t="s">
+      <c r="B9" s="4">
+        <v>9</v>
+      </c>
+      <c r="C9" s="4">
+        <v>1</v>
+      </c>
+      <c r="D9" s="4">
+        <v>2</v>
+      </c>
+      <c r="E9" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F9" s="6">
+      <c r="F9" s="5">
         <v>46267</v>
       </c>
-      <c r="G9" s="5" t="s">
+      <c r="G9" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="10" ht="13.5" customHeight="1">
-      <c r="A10" s="4">
+      <c r="A10" s="3">
         <v>1773</v>
       </c>
-      <c r="B10" s="5">
-        <v>9</v>
-      </c>
-      <c r="C10" s="5">
-        <v>1</v>
-      </c>
-      <c r="D10" s="5">
-        <v>2</v>
-      </c>
-      <c r="E10" s="5" t="s">
+      <c r="B10" s="4">
+        <v>9</v>
+      </c>
+      <c r="C10" s="4">
+        <v>1</v>
+      </c>
+      <c r="D10" s="4">
+        <v>2</v>
+      </c>
+      <c r="E10" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="F10" s="6">
+      <c r="F10" s="5">
         <v>46263</v>
       </c>
-      <c r="G10" s="5" t="s">
+      <c r="G10" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="11" ht="13.5" customHeight="1">
-      <c r="A11" s="4">
+      <c r="A11" s="3">
         <v>1785</v>
       </c>
-      <c r="B11" s="5">
-        <v>9</v>
-      </c>
-      <c r="C11" s="5">
-        <v>1</v>
-      </c>
-      <c r="D11" s="5">
-        <v>2</v>
-      </c>
-      <c r="E11" s="5" t="s">
+      <c r="B11" s="4">
+        <v>9</v>
+      </c>
+      <c r="C11" s="4">
+        <v>1</v>
+      </c>
+      <c r="D11" s="4">
+        <v>2</v>
+      </c>
+      <c r="E11" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="F11" s="6">
+      <c r="F11" s="5">
         <v>46263</v>
       </c>
-      <c r="G11" s="5" t="s">
+      <c r="G11" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="12" ht="13.5" customHeight="1">
-      <c r="A12" s="4">
+      <c r="A12" s="3">
         <v>1796</v>
       </c>
-      <c r="B12" s="5">
-        <v>9</v>
-      </c>
-      <c r="C12" s="5">
-        <v>1</v>
-      </c>
-      <c r="D12" s="5">
-        <v>2</v>
-      </c>
-      <c r="E12" s="5" t="s">
+      <c r="B12" s="4">
+        <v>9</v>
+      </c>
+      <c r="C12" s="4">
+        <v>1</v>
+      </c>
+      <c r="D12" s="4">
+        <v>2</v>
+      </c>
+      <c r="E12" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="F12" s="6">
+      <c r="F12" s="5">
         <v>46263</v>
       </c>
-      <c r="G12" s="5" t="s">
+      <c r="G12" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="13" ht="13.5" customHeight="1">
-      <c r="A13" s="4">
+      <c r="A13" s="3">
         <v>1806</v>
       </c>
-      <c r="B13" s="5">
-        <v>9</v>
-      </c>
-      <c r="C13" s="5">
-        <v>2</v>
-      </c>
-      <c r="D13" s="5">
+      <c r="B13" s="4">
+        <v>9</v>
+      </c>
+      <c r="C13" s="4">
+        <v>2</v>
+      </c>
+      <c r="D13" s="4">
         <v>7</v>
       </c>
-      <c r="E13" s="5" t="s">
+      <c r="E13" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="F13" s="6">
+      <c r="F13" s="5">
         <v>46248</v>
       </c>
-      <c r="G13" s="5" t="s">
+      <c r="G13" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="14" ht="13.5" customHeight="1">
-      <c r="A14" s="4">
+      <c r="A14" s="3">
         <v>1807</v>
       </c>
-      <c r="B14" s="5">
-        <v>9</v>
-      </c>
-      <c r="C14" s="5">
-        <v>2</v>
-      </c>
-      <c r="D14" s="5">
+      <c r="B14" s="4">
+        <v>9</v>
+      </c>
+      <c r="C14" s="4">
+        <v>2</v>
+      </c>
+      <c r="D14" s="4">
         <v>10</v>
       </c>
-      <c r="E14" s="5" t="s">
+      <c r="E14" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="F14" s="6">
+      <c r="F14" s="5">
         <v>46274</v>
       </c>
-      <c r="G14" s="5" t="s">
+      <c r="G14" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="15" ht="13.5" customHeight="1">
-      <c r="A15" s="4">
+      <c r="A15" s="3">
         <v>1808</v>
       </c>
-      <c r="B15" s="5">
-        <v>9</v>
-      </c>
-      <c r="C15" s="5">
-        <v>1</v>
-      </c>
-      <c r="D15" s="5">
-        <v>2</v>
-      </c>
-      <c r="E15" s="5" t="s">
+      <c r="B15" s="4">
+        <v>9</v>
+      </c>
+      <c r="C15" s="4">
+        <v>1</v>
+      </c>
+      <c r="D15" s="4">
+        <v>2</v>
+      </c>
+      <c r="E15" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="F15" s="6">
+      <c r="F15" s="5">
         <v>46254</v>
       </c>
-      <c r="G15" s="5" t="s">
+      <c r="G15" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="16" ht="13.5" customHeight="1">
-      <c r="A16" s="4">
+      <c r="A16" s="3">
         <v>1809</v>
       </c>
-      <c r="B16" s="5">
-        <v>9</v>
-      </c>
-      <c r="C16" s="5">
-        <v>2</v>
-      </c>
-      <c r="D16" s="5">
+      <c r="B16" s="4">
+        <v>9</v>
+      </c>
+      <c r="C16" s="4">
+        <v>2</v>
+      </c>
+      <c r="D16" s="4">
         <v>6</v>
       </c>
-      <c r="E16" s="5" t="s">
+      <c r="E16" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="F16" s="6">
+      <c r="F16" s="5">
         <v>46274</v>
       </c>
-      <c r="G16" s="5" t="s">
+      <c r="G16" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="17" ht="13.5" customHeight="1">
-      <c r="A17" s="4">
+      <c r="A17" s="3">
         <v>1810</v>
       </c>
-      <c r="B17" s="5">
-        <v>9</v>
-      </c>
-      <c r="C17" s="5">
+      <c r="B17" s="4">
+        <v>9</v>
+      </c>
+      <c r="C17" s="4">
         <v>3</v>
       </c>
-      <c r="D17" s="5">
+      <c r="D17" s="4">
         <v>11</v>
       </c>
-      <c r="E17" s="5" t="s">
+      <c r="E17" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="F17" s="6">
+      <c r="F17" s="5">
         <v>46248</v>
       </c>
-      <c r="G17" s="5" t="s">
+      <c r="G17" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="18" ht="13.5" customHeight="1">
-      <c r="A18" s="4">
+      <c r="A18" s="3">
         <v>1811</v>
       </c>
-      <c r="B18" s="5">
-        <v>9</v>
-      </c>
-      <c r="C18" s="5">
-        <v>1</v>
-      </c>
-      <c r="D18" s="5">
-        <v>2</v>
-      </c>
-      <c r="E18" s="5" t="s">
+      <c r="B18" s="4">
+        <v>9</v>
+      </c>
+      <c r="C18" s="4">
+        <v>1</v>
+      </c>
+      <c r="D18" s="4">
+        <v>2</v>
+      </c>
+      <c r="E18" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="F18" s="6">
+      <c r="F18" s="5">
         <v>46248</v>
       </c>
-      <c r="G18" s="5" t="s">
+      <c r="G18" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="19" ht="13.5" customHeight="1">
-      <c r="A19" s="4">
+      <c r="A19" s="3">
         <v>1812</v>
       </c>
-      <c r="B19" s="5">
-        <v>9</v>
-      </c>
-      <c r="C19" s="5">
-        <v>2</v>
-      </c>
-      <c r="D19" s="5">
-        <v>8</v>
-      </c>
-      <c r="E19" s="5" t="s">
+      <c r="B19" s="4">
+        <v>9</v>
+      </c>
+      <c r="C19" s="4">
+        <v>2</v>
+      </c>
+      <c r="D19" s="4">
+        <v>8</v>
+      </c>
+      <c r="E19" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="F19" s="6">
+      <c r="F19" s="5">
         <v>46248</v>
       </c>
-      <c r="G19" s="5" t="s">
+      <c r="G19" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="20" ht="13.5" customHeight="1">
-      <c r="A20" s="7">
+      <c r="A20" s="6">
         <v>1813</v>
       </c>
-      <c r="B20" s="8">
-        <v>9</v>
-      </c>
-      <c r="C20" s="8">
+      <c r="B20" s="7">
+        <v>9</v>
+      </c>
+      <c r="C20" s="7">
         <v>3</v>
       </c>
-      <c r="D20" s="8">
+      <c r="D20" s="7">
         <v>13</v>
       </c>
-      <c r="E20" s="5" t="s">
+      <c r="E20" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="F20" s="6">
+      <c r="F20" s="5">
         <v>46248</v>
       </c>
-      <c r="G20" s="5" t="s">
+      <c r="G20" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="21" ht="13.5" customHeight="1">
-      <c r="A21" s="4">
+      <c r="A21" s="3">
         <v>1814</v>
       </c>
-      <c r="B21" s="5">
-        <v>9</v>
-      </c>
-      <c r="C21" s="5">
-        <v>2</v>
-      </c>
-      <c r="D21" s="5">
+      <c r="B21" s="4">
+        <v>9</v>
+      </c>
+      <c r="C21" s="4">
+        <v>2</v>
+      </c>
+      <c r="D21" s="4">
         <v>7</v>
       </c>
-      <c r="E21" s="5" t="s">
+      <c r="E21" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="F21" s="6">
+      <c r="F21" s="5">
         <v>46248</v>
       </c>
-      <c r="G21" s="5" t="s">
+      <c r="G21" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="22" ht="13.5" customHeight="1">
-      <c r="A22" s="4">
+      <c r="A22" s="3">
         <v>1815</v>
       </c>
-      <c r="B22" s="5">
-        <v>9</v>
-      </c>
-      <c r="C22" s="5">
-        <v>2</v>
-      </c>
-      <c r="D22" s="5">
-        <v>9</v>
-      </c>
-      <c r="E22" s="5" t="s">
+      <c r="B22" s="4">
+        <v>9</v>
+      </c>
+      <c r="C22" s="4">
+        <v>2</v>
+      </c>
+      <c r="D22" s="4">
+        <v>9</v>
+      </c>
+      <c r="E22" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="F22" s="6">
+      <c r="F22" s="5">
         <v>46248</v>
       </c>
-      <c r="G22" s="5" t="s">
+      <c r="G22" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="23" ht="13.5" customHeight="1">
-      <c r="A23" s="4">
+      <c r="A23" s="3">
         <v>1816</v>
       </c>
-      <c r="B23" s="5">
-        <v>9</v>
-      </c>
-      <c r="C23" s="5">
-        <v>2</v>
-      </c>
-      <c r="D23" s="5">
-        <v>9</v>
-      </c>
-      <c r="E23" s="5" t="s">
+      <c r="B23" s="4">
+        <v>9</v>
+      </c>
+      <c r="C23" s="4">
+        <v>2</v>
+      </c>
+      <c r="D23" s="4">
+        <v>9</v>
+      </c>
+      <c r="E23" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="F23" s="6">
+      <c r="F23" s="5">
         <v>46248</v>
       </c>
-      <c r="G23" s="5" t="s">
+      <c r="G23" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="24" ht="13.5" customHeight="1">
-      <c r="A24" s="4">
+      <c r="A24" s="3">
         <v>1817</v>
       </c>
-      <c r="B24" s="5">
-        <v>9</v>
-      </c>
-      <c r="C24" s="5">
-        <v>2</v>
-      </c>
-      <c r="D24" s="5">
-        <v>9</v>
-      </c>
-      <c r="E24" s="5" t="s">
+      <c r="B24" s="4">
+        <v>9</v>
+      </c>
+      <c r="C24" s="4">
+        <v>2</v>
+      </c>
+      <c r="D24" s="4">
+        <v>9</v>
+      </c>
+      <c r="E24" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="F24" s="6">
+      <c r="F24" s="5">
         <v>46251</v>
       </c>
-      <c r="G24" s="5" t="s">
+      <c r="G24" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="25" ht="13.5" customHeight="1">
-      <c r="A25" s="4">
+      <c r="A25" s="3">
         <v>1818</v>
       </c>
-      <c r="B25" s="5">
-        <v>9</v>
-      </c>
-      <c r="C25" s="5">
-        <v>2</v>
-      </c>
-      <c r="D25" s="5">
+      <c r="B25" s="4">
+        <v>9</v>
+      </c>
+      <c r="C25" s="4">
+        <v>2</v>
+      </c>
+      <c r="D25" s="4">
         <v>6</v>
       </c>
-      <c r="E25" s="5" t="s">
+      <c r="E25" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="F25" s="6">
+      <c r="F25" s="5">
         <v>46251</v>
       </c>
-      <c r="G25" s="5" t="s">
+      <c r="G25" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="26" ht="13.5" customHeight="1">
-      <c r="A26" s="4">
+      <c r="A26" s="3">
         <v>1819</v>
       </c>
-      <c r="B26" s="5">
-        <v>9</v>
-      </c>
-      <c r="C26" s="9">
+      <c r="B26" s="4">
+        <v>9</v>
+      </c>
+      <c r="C26" s="4">
         <v>3</v>
       </c>
-      <c r="D26" s="5">
+      <c r="D26" s="4">
         <v>13</v>
       </c>
-      <c r="E26" s="5" t="s">
+      <c r="E26" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="F26" s="6">
+      <c r="F26" s="5">
         <v>46251</v>
       </c>
-      <c r="G26" s="5" t="s">
+      <c r="G26" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="27" ht="13.5" customHeight="1">
-      <c r="A27" s="4">
+      <c r="A27" s="3">
         <v>1820</v>
       </c>
-      <c r="B27" s="5">
-        <v>9</v>
-      </c>
-      <c r="C27" s="5">
-        <v>2</v>
-      </c>
-      <c r="D27" s="5">
-        <v>9</v>
-      </c>
-      <c r="E27" s="5" t="s">
+      <c r="B27" s="4">
+        <v>9</v>
+      </c>
+      <c r="C27" s="4">
+        <v>2</v>
+      </c>
+      <c r="D27" s="4">
+        <v>9</v>
+      </c>
+      <c r="E27" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="F27" s="6">
+      <c r="F27" s="5">
         <v>46251</v>
       </c>
-      <c r="G27" s="5" t="s">
+      <c r="G27" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="28" ht="13.5" customHeight="1">
-      <c r="A28" s="4">
+      <c r="A28" s="3">
         <v>1821</v>
       </c>
-      <c r="B28" s="5">
-        <v>9</v>
-      </c>
-      <c r="C28" s="5">
-        <v>1</v>
-      </c>
-      <c r="D28" s="5">
+      <c r="B28" s="4">
+        <v>9</v>
+      </c>
+      <c r="C28" s="4">
+        <v>1</v>
+      </c>
+      <c r="D28" s="4">
         <v>4</v>
       </c>
-      <c r="E28" s="5" t="s">
+      <c r="E28" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="F28" s="6">
+      <c r="F28" s="5">
         <v>46251</v>
       </c>
-      <c r="G28" s="5" t="s">
+      <c r="G28" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="29" ht="13.5" customHeight="1">
-      <c r="A29" s="4">
+      <c r="A29" s="3">
         <v>1822</v>
       </c>
-      <c r="B29" s="5">
-        <v>9</v>
-      </c>
-      <c r="C29" s="5">
-        <v>1</v>
-      </c>
-      <c r="D29" s="5">
-        <v>2</v>
-      </c>
-      <c r="E29" s="5" t="s">
+      <c r="B29" s="4">
+        <v>9</v>
+      </c>
+      <c r="C29" s="4">
+        <v>1</v>
+      </c>
+      <c r="D29" s="4">
+        <v>2</v>
+      </c>
+      <c r="E29" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F29" s="6">
+      <c r="F29" s="5">
         <v>46251</v>
       </c>
-      <c r="G29" s="5" t="s">
+      <c r="G29" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="30" ht="13.5" customHeight="1">
-      <c r="A30" s="4">
+      <c r="A30" s="3">
         <v>1823</v>
       </c>
-      <c r="B30" s="5">
-        <v>9</v>
-      </c>
-      <c r="C30" s="5">
+      <c r="B30" s="4">
+        <v>9</v>
+      </c>
+      <c r="C30" s="4">
         <v>3</v>
       </c>
-      <c r="D30" s="5">
+      <c r="D30" s="4">
         <v>12</v>
       </c>
-      <c r="E30" s="5" t="s">
+      <c r="E30" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="F30" s="6">
+      <c r="F30" s="5">
         <v>46251</v>
       </c>
-      <c r="G30" s="5" t="s">
+      <c r="G30" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="31" ht="13.5" customHeight="1">
-      <c r="A31" s="4">
+      <c r="A31" s="3">
         <v>1824</v>
       </c>
-      <c r="B31" s="5">
-        <v>9</v>
-      </c>
-      <c r="C31" s="5">
-        <v>1</v>
-      </c>
-      <c r="D31" s="5">
+      <c r="B31" s="4">
+        <v>9</v>
+      </c>
+      <c r="C31" s="4">
+        <v>1</v>
+      </c>
+      <c r="D31" s="4">
         <v>3</v>
       </c>
-      <c r="E31" s="5" t="s">
+      <c r="E31" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="F31" s="6">
+      <c r="F31" s="5">
         <v>46251</v>
       </c>
-      <c r="G31" s="5" t="s">
+      <c r="G31" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="32" ht="13.5" customHeight="1">
-      <c r="A32" s="4">
+      <c r="A32" s="3">
         <v>1825</v>
       </c>
-      <c r="B32" s="5">
-        <v>9</v>
-      </c>
-      <c r="C32" s="5">
-        <v>1</v>
-      </c>
-      <c r="D32" s="5">
-        <v>2</v>
-      </c>
-      <c r="E32" s="5" t="s">
+      <c r="B32" s="4">
+        <v>9</v>
+      </c>
+      <c r="C32" s="4">
+        <v>1</v>
+      </c>
+      <c r="D32" s="4">
+        <v>2</v>
+      </c>
+      <c r="E32" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="F32" s="6">
+      <c r="F32" s="5">
         <v>46274</v>
       </c>
-      <c r="G32" s="5" t="s">
+      <c r="G32" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="33" ht="13.5" customHeight="1">
-      <c r="A33" s="4">
+      <c r="A33" s="3">
         <v>1826</v>
       </c>
-      <c r="B33" s="5">
-        <v>9</v>
-      </c>
-      <c r="C33" s="5">
+      <c r="B33" s="4">
+        <v>9</v>
+      </c>
+      <c r="C33" s="4">
         <v>3</v>
       </c>
-      <c r="D33" s="5">
+      <c r="D33" s="4">
         <v>11</v>
       </c>
-      <c r="E33" s="5" t="s">
+      <c r="E33" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="F33" s="6">
+      <c r="F33" s="5">
         <v>46251</v>
       </c>
-      <c r="G33" s="5" t="s">
+      <c r="G33" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="34" ht="13.5" customHeight="1">
-      <c r="A34" s="4">
+      <c r="A34" s="3">
         <v>1827</v>
       </c>
-      <c r="B34" s="5">
-        <v>9</v>
-      </c>
-      <c r="C34" s="5">
+      <c r="B34" s="4">
+        <v>9</v>
+      </c>
+      <c r="C34" s="4">
         <v>3</v>
       </c>
-      <c r="D34" s="5">
+      <c r="D34" s="4">
         <v>11</v>
       </c>
-      <c r="E34" s="5" t="s">
+      <c r="E34" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="F34" s="6">
+      <c r="F34" s="5">
         <v>46251</v>
       </c>
-      <c r="G34" s="5" t="s">
+      <c r="G34" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="35" ht="13.5" customHeight="1">
-      <c r="A35" s="4">
+      <c r="A35" s="3">
         <v>1828</v>
       </c>
-      <c r="B35" s="5">
-        <v>9</v>
-      </c>
-      <c r="C35" s="5">
-        <v>1</v>
-      </c>
-      <c r="D35" s="5">
+      <c r="B35" s="4">
+        <v>9</v>
+      </c>
+      <c r="C35" s="4">
+        <v>1</v>
+      </c>
+      <c r="D35" s="4">
         <v>4</v>
       </c>
-      <c r="E35" s="5" t="s">
+      <c r="E35" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="F35" s="6">
+      <c r="F35" s="5">
         <v>46251</v>
       </c>
-      <c r="G35" s="5" t="s">
+      <c r="G35" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="36" ht="13.5" customHeight="1">
-      <c r="A36" s="4">
+      <c r="A36" s="3">
         <v>1829</v>
       </c>
-      <c r="B36" s="5">
-        <v>9</v>
-      </c>
-      <c r="C36" s="5">
-        <v>2</v>
-      </c>
-      <c r="D36" s="5">
+      <c r="B36" s="4">
+        <v>9</v>
+      </c>
+      <c r="C36" s="4">
+        <v>2</v>
+      </c>
+      <c r="D36" s="4">
         <v>7</v>
       </c>
-      <c r="E36" s="5" t="s">
+      <c r="E36" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="F36" s="6">
+      <c r="F36" s="5">
         <v>46251</v>
       </c>
-      <c r="G36" s="5" t="s">
+      <c r="G36" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="37" ht="13.5" customHeight="1">
-      <c r="A37" s="4">
+      <c r="A37" s="3">
         <v>1830</v>
       </c>
-      <c r="B37" s="5">
-        <v>9</v>
-      </c>
-      <c r="C37" s="5">
-        <v>1</v>
-      </c>
-      <c r="D37" s="5">
-        <v>2</v>
-      </c>
-      <c r="E37" s="5" t="s">
+      <c r="B37" s="4">
+        <v>9</v>
+      </c>
+      <c r="C37" s="4">
+        <v>1</v>
+      </c>
+      <c r="D37" s="4">
+        <v>2</v>
+      </c>
+      <c r="E37" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="F37" s="6">
+      <c r="F37" s="5">
         <v>46251</v>
       </c>
-      <c r="G37" s="5" t="s">
+      <c r="G37" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="38" ht="13.5" customHeight="1">
-      <c r="A38" s="4">
+      <c r="A38" s="3">
         <v>1831</v>
       </c>
-      <c r="B38" s="5">
-        <v>9</v>
-      </c>
-      <c r="C38" s="5">
-        <v>2</v>
-      </c>
-      <c r="D38" s="5">
+      <c r="B38" s="4">
+        <v>9</v>
+      </c>
+      <c r="C38" s="4">
+        <v>2</v>
+      </c>
+      <c r="D38" s="4">
         <v>7</v>
       </c>
-      <c r="E38" s="5" t="s">
+      <c r="E38" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="F38" s="6">
+      <c r="F38" s="5">
         <v>46251</v>
       </c>
-      <c r="G38" s="5" t="s">
+      <c r="G38" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="39" ht="13.5" customHeight="1">
-      <c r="A39" s="4">
+      <c r="A39" s="3">
         <v>1832</v>
       </c>
-      <c r="B39" s="5">
-        <v>9</v>
-      </c>
-      <c r="C39" s="5">
-        <v>1</v>
-      </c>
-      <c r="D39" s="5">
-        <v>2</v>
-      </c>
-      <c r="E39" s="5" t="s">
+      <c r="B39" s="4">
+        <v>9</v>
+      </c>
+      <c r="C39" s="4">
+        <v>1</v>
+      </c>
+      <c r="D39" s="4">
+        <v>2</v>
+      </c>
+      <c r="E39" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="F39" s="6">
+      <c r="F39" s="5">
         <v>46251</v>
       </c>
-      <c r="G39" s="5" t="s">
+      <c r="G39" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="40" ht="13.5" customHeight="1">
-      <c r="A40" s="4">
+      <c r="A40" s="3">
         <v>1833</v>
       </c>
-      <c r="B40" s="5">
-        <v>9</v>
-      </c>
-      <c r="C40" s="5">
-        <v>2</v>
-      </c>
-      <c r="D40" s="5">
-        <v>8</v>
-      </c>
-      <c r="E40" s="5" t="s">
+      <c r="B40" s="4">
+        <v>9</v>
+      </c>
+      <c r="C40" s="4">
+        <v>2</v>
+      </c>
+      <c r="D40" s="4">
+        <v>8</v>
+      </c>
+      <c r="E40" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="F40" s="6">
+      <c r="F40" s="5">
         <v>46254</v>
       </c>
-      <c r="G40" s="5" t="s">
+      <c r="G40" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="41" ht="13.5" customHeight="1">
-      <c r="A41" s="4">
+      <c r="A41" s="3">
         <v>1834</v>
       </c>
-      <c r="B41" s="5">
-        <v>9</v>
-      </c>
-      <c r="C41" s="5">
-        <v>2</v>
-      </c>
-      <c r="D41" s="5">
+      <c r="B41" s="4">
+        <v>9</v>
+      </c>
+      <c r="C41" s="4">
+        <v>2</v>
+      </c>
+      <c r="D41" s="4">
         <v>10</v>
       </c>
-      <c r="E41" s="5" t="s">
+      <c r="E41" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="F41" s="6">
+      <c r="F41" s="5">
         <v>46254</v>
       </c>
-      <c r="G41" s="5" t="s">
+      <c r="G41" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="42" ht="13.5" customHeight="1">
-      <c r="A42" s="4">
+      <c r="A42" s="3">
         <v>1835</v>
       </c>
-      <c r="B42" s="5">
-        <v>9</v>
-      </c>
-      <c r="C42" s="5">
-        <v>2</v>
-      </c>
-      <c r="D42" s="5">
-        <v>8</v>
-      </c>
-      <c r="E42" s="5" t="s">
+      <c r="B42" s="4">
+        <v>9</v>
+      </c>
+      <c r="C42" s="4">
+        <v>2</v>
+      </c>
+      <c r="D42" s="4">
+        <v>8</v>
+      </c>
+      <c r="E42" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="F42" s="6">
+      <c r="F42" s="5">
         <v>46254</v>
       </c>
-      <c r="G42" s="5" t="s">
+      <c r="G42" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="43" ht="13.5" customHeight="1">
-      <c r="A43" s="4">
+      <c r="A43" s="3">
         <v>1836</v>
       </c>
-      <c r="B43" s="5">
-        <v>9</v>
-      </c>
-      <c r="C43" s="5">
+      <c r="B43" s="4">
+        <v>9</v>
+      </c>
+      <c r="C43" s="4">
         <v>3</v>
       </c>
-      <c r="D43" s="5">
+      <c r="D43" s="4">
         <v>11</v>
       </c>
-      <c r="E43" s="5" t="s">
+      <c r="E43" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="F43" s="6">
+      <c r="F43" s="5">
         <v>46254</v>
       </c>
-      <c r="G43" s="5" t="s">
+      <c r="G43" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="44" ht="13.5" customHeight="1">
-      <c r="A44" s="4">
+      <c r="A44" s="3">
         <v>1837</v>
       </c>
-      <c r="B44" s="5">
-        <v>9</v>
-      </c>
-      <c r="C44" s="5">
+      <c r="B44" s="4">
+        <v>9</v>
+      </c>
+      <c r="C44" s="4">
         <v>3</v>
       </c>
-      <c r="D44" s="5">
+      <c r="D44" s="4">
         <v>13</v>
       </c>
-      <c r="E44" s="5" t="s">
+      <c r="E44" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="F44" s="6">
+      <c r="F44" s="5">
         <v>46254</v>
       </c>
-      <c r="G44" s="5" t="s">
+      <c r="G44" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="45" ht="13.5" customHeight="1">
-      <c r="A45" s="4">
+      <c r="A45" s="3">
         <v>1838</v>
       </c>
-      <c r="B45" s="5">
-        <v>9</v>
-      </c>
-      <c r="C45" s="5">
+      <c r="B45" s="4">
+        <v>9</v>
+      </c>
+      <c r="C45" s="4">
         <v>3</v>
       </c>
-      <c r="D45" s="5">
+      <c r="D45" s="4">
         <v>11</v>
       </c>
-      <c r="E45" s="5" t="s">
+      <c r="E45" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="F45" s="6">
+      <c r="F45" s="5">
         <v>46254</v>
       </c>
-      <c r="G45" s="5" t="s">
+      <c r="G45" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="46" ht="13.5" customHeight="1">
-      <c r="A46" s="4">
+      <c r="A46" s="3">
         <v>1839</v>
       </c>
-      <c r="B46" s="5">
-        <v>9</v>
-      </c>
-      <c r="C46" s="5">
+      <c r="B46" s="4">
+        <v>9</v>
+      </c>
+      <c r="C46" s="4">
         <v>3</v>
       </c>
-      <c r="D46" s="5">
+      <c r="D46" s="4">
         <v>13</v>
       </c>
-      <c r="E46" s="5" t="s">
+      <c r="E46" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="F46" s="6">
+      <c r="F46" s="5">
         <v>46254</v>
       </c>
-      <c r="G46" s="5" t="s">
+      <c r="G46" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="47" ht="13.5" customHeight="1">
-      <c r="A47" s="4">
+      <c r="A47" s="3">
         <v>1840</v>
       </c>
-      <c r="B47" s="5">
-        <v>9</v>
-      </c>
-      <c r="C47" s="5">
+      <c r="B47" s="4">
+        <v>9</v>
+      </c>
+      <c r="C47" s="4">
         <v>3</v>
       </c>
-      <c r="D47" s="5">
+      <c r="D47" s="4">
         <v>13</v>
       </c>
-      <c r="E47" s="5" t="s">
+      <c r="E47" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="F47" s="6">
+      <c r="F47" s="5">
         <v>46254</v>
       </c>
-      <c r="G47" s="5" t="s">
+      <c r="G47" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="48" ht="13.5" customHeight="1">
-      <c r="A48" s="4">
+      <c r="A48" s="3">
         <v>1841</v>
       </c>
-      <c r="B48" s="5">
-        <v>9</v>
-      </c>
-      <c r="C48" s="5">
+      <c r="B48" s="4">
+        <v>9</v>
+      </c>
+      <c r="C48" s="4">
         <v>3</v>
       </c>
-      <c r="D48" s="5">
+      <c r="D48" s="4">
         <v>13</v>
       </c>
-      <c r="E48" s="5" t="s">
+      <c r="E48" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="F48" s="6">
+      <c r="F48" s="5">
         <v>46254</v>
       </c>
-      <c r="G48" s="5" t="s">
+      <c r="G48" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="49" ht="13.5" customHeight="1">
-      <c r="A49" s="4">
+      <c r="A49" s="3">
         <v>1842</v>
       </c>
-      <c r="B49" s="5">
-        <v>9</v>
-      </c>
-      <c r="C49" s="5">
+      <c r="B49" s="4">
+        <v>9</v>
+      </c>
+      <c r="C49" s="4">
         <v>3</v>
       </c>
-      <c r="D49" s="5">
+      <c r="D49" s="4">
         <v>13</v>
       </c>
-      <c r="E49" s="5" t="s">
+      <c r="E49" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="F49" s="6">
+      <c r="F49" s="5">
         <v>46254</v>
       </c>
-      <c r="G49" s="5" t="s">
+      <c r="G49" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="50" ht="13.5" customHeight="1">
-      <c r="A50" s="4">
+      <c r="A50" s="3">
         <v>1843</v>
       </c>
-      <c r="B50" s="5">
-        <v>9</v>
-      </c>
-      <c r="C50" s="5">
+      <c r="B50" s="4">
+        <v>9</v>
+      </c>
+      <c r="C50" s="4">
         <v>3</v>
       </c>
-      <c r="D50" s="5">
+      <c r="D50" s="4">
         <v>13</v>
       </c>
-      <c r="E50" s="5" t="s">
+      <c r="E50" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="F50" s="6">
+      <c r="F50" s="5">
         <v>46254</v>
       </c>
-      <c r="G50" s="5" t="s">
+      <c r="G50" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="51" ht="13.5" customHeight="1">
-      <c r="A51" s="4">
+      <c r="A51" s="3">
         <v>1844</v>
       </c>
-      <c r="B51" s="5">
-        <v>9</v>
-      </c>
-      <c r="C51" s="5">
-        <v>1</v>
-      </c>
-      <c r="D51" s="5">
-        <v>2</v>
-      </c>
-      <c r="E51" s="5" t="s">
+      <c r="B51" s="4">
+        <v>9</v>
+      </c>
+      <c r="C51" s="4">
+        <v>1</v>
+      </c>
+      <c r="D51" s="4">
+        <v>2</v>
+      </c>
+      <c r="E51" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="F51" s="6">
+      <c r="F51" s="5">
         <v>46254</v>
       </c>
-      <c r="G51" s="5" t="s">
+      <c r="G51" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="52" ht="13.5" customHeight="1">
-      <c r="A52" s="4">
+      <c r="A52" s="3">
         <v>1845</v>
       </c>
-      <c r="B52" s="5">
-        <v>9</v>
-      </c>
-      <c r="C52" s="5">
-        <v>1</v>
-      </c>
-      <c r="D52" s="5">
+      <c r="B52" s="4">
+        <v>9</v>
+      </c>
+      <c r="C52" s="4">
+        <v>1</v>
+      </c>
+      <c r="D52" s="4">
         <v>3</v>
       </c>
-      <c r="E52" s="5" t="s">
+      <c r="E52" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="F52" s="6">
+      <c r="F52" s="5">
         <v>46281</v>
       </c>
-      <c r="G52" s="5" t="s">
+      <c r="G52" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="53" ht="13.5" customHeight="1">
-      <c r="A53" s="4">
+      <c r="A53" s="3">
         <v>1846</v>
       </c>
-      <c r="B53" s="5">
-        <v>9</v>
-      </c>
-      <c r="C53" s="5">
-        <v>2</v>
-      </c>
-      <c r="D53" s="5">
+      <c r="B53" s="4">
+        <v>9</v>
+      </c>
+      <c r="C53" s="4">
+        <v>2</v>
+      </c>
+      <c r="D53" s="4">
         <v>6</v>
       </c>
-      <c r="E53" s="5" t="s">
+      <c r="E53" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="F53" s="6">
+      <c r="F53" s="5">
         <v>46254</v>
       </c>
-      <c r="G53" s="5" t="s">
+      <c r="G53" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="54" ht="13.5" customHeight="1">
-      <c r="A54" s="4">
+      <c r="A54" s="3">
         <v>1847</v>
       </c>
-      <c r="B54" s="5">
-        <v>9</v>
-      </c>
-      <c r="C54" s="5">
-        <v>2</v>
-      </c>
-      <c r="D54" s="5">
+      <c r="B54" s="4">
+        <v>9</v>
+      </c>
+      <c r="C54" s="4">
+        <v>2</v>
+      </c>
+      <c r="D54" s="4">
         <v>6</v>
       </c>
-      <c r="E54" s="5" t="s">
+      <c r="E54" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="F54" s="6">
+      <c r="F54" s="5">
         <v>46254</v>
       </c>
-      <c r="G54" s="5" t="s">
+      <c r="G54" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="55" ht="13.5" customHeight="1">
-      <c r="A55" s="4">
+      <c r="A55" s="3">
         <v>1848</v>
       </c>
-      <c r="B55" s="5">
-        <v>9</v>
-      </c>
-      <c r="C55" s="5">
-        <v>2</v>
-      </c>
-      <c r="D55" s="5">
+      <c r="B55" s="4">
+        <v>9</v>
+      </c>
+      <c r="C55" s="4">
+        <v>2</v>
+      </c>
+      <c r="D55" s="4">
         <v>7</v>
       </c>
-      <c r="E55" s="5" t="s">
+      <c r="E55" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="F55" s="6">
+      <c r="F55" s="5">
         <v>46274</v>
       </c>
-      <c r="G55" s="5" t="s">
+      <c r="G55" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="56" ht="13.5" customHeight="1">
-      <c r="A56" s="4">
+      <c r="A56" s="3">
         <v>1849</v>
       </c>
-      <c r="B56" s="5">
-        <v>9</v>
-      </c>
-      <c r="C56" s="5">
-        <v>2</v>
-      </c>
-      <c r="D56" s="5">
-        <v>9</v>
-      </c>
-      <c r="E56" s="5" t="s">
+      <c r="B56" s="4">
+        <v>9</v>
+      </c>
+      <c r="C56" s="4">
+        <v>2</v>
+      </c>
+      <c r="D56" s="4">
+        <v>9</v>
+      </c>
+      <c r="E56" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="F56" s="6">
+      <c r="F56" s="5">
         <v>46255</v>
       </c>
-      <c r="G56" s="5" t="s">
+      <c r="G56" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="57" ht="13.5" customHeight="1">
-      <c r="A57" s="4">
+      <c r="A57" s="3">
         <v>1850</v>
       </c>
-      <c r="B57" s="5">
-        <v>9</v>
-      </c>
-      <c r="C57" s="5">
+      <c r="B57" s="4">
+        <v>9</v>
+      </c>
+      <c r="C57" s="4">
         <v>3</v>
       </c>
-      <c r="D57" s="5">
+      <c r="D57" s="4">
         <v>11</v>
       </c>
-      <c r="E57" s="5" t="s">
+      <c r="E57" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="F57" s="6">
+      <c r="F57" s="5">
         <v>46255</v>
       </c>
-      <c r="G57" s="5" t="s">
+      <c r="G57" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="58" ht="13.5" customHeight="1">
-      <c r="A58" s="4">
+      <c r="A58" s="3">
         <v>1851</v>
       </c>
-      <c r="B58" s="5">
-        <v>9</v>
-      </c>
-      <c r="C58" s="5">
-        <v>2</v>
-      </c>
-      <c r="D58" s="5">
+      <c r="B58" s="4">
+        <v>9</v>
+      </c>
+      <c r="C58" s="4">
+        <v>2</v>
+      </c>
+      <c r="D58" s="4">
         <v>7</v>
       </c>
-      <c r="E58" s="5" t="s">
+      <c r="E58" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="F58" s="6">
+      <c r="F58" s="5">
         <v>46255</v>
       </c>
-      <c r="G58" s="5" t="s">
+      <c r="G58" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="59" ht="13.5" customHeight="1">
-      <c r="A59" s="4">
+      <c r="A59" s="3">
         <v>1852</v>
       </c>
-      <c r="B59" s="5">
-        <v>9</v>
-      </c>
-      <c r="C59" s="5">
-        <v>1</v>
-      </c>
-      <c r="D59" s="5">
+      <c r="B59" s="4">
+        <v>9</v>
+      </c>
+      <c r="C59" s="4">
+        <v>1</v>
+      </c>
+      <c r="D59" s="4">
         <v>4</v>
       </c>
-      <c r="E59" s="5" t="s">
+      <c r="E59" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="F59" s="6">
+      <c r="F59" s="5">
         <v>46255</v>
       </c>
-      <c r="G59" s="5" t="s">
+      <c r="G59" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="60" ht="13.5" customHeight="1">
-      <c r="A60" s="4">
+      <c r="A60" s="3">
         <v>1853</v>
       </c>
-      <c r="B60" s="5">
-        <v>9</v>
-      </c>
-      <c r="C60" s="5">
-        <v>1</v>
-      </c>
-      <c r="D60" s="5">
+      <c r="B60" s="4">
+        <v>9</v>
+      </c>
+      <c r="C60" s="4">
+        <v>1</v>
+      </c>
+      <c r="D60" s="4">
         <v>5</v>
       </c>
-      <c r="E60" s="5" t="s">
+      <c r="E60" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="F60" s="6">
+      <c r="F60" s="5">
         <v>46255</v>
       </c>
-      <c r="G60" s="5" t="s">
+      <c r="G60" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="61" ht="13.5" customHeight="1">
-      <c r="A61" s="4">
+      <c r="A61" s="3">
         <v>1854</v>
       </c>
-      <c r="B61" s="5">
-        <v>9</v>
-      </c>
-      <c r="C61" s="5">
-        <v>2</v>
-      </c>
-      <c r="D61" s="5">
-        <v>9</v>
-      </c>
-      <c r="E61" s="5" t="s">
+      <c r="B61" s="4">
+        <v>9</v>
+      </c>
+      <c r="C61" s="4">
+        <v>2</v>
+      </c>
+      <c r="D61" s="4">
+        <v>9</v>
+      </c>
+      <c r="E61" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="F61" s="6">
+      <c r="F61" s="5">
         <v>46256</v>
       </c>
-      <c r="G61" s="5" t="s">
+      <c r="G61" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="62" ht="13.5" customHeight="1">
-      <c r="A62" s="4">
+      <c r="A62" s="3">
         <v>1855</v>
       </c>
-      <c r="B62" s="5">
-        <v>9</v>
-      </c>
-      <c r="C62" s="5">
-        <v>2</v>
-      </c>
-      <c r="D62" s="5">
+      <c r="B62" s="4">
+        <v>9</v>
+      </c>
+      <c r="C62" s="4">
+        <v>2</v>
+      </c>
+      <c r="D62" s="4">
         <v>6</v>
       </c>
-      <c r="E62" s="5" t="s">
+      <c r="E62" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="F62" s="6">
+      <c r="F62" s="5">
         <v>46263</v>
       </c>
-      <c r="G62" s="5" t="s">
+      <c r="G62" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="63" ht="13.5" customHeight="1">
-      <c r="A63" s="4">
+      <c r="A63" s="3">
         <v>1856</v>
       </c>
-      <c r="B63" s="5">
-        <v>9</v>
-      </c>
-      <c r="C63" s="5">
+      <c r="B63" s="4">
+        <v>9</v>
+      </c>
+      <c r="C63" s="4">
         <v>3</v>
       </c>
-      <c r="D63" s="5">
+      <c r="D63" s="4">
         <v>11</v>
       </c>
-      <c r="E63" s="5" t="s">
+      <c r="E63" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="F63" s="6">
+      <c r="F63" s="5">
         <v>46260</v>
       </c>
-      <c r="G63" s="5" t="s">
+      <c r="G63" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="64" ht="13.5" customHeight="1">
-      <c r="A64" s="4">
+      <c r="A64" s="3">
         <v>1857</v>
       </c>
-      <c r="B64" s="5">
-        <v>9</v>
-      </c>
-      <c r="C64" s="5">
+      <c r="B64" s="4">
+        <v>9</v>
+      </c>
+      <c r="C64" s="4">
         <v>3</v>
       </c>
-      <c r="D64" s="5">
+      <c r="D64" s="4">
         <v>11</v>
       </c>
-      <c r="E64" s="5" t="s">
+      <c r="E64" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="F64" s="6">
+      <c r="F64" s="5">
         <v>46260</v>
       </c>
-      <c r="G64" s="5" t="s">
+      <c r="G64" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="65" ht="13.5" customHeight="1">
-      <c r="A65" s="4">
+      <c r="A65" s="3">
         <v>1858</v>
       </c>
-      <c r="B65" s="5">
-        <v>9</v>
-      </c>
-      <c r="C65" s="5">
+      <c r="B65" s="4">
+        <v>9</v>
+      </c>
+      <c r="C65" s="4">
         <v>3</v>
       </c>
-      <c r="D65" s="5">
+      <c r="D65" s="4">
         <v>11</v>
       </c>
-      <c r="E65" s="5" t="s">
+      <c r="E65" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="F65" s="6">
+      <c r="F65" s="5">
         <v>46262</v>
       </c>
-      <c r="G65" s="5" t="s">
+      <c r="G65" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="66" ht="13.5" customHeight="1">
-      <c r="A66" s="4">
+      <c r="A66" s="3">
         <v>1859</v>
       </c>
-      <c r="B66" s="5">
-        <v>9</v>
-      </c>
-      <c r="C66" s="5">
+      <c r="B66" s="4">
+        <v>9</v>
+      </c>
+      <c r="C66" s="4">
         <v>3</v>
       </c>
-      <c r="D66" s="5">
+      <c r="D66" s="4">
         <v>11</v>
       </c>
-      <c r="E66" s="5" t="s">
+      <c r="E66" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="F66" s="6">
+      <c r="F66" s="5">
         <v>46260</v>
       </c>
-      <c r="G66" s="5" t="s">
+      <c r="G66" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="67" ht="13.5" customHeight="1">
-      <c r="A67" s="4">
+      <c r="A67" s="3">
         <v>1860</v>
       </c>
-      <c r="B67" s="5">
-        <v>9</v>
-      </c>
-      <c r="C67" s="5">
+      <c r="B67" s="4">
+        <v>9</v>
+      </c>
+      <c r="C67" s="4">
         <v>3</v>
       </c>
-      <c r="D67" s="5">
+      <c r="D67" s="4">
         <v>11</v>
       </c>
-      <c r="E67" s="5" t="s">
+      <c r="E67" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="F67" s="6">
+      <c r="F67" s="5">
         <v>46260</v>
       </c>
-      <c r="G67" s="5" t="s">
+      <c r="G67" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="68" ht="13.5" customHeight="1">
-      <c r="A68" s="4">
+      <c r="A68" s="3">
         <v>1861</v>
       </c>
-      <c r="B68" s="5">
-        <v>9</v>
-      </c>
-      <c r="C68" s="5">
+      <c r="B68" s="4">
+        <v>9</v>
+      </c>
+      <c r="C68" s="4">
         <v>3</v>
       </c>
-      <c r="D68" s="5">
+      <c r="D68" s="4">
         <v>11</v>
       </c>
-      <c r="E68" s="5" t="s">
+      <c r="E68" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="F68" s="6">
+      <c r="F68" s="5">
         <v>46260</v>
       </c>
-      <c r="G68" s="5" t="s">
+      <c r="G68" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="69" ht="13.5" customHeight="1">
-      <c r="A69" s="4">
+      <c r="A69" s="3">
         <v>1862</v>
       </c>
-      <c r="B69" s="5">
-        <v>9</v>
-      </c>
-      <c r="C69" s="5">
+      <c r="B69" s="4">
+        <v>9</v>
+      </c>
+      <c r="C69" s="4">
         <v>3</v>
       </c>
-      <c r="D69" s="5">
+      <c r="D69" s="4">
         <v>11</v>
       </c>
-      <c r="E69" s="5" t="s">
+      <c r="E69" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="F69" s="6">
+      <c r="F69" s="5">
         <v>46260</v>
       </c>
-      <c r="G69" s="5" t="s">
+      <c r="G69" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="70" ht="13.5" customHeight="1">
-      <c r="A70" s="4">
+      <c r="A70" s="3">
         <v>1863</v>
       </c>
-      <c r="B70" s="5">
-        <v>9</v>
-      </c>
-      <c r="C70" s="5">
+      <c r="B70" s="4">
+        <v>9</v>
+      </c>
+      <c r="C70" s="4">
         <v>3</v>
       </c>
-      <c r="D70" s="5">
+      <c r="D70" s="4">
         <v>11</v>
       </c>
-      <c r="E70" s="5" t="s">
+      <c r="E70" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="F70" s="6">
+      <c r="F70" s="5">
         <v>46260</v>
       </c>
-      <c r="G70" s="5" t="s">
+      <c r="G70" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="71" ht="13.5" customHeight="1">
-      <c r="A71" s="4">
+      <c r="A71" s="3">
         <v>1864</v>
       </c>
-      <c r="B71" s="5">
-        <v>9</v>
-      </c>
-      <c r="C71" s="5">
+      <c r="B71" s="4">
+        <v>9</v>
+      </c>
+      <c r="C71" s="4">
         <v>3</v>
       </c>
-      <c r="D71" s="5">
+      <c r="D71" s="4">
         <v>11</v>
       </c>
-      <c r="E71" s="5" t="s">
+      <c r="E71" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="F71" s="6">
+      <c r="F71" s="5">
         <v>46260</v>
       </c>
-      <c r="G71" s="5" t="s">
+      <c r="G71" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="72" ht="13.5" customHeight="1">
-      <c r="A72" s="4">
+      <c r="A72" s="3">
         <v>1865</v>
       </c>
-      <c r="B72" s="5">
-        <v>9</v>
-      </c>
-      <c r="C72" s="5">
+      <c r="B72" s="4">
+        <v>9</v>
+      </c>
+      <c r="C72" s="4">
         <v>3</v>
       </c>
-      <c r="D72" s="5">
+      <c r="D72" s="4">
         <v>11</v>
       </c>
-      <c r="E72" s="5" t="s">
+      <c r="E72" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="F72" s="6">
+      <c r="F72" s="5">
         <v>46260</v>
       </c>
-      <c r="G72" s="5" t="s">
+      <c r="G72" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="73" ht="13.5" customHeight="1">
-      <c r="A73" s="4">
+      <c r="A73" s="3">
         <v>2028</v>
       </c>
-      <c r="B73" s="5">
-        <v>9</v>
-      </c>
-      <c r="C73" s="5">
+      <c r="B73" s="4">
+        <v>9</v>
+      </c>
+      <c r="C73" s="4">
         <v>3</v>
       </c>
-      <c r="D73" s="5">
+      <c r="D73" s="4">
         <v>13</v>
       </c>
-      <c r="E73" s="5" t="s">
+      <c r="E73" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="F73" s="6">
+      <c r="F73" s="5">
         <v>46276</v>
       </c>
-      <c r="G73" s="5" t="s">
+      <c r="G73" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="74" ht="13.5" customHeight="1">
-      <c r="A74" s="4">
+      <c r="A74" s="3">
         <v>1867</v>
       </c>
-      <c r="B74" s="5">
-        <v>9</v>
-      </c>
-      <c r="C74" s="5">
+      <c r="B74" s="4">
+        <v>9</v>
+      </c>
+      <c r="C74" s="4">
         <v>3</v>
       </c>
-      <c r="D74" s="5">
+      <c r="D74" s="4">
         <v>12</v>
       </c>
-      <c r="E74" s="5" t="s">
+      <c r="E74" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="F74" s="6">
+      <c r="F74" s="5">
         <v>46260</v>
       </c>
-      <c r="G74" s="5" t="s">
+      <c r="G74" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="75" ht="13.5" customHeight="1">
-      <c r="A75" s="4">
+      <c r="A75" s="3">
         <v>1868</v>
       </c>
-      <c r="B75" s="5">
-        <v>9</v>
-      </c>
-      <c r="C75" s="5">
+      <c r="B75" s="4">
+        <v>9</v>
+      </c>
+      <c r="C75" s="4">
         <v>3</v>
       </c>
-      <c r="D75" s="5">
+      <c r="D75" s="4">
         <v>12</v>
       </c>
-      <c r="E75" s="5" t="s">
+      <c r="E75" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="F75" s="6">
+      <c r="F75" s="5">
         <v>46260</v>
       </c>
-      <c r="G75" s="5" t="s">
+      <c r="G75" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="76" ht="13.5" customHeight="1">
-      <c r="A76" s="4">
+      <c r="A76" s="3">
         <v>1869</v>
       </c>
-      <c r="B76" s="5">
-        <v>9</v>
-      </c>
-      <c r="C76" s="5">
+      <c r="B76" s="4">
+        <v>9</v>
+      </c>
+      <c r="C76" s="4">
         <v>3</v>
       </c>
-      <c r="D76" s="5">
+      <c r="D76" s="4">
         <v>12</v>
       </c>
-      <c r="E76" s="5" t="s">
+      <c r="E76" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="F76" s="6">
+      <c r="F76" s="5">
         <v>46260</v>
       </c>
-      <c r="G76" s="5" t="s">
+      <c r="G76" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="77" ht="13.5" customHeight="1">
-      <c r="A77" s="4">
+      <c r="A77" s="3">
         <v>1870</v>
       </c>
-      <c r="B77" s="5">
-        <v>9</v>
-      </c>
-      <c r="C77" s="5">
+      <c r="B77" s="4">
+        <v>9</v>
+      </c>
+      <c r="C77" s="4">
         <v>3</v>
       </c>
-      <c r="D77" s="5">
+      <c r="D77" s="4">
         <v>12</v>
       </c>
-      <c r="E77" s="5" t="s">
+      <c r="E77" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="F77" s="6">
+      <c r="F77" s="5">
         <v>46260</v>
       </c>
-      <c r="G77" s="5" t="s">
+      <c r="G77" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="78" ht="13.5" customHeight="1">
-      <c r="A78" s="4">
+      <c r="A78" s="3">
         <v>1871</v>
       </c>
-      <c r="B78" s="5">
-        <v>9</v>
-      </c>
-      <c r="C78" s="5">
+      <c r="B78" s="4">
+        <v>9</v>
+      </c>
+      <c r="C78" s="4">
         <v>3</v>
       </c>
-      <c r="D78" s="5">
+      <c r="D78" s="4">
         <v>12</v>
       </c>
-      <c r="E78" s="5" t="s">
+      <c r="E78" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="F78" s="6">
+      <c r="F78" s="5">
         <v>46260</v>
       </c>
-      <c r="G78" s="5" t="s">
+      <c r="G78" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="79" ht="13.5" customHeight="1">
-      <c r="A79" s="4">
+      <c r="A79" s="3">
         <v>1872</v>
       </c>
-      <c r="B79" s="5">
-        <v>9</v>
-      </c>
-      <c r="C79" s="5">
+      <c r="B79" s="4">
+        <v>9</v>
+      </c>
+      <c r="C79" s="4">
         <v>3</v>
       </c>
-      <c r="D79" s="5">
+      <c r="D79" s="4">
         <v>12</v>
       </c>
-      <c r="E79" s="5" t="s">
+      <c r="E79" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="F79" s="6">
+      <c r="F79" s="5">
         <v>46260</v>
       </c>
-      <c r="G79" s="5" t="s">
+      <c r="G79" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="80" ht="13.5" customHeight="1">
-      <c r="A80" s="4">
+      <c r="A80" s="3">
         <v>1873</v>
       </c>
-      <c r="B80" s="5">
-        <v>9</v>
-      </c>
-      <c r="C80" s="5">
+      <c r="B80" s="4">
+        <v>9</v>
+      </c>
+      <c r="C80" s="4">
         <v>3</v>
       </c>
-      <c r="D80" s="5">
+      <c r="D80" s="4">
         <v>13</v>
       </c>
-      <c r="E80" s="5" t="s">
+      <c r="E80" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="F80" s="6">
+      <c r="F80" s="5">
         <v>46260</v>
       </c>
-      <c r="G80" s="5" t="s">
+      <c r="G80" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="81" ht="13.5" customHeight="1">
-      <c r="A81" s="4">
+      <c r="A81" s="3">
         <v>1874</v>
       </c>
-      <c r="B81" s="5">
-        <v>9</v>
-      </c>
-      <c r="C81" s="5">
+      <c r="B81" s="4">
+        <v>9</v>
+      </c>
+      <c r="C81" s="4">
         <v>3</v>
       </c>
-      <c r="D81" s="5">
+      <c r="D81" s="4">
         <v>13</v>
       </c>
-      <c r="E81" s="5" t="s">
+      <c r="E81" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="F81" s="6">
+      <c r="F81" s="5">
         <v>46260</v>
       </c>
-      <c r="G81" s="5" t="s">
+      <c r="G81" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="82" ht="13.5" customHeight="1">
-      <c r="A82" s="4">
+      <c r="A82" s="3">
         <v>1875</v>
       </c>
-      <c r="B82" s="5">
-        <v>9</v>
-      </c>
-      <c r="C82" s="5">
+      <c r="B82" s="4">
+        <v>9</v>
+      </c>
+      <c r="C82" s="4">
         <v>3</v>
       </c>
-      <c r="D82" s="5">
+      <c r="D82" s="4">
         <v>13</v>
       </c>
-      <c r="E82" s="5" t="s">
+      <c r="E82" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="F82" s="6">
+      <c r="F82" s="5">
         <v>46260</v>
       </c>
-      <c r="G82" s="5" t="s">
+      <c r="G82" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="83" ht="13.5" customHeight="1">
-      <c r="A83" s="4">
+      <c r="A83" s="3">
         <v>1877</v>
       </c>
-      <c r="B83" s="5">
-        <v>9</v>
-      </c>
-      <c r="C83" s="5">
+      <c r="B83" s="4">
+        <v>9</v>
+      </c>
+      <c r="C83" s="4">
         <v>3</v>
       </c>
-      <c r="D83" s="5">
+      <c r="D83" s="4">
         <v>14</v>
       </c>
-      <c r="E83" s="5">
+      <c r="E83" s="4">
         <v>20186</v>
       </c>
-      <c r="F83" s="6">
+      <c r="F83" s="5">
         <v>46260</v>
       </c>
-      <c r="G83" s="5" t="s">
+      <c r="G83" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="84" ht="13.5" customHeight="1">
-      <c r="A84" s="4">
+      <c r="A84" s="3">
         <v>1878</v>
       </c>
-      <c r="B84" s="5">
-        <v>9</v>
-      </c>
-      <c r="C84" s="5">
+      <c r="B84" s="4">
+        <v>9</v>
+      </c>
+      <c r="C84" s="4">
         <v>3</v>
       </c>
-      <c r="D84" s="5">
+      <c r="D84" s="4">
         <v>14</v>
       </c>
-      <c r="E84" s="5" t="s">
+      <c r="E84" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="F84" s="6">
+      <c r="F84" s="5">
         <v>46260</v>
       </c>
-      <c r="G84" s="5" t="s">
+      <c r="G84" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="85" ht="13.5" customHeight="1">
-      <c r="A85" s="4">
+      <c r="A85" s="3">
         <v>1879</v>
       </c>
-      <c r="B85" s="5">
-        <v>9</v>
-      </c>
-      <c r="C85" s="5">
+      <c r="B85" s="4">
+        <v>9</v>
+      </c>
+      <c r="C85" s="4">
         <v>3</v>
       </c>
-      <c r="D85" s="5">
+      <c r="D85" s="4">
         <v>14</v>
       </c>
-      <c r="E85" s="5" t="s">
+      <c r="E85" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="F85" s="6">
+      <c r="F85" s="5">
         <v>46260</v>
       </c>
-      <c r="G85" s="5" t="s">
+      <c r="G85" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="86" ht="13.5" customHeight="1">
-      <c r="A86" s="4">
+      <c r="A86" s="3">
         <v>1880</v>
       </c>
-      <c r="B86" s="5">
-        <v>9</v>
-      </c>
-      <c r="C86" s="5">
-        <v>2</v>
-      </c>
-      <c r="D86" s="5">
+      <c r="B86" s="4">
+        <v>9</v>
+      </c>
+      <c r="C86" s="4">
+        <v>2</v>
+      </c>
+      <c r="D86" s="4">
         <v>10</v>
       </c>
-      <c r="E86" s="5" t="s">
+      <c r="E86" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="F86" s="6">
+      <c r="F86" s="5">
         <v>46260</v>
       </c>
-      <c r="G86" s="5" t="s">
+      <c r="G86" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="87" ht="13.5" customHeight="1">
-      <c r="A87" s="4">
+      <c r="A87" s="3">
         <v>1881</v>
       </c>
-      <c r="B87" s="5">
-        <v>9</v>
-      </c>
-      <c r="C87" s="5">
-        <v>2</v>
-      </c>
-      <c r="D87" s="5">
+      <c r="B87" s="4">
+        <v>9</v>
+      </c>
+      <c r="C87" s="4">
+        <v>2</v>
+      </c>
+      <c r="D87" s="4">
         <v>10</v>
       </c>
-      <c r="E87" s="5" t="s">
+      <c r="E87" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="F87" s="6">
+      <c r="F87" s="5">
         <v>46261</v>
       </c>
-      <c r="G87" s="5" t="s">
+      <c r="G87" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="88" ht="13.5" customHeight="1">
-      <c r="A88" s="4">
+      <c r="A88" s="3">
         <v>1882</v>
       </c>
-      <c r="B88" s="5">
-        <v>9</v>
-      </c>
-      <c r="C88" s="5">
-        <v>2</v>
-      </c>
-      <c r="D88" s="5">
+      <c r="B88" s="4">
+        <v>9</v>
+      </c>
+      <c r="C88" s="4">
+        <v>2</v>
+      </c>
+      <c r="D88" s="4">
         <v>10</v>
       </c>
-      <c r="E88" s="5" t="s">
+      <c r="E88" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="F88" s="6">
+      <c r="F88" s="5">
         <v>46261</v>
       </c>
-      <c r="G88" s="5" t="s">
+      <c r="G88" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="89" ht="13.5" customHeight="1">
-      <c r="A89" s="4">
+      <c r="A89" s="3">
         <v>1883</v>
       </c>
-      <c r="B89" s="5">
-        <v>9</v>
-      </c>
-      <c r="C89" s="5">
-        <v>2</v>
-      </c>
-      <c r="D89" s="5">
+      <c r="B89" s="4">
+        <v>9</v>
+      </c>
+      <c r="C89" s="4">
+        <v>2</v>
+      </c>
+      <c r="D89" s="4">
         <v>10</v>
       </c>
-      <c r="E89" s="5" t="s">
+      <c r="E89" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="F89" s="6">
+      <c r="F89" s="5">
         <v>46261</v>
       </c>
-      <c r="G89" s="5" t="s">
+      <c r="G89" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="90" ht="13.5" customHeight="1">
-      <c r="A90" s="4">
+      <c r="A90" s="3">
         <v>1884</v>
       </c>
-      <c r="B90" s="5">
-        <v>9</v>
-      </c>
-      <c r="C90" s="5">
-        <v>2</v>
-      </c>
-      <c r="D90" s="5">
+      <c r="B90" s="4">
+        <v>9</v>
+      </c>
+      <c r="C90" s="4">
+        <v>2</v>
+      </c>
+      <c r="D90" s="4">
         <v>10</v>
       </c>
-      <c r="E90" s="5" t="s">
+      <c r="E90" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="F90" s="6">
+      <c r="F90" s="5">
         <v>46261</v>
       </c>
-      <c r="G90" s="5" t="s">
+      <c r="G90" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="91" ht="13.5" customHeight="1">
-      <c r="A91" s="4">
+      <c r="A91" s="3">
         <v>1885</v>
       </c>
-      <c r="B91" s="5">
-        <v>9</v>
-      </c>
-      <c r="C91" s="5">
-        <v>2</v>
-      </c>
-      <c r="D91" s="5">
+      <c r="B91" s="4">
+        <v>9</v>
+      </c>
+      <c r="C91" s="4">
+        <v>2</v>
+      </c>
+      <c r="D91" s="4">
         <v>10</v>
       </c>
-      <c r="E91" s="5" t="s">
+      <c r="E91" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="F91" s="6">
+      <c r="F91" s="5">
         <v>46261</v>
       </c>
-      <c r="G91" s="5" t="s">
+      <c r="G91" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="92" ht="13.5" customHeight="1">
-      <c r="A92" s="4">
+      <c r="A92" s="3">
         <v>1886</v>
       </c>
-      <c r="B92" s="5">
-        <v>9</v>
-      </c>
-      <c r="C92" s="5">
-        <v>2</v>
-      </c>
-      <c r="D92" s="5">
+      <c r="B92" s="4">
+        <v>9</v>
+      </c>
+      <c r="C92" s="4">
+        <v>2</v>
+      </c>
+      <c r="D92" s="4">
         <v>10</v>
       </c>
-      <c r="E92" s="5" t="s">
+      <c r="E92" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="F92" s="6">
+      <c r="F92" s="5">
         <v>46261</v>
       </c>
-      <c r="G92" s="5" t="s">
+      <c r="G92" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="93" ht="13.5" customHeight="1">
-      <c r="A93" s="4">
+      <c r="A93" s="3">
         <v>1887</v>
       </c>
-      <c r="B93" s="5">
-        <v>9</v>
-      </c>
-      <c r="C93" s="5">
-        <v>2</v>
-      </c>
-      <c r="D93" s="5">
-        <v>9</v>
-      </c>
-      <c r="E93" s="5" t="s">
+      <c r="B93" s="4">
+        <v>9</v>
+      </c>
+      <c r="C93" s="4">
+        <v>2</v>
+      </c>
+      <c r="D93" s="4">
+        <v>9</v>
+      </c>
+      <c r="E93" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="F93" s="6">
+      <c r="F93" s="5">
         <v>46261</v>
       </c>
-      <c r="G93" s="5" t="s">
+      <c r="G93" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="94" ht="13.5" customHeight="1">
-      <c r="A94" s="4">
+      <c r="A94" s="3">
         <v>1888</v>
       </c>
-      <c r="B94" s="5">
-        <v>9</v>
-      </c>
-      <c r="C94" s="5">
-        <v>2</v>
-      </c>
-      <c r="D94" s="5">
-        <v>9</v>
-      </c>
-      <c r="E94" s="5" t="s">
+      <c r="B94" s="4">
+        <v>9</v>
+      </c>
+      <c r="C94" s="4">
+        <v>2</v>
+      </c>
+      <c r="D94" s="4">
+        <v>9</v>
+      </c>
+      <c r="E94" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="F94" s="6">
+      <c r="F94" s="5">
         <v>46261</v>
       </c>
-      <c r="G94" s="5" t="s">
+      <c r="G94" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="95" ht="13.5" customHeight="1">
-      <c r="A95" s="4">
+      <c r="A95" s="3">
         <v>1889</v>
       </c>
-      <c r="B95" s="5">
-        <v>9</v>
-      </c>
-      <c r="C95" s="5">
-        <v>2</v>
-      </c>
-      <c r="D95" s="5">
-        <v>9</v>
-      </c>
-      <c r="E95" s="5" t="s">
+      <c r="B95" s="4">
+        <v>9</v>
+      </c>
+      <c r="C95" s="4">
+        <v>2</v>
+      </c>
+      <c r="D95" s="4">
+        <v>9</v>
+      </c>
+      <c r="E95" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="F95" s="6">
+      <c r="F95" s="5">
         <v>46261</v>
       </c>
-      <c r="G95" s="5" t="s">
+      <c r="G95" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="96" ht="13.5" customHeight="1">
-      <c r="A96" s="4">
+      <c r="A96" s="3">
         <v>1890</v>
       </c>
-      <c r="B96" s="5">
-        <v>9</v>
-      </c>
-      <c r="C96" s="5">
-        <v>2</v>
-      </c>
-      <c r="D96" s="5">
-        <v>9</v>
-      </c>
-      <c r="E96" s="5" t="s">
+      <c r="B96" s="4">
+        <v>9</v>
+      </c>
+      <c r="C96" s="4">
+        <v>2</v>
+      </c>
+      <c r="D96" s="4">
+        <v>9</v>
+      </c>
+      <c r="E96" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="F96" s="6">
+      <c r="F96" s="5">
         <v>46261</v>
       </c>
-      <c r="G96" s="5" t="s">
+      <c r="G96" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="97" ht="13.5" customHeight="1">
-      <c r="A97" s="4">
+      <c r="A97" s="3">
         <v>1891</v>
       </c>
-      <c r="B97" s="5">
-        <v>9</v>
-      </c>
-      <c r="C97" s="5">
-        <v>2</v>
-      </c>
-      <c r="D97" s="5">
-        <v>9</v>
-      </c>
-      <c r="E97" s="5" t="s">
+      <c r="B97" s="4">
+        <v>9</v>
+      </c>
+      <c r="C97" s="4">
+        <v>2</v>
+      </c>
+      <c r="D97" s="4">
+        <v>9</v>
+      </c>
+      <c r="E97" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="F97" s="6">
+      <c r="F97" s="5">
         <v>46261</v>
       </c>
-      <c r="G97" s="5" t="s">
+      <c r="G97" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="98" ht="13.5" customHeight="1">
-      <c r="A98" s="4">
+      <c r="A98" s="3">
         <v>1892</v>
       </c>
-      <c r="B98" s="5">
-        <v>9</v>
-      </c>
-      <c r="C98" s="5">
-        <v>2</v>
-      </c>
-      <c r="D98" s="5">
-        <v>9</v>
-      </c>
-      <c r="E98" s="5" t="s">
+      <c r="B98" s="4">
+        <v>9</v>
+      </c>
+      <c r="C98" s="4">
+        <v>2</v>
+      </c>
+      <c r="D98" s="4">
+        <v>9</v>
+      </c>
+      <c r="E98" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="F98" s="6">
+      <c r="F98" s="5">
         <v>46261</v>
       </c>
-      <c r="G98" s="5" t="s">
+      <c r="G98" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="99" ht="13.5" customHeight="1">
-      <c r="A99" s="4">
+      <c r="A99" s="3">
         <v>1893</v>
       </c>
-      <c r="B99" s="5">
-        <v>9</v>
-      </c>
-      <c r="C99" s="5">
-        <v>2</v>
-      </c>
-      <c r="D99" s="5">
-        <v>9</v>
-      </c>
-      <c r="E99" s="5" t="s">
+      <c r="B99" s="4">
+        <v>9</v>
+      </c>
+      <c r="C99" s="4">
+        <v>2</v>
+      </c>
+      <c r="D99" s="4">
+        <v>9</v>
+      </c>
+      <c r="E99" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="F99" s="6">
+      <c r="F99" s="5">
         <v>46261</v>
       </c>
-      <c r="G99" s="5" t="s">
+      <c r="G99" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="100" ht="13.5" customHeight="1">
-      <c r="A100" s="4">
+      <c r="A100" s="3">
         <v>1894</v>
       </c>
-      <c r="B100" s="5">
-        <v>9</v>
-      </c>
-      <c r="C100" s="5">
-        <v>2</v>
-      </c>
-      <c r="D100" s="5">
-        <v>9</v>
-      </c>
-      <c r="E100" s="5" t="s">
+      <c r="B100" s="4">
+        <v>9</v>
+      </c>
+      <c r="C100" s="4">
+        <v>2</v>
+      </c>
+      <c r="D100" s="4">
+        <v>9</v>
+      </c>
+      <c r="E100" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="F100" s="6">
+      <c r="F100" s="5">
         <v>46261</v>
       </c>
-      <c r="G100" s="5" t="s">
+      <c r="G100" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="101" ht="13.5" customHeight="1">
-      <c r="A101" s="4">
+      <c r="A101" s="3">
         <v>1895</v>
       </c>
-      <c r="B101" s="5">
-        <v>9</v>
-      </c>
-      <c r="C101" s="5">
-        <v>2</v>
-      </c>
-      <c r="D101" s="5">
-        <v>9</v>
-      </c>
-      <c r="E101" s="5" t="s">
+      <c r="B101" s="4">
+        <v>9</v>
+      </c>
+      <c r="C101" s="4">
+        <v>2</v>
+      </c>
+      <c r="D101" s="4">
+        <v>9</v>
+      </c>
+      <c r="E101" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="F101" s="6">
+      <c r="F101" s="5">
         <v>46261</v>
       </c>
-      <c r="G101" s="5" t="s">
+      <c r="G101" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="102" ht="13.5" customHeight="1">
-      <c r="A102" s="4">
+      <c r="A102" s="3">
         <v>1896</v>
       </c>
-      <c r="B102" s="5">
-        <v>9</v>
-      </c>
-      <c r="C102" s="5">
-        <v>2</v>
-      </c>
-      <c r="D102" s="5">
-        <v>9</v>
-      </c>
-      <c r="E102" s="5" t="s">
+      <c r="B102" s="4">
+        <v>9</v>
+      </c>
+      <c r="C102" s="4">
+        <v>2</v>
+      </c>
+      <c r="D102" s="4">
+        <v>9</v>
+      </c>
+      <c r="E102" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="F102" s="6">
+      <c r="F102" s="5">
         <v>46261</v>
       </c>
-      <c r="G102" s="5" t="s">
+      <c r="G102" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="103" ht="13.5" customHeight="1">
-      <c r="A103" s="4">
+      <c r="A103" s="3">
         <v>1897</v>
       </c>
-      <c r="B103" s="5">
-        <v>9</v>
-      </c>
-      <c r="C103" s="5">
-        <v>2</v>
-      </c>
-      <c r="D103" s="5">
-        <v>9</v>
-      </c>
-      <c r="E103" s="5" t="s">
+      <c r="B103" s="4">
+        <v>9</v>
+      </c>
+      <c r="C103" s="4">
+        <v>2</v>
+      </c>
+      <c r="D103" s="4">
+        <v>9</v>
+      </c>
+      <c r="E103" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="F103" s="6">
+      <c r="F103" s="5">
         <v>46261</v>
       </c>
-      <c r="G103" s="5" t="s">
+      <c r="G103" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="104" ht="13.5" customHeight="1">
-      <c r="A104" s="4">
+      <c r="A104" s="3">
         <v>1898</v>
       </c>
-      <c r="B104" s="5">
-        <v>9</v>
-      </c>
-      <c r="C104" s="5">
-        <v>2</v>
-      </c>
-      <c r="D104" s="5">
-        <v>9</v>
-      </c>
-      <c r="E104" s="5" t="s">
+      <c r="B104" s="4">
+        <v>9</v>
+      </c>
+      <c r="C104" s="4">
+        <v>2</v>
+      </c>
+      <c r="D104" s="4">
+        <v>9</v>
+      </c>
+      <c r="E104" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="F104" s="6">
+      <c r="F104" s="5">
         <v>46261</v>
       </c>
-      <c r="G104" s="5" t="s">
+      <c r="G104" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="105" ht="13.5" customHeight="1">
-      <c r="A105" s="4">
+      <c r="A105" s="3">
         <v>1899</v>
       </c>
-      <c r="B105" s="5">
-        <v>9</v>
-      </c>
-      <c r="C105" s="5">
-        <v>2</v>
-      </c>
-      <c r="D105" s="5">
-        <v>8</v>
-      </c>
-      <c r="E105" s="5" t="s">
+      <c r="B105" s="4">
+        <v>9</v>
+      </c>
+      <c r="C105" s="4">
+        <v>2</v>
+      </c>
+      <c r="D105" s="4">
+        <v>8</v>
+      </c>
+      <c r="E105" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="F105" s="6">
+      <c r="F105" s="5">
         <v>46261</v>
       </c>
-      <c r="G105" s="5" t="s">
+      <c r="G105" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="106" ht="13.5" customHeight="1">
-      <c r="A106" s="4">
+      <c r="A106" s="3">
         <v>1900</v>
       </c>
-      <c r="B106" s="5">
-        <v>9</v>
-      </c>
-      <c r="C106" s="5">
-        <v>2</v>
-      </c>
-      <c r="D106" s="5">
-        <v>8</v>
-      </c>
-      <c r="E106" s="5" t="s">
+      <c r="B106" s="4">
+        <v>9</v>
+      </c>
+      <c r="C106" s="4">
+        <v>2</v>
+      </c>
+      <c r="D106" s="4">
+        <v>8</v>
+      </c>
+      <c r="E106" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="F106" s="6">
+      <c r="F106" s="5">
         <v>46261</v>
       </c>
-      <c r="G106" s="5" t="s">
+      <c r="G106" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="107" ht="13.5" customHeight="1">
-      <c r="A107" s="4">
+      <c r="A107" s="3">
         <v>1901</v>
       </c>
-      <c r="B107" s="5">
-        <v>9</v>
-      </c>
-      <c r="C107" s="5">
-        <v>2</v>
-      </c>
-      <c r="D107" s="5">
-        <v>8</v>
-      </c>
-      <c r="E107" s="5" t="s">
+      <c r="B107" s="4">
+        <v>9</v>
+      </c>
+      <c r="C107" s="4">
+        <v>2</v>
+      </c>
+      <c r="D107" s="4">
+        <v>8</v>
+      </c>
+      <c r="E107" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="F107" s="6">
+      <c r="F107" s="5">
         <v>46261</v>
       </c>
-      <c r="G107" s="5" t="s">
+      <c r="G107" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="108" ht="13.5" customHeight="1">
-      <c r="A108" s="4">
+      <c r="A108" s="3">
         <v>1902</v>
       </c>
-      <c r="B108" s="5">
-        <v>9</v>
-      </c>
-      <c r="C108" s="5">
-        <v>2</v>
-      </c>
-      <c r="D108" s="5">
-        <v>8</v>
-      </c>
-      <c r="E108" s="5" t="s">
+      <c r="B108" s="4">
+        <v>9</v>
+      </c>
+      <c r="C108" s="4">
+        <v>2</v>
+      </c>
+      <c r="D108" s="4">
+        <v>8</v>
+      </c>
+      <c r="E108" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="F108" s="6">
+      <c r="F108" s="5">
         <v>46261</v>
       </c>
-      <c r="G108" s="5" t="s">
+      <c r="G108" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="109" ht="13.5" customHeight="1">
-      <c r="A109" s="4">
+      <c r="A109" s="3">
         <v>1903</v>
       </c>
-      <c r="B109" s="5">
-        <v>9</v>
-      </c>
-      <c r="C109" s="5">
-        <v>2</v>
-      </c>
-      <c r="D109" s="5">
-        <v>8</v>
-      </c>
-      <c r="E109" s="5" t="s">
+      <c r="B109" s="4">
+        <v>9</v>
+      </c>
+      <c r="C109" s="4">
+        <v>2</v>
+      </c>
+      <c r="D109" s="4">
+        <v>8</v>
+      </c>
+      <c r="E109" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="F109" s="6">
+      <c r="F109" s="5">
         <v>46261</v>
       </c>
-      <c r="G109" s="5" t="s">
+      <c r="G109" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="110" ht="13.5" customHeight="1">
-      <c r="A110" s="4">
+      <c r="A110" s="3">
         <v>1904</v>
       </c>
-      <c r="B110" s="5">
-        <v>9</v>
-      </c>
-      <c r="C110" s="5">
-        <v>2</v>
-      </c>
-      <c r="D110" s="5">
-        <v>8</v>
-      </c>
-      <c r="E110" s="5" t="s">
+      <c r="B110" s="4">
+        <v>9</v>
+      </c>
+      <c r="C110" s="4">
+        <v>2</v>
+      </c>
+      <c r="D110" s="4">
+        <v>8</v>
+      </c>
+      <c r="E110" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="F110" s="6">
+      <c r="F110" s="5">
         <v>46261</v>
       </c>
-      <c r="G110" s="5" t="s">
+      <c r="G110" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="111" ht="13.5" customHeight="1">
-      <c r="A111" s="4">
+      <c r="A111" s="3">
         <v>1905</v>
       </c>
-      <c r="B111" s="5">
-        <v>9</v>
-      </c>
-      <c r="C111" s="5">
-        <v>2</v>
-      </c>
-      <c r="D111" s="5">
+      <c r="B111" s="4">
+        <v>9</v>
+      </c>
+      <c r="C111" s="4">
+        <v>2</v>
+      </c>
+      <c r="D111" s="4">
         <v>7</v>
       </c>
-      <c r="E111" s="5" t="s">
+      <c r="E111" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="F111" s="6">
+      <c r="F111" s="5">
         <v>46261</v>
       </c>
-      <c r="G111" s="5" t="s">
+      <c r="G111" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="112" ht="13.5" customHeight="1">
-      <c r="A112" s="4">
+      <c r="A112" s="3">
         <v>1906</v>
       </c>
-      <c r="B112" s="5">
-        <v>9</v>
-      </c>
-      <c r="C112" s="5">
-        <v>2</v>
-      </c>
-      <c r="D112" s="5">
+      <c r="B112" s="4">
+        <v>9</v>
+      </c>
+      <c r="C112" s="4">
+        <v>2</v>
+      </c>
+      <c r="D112" s="4">
         <v>7</v>
       </c>
-      <c r="E112" s="5" t="s">
+      <c r="E112" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="F112" s="6">
+      <c r="F112" s="5">
         <v>46261</v>
       </c>
-      <c r="G112" s="5" t="s">
+      <c r="G112" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="113" ht="13.5" customHeight="1">
-      <c r="A113" s="4">
+      <c r="A113" s="3">
         <v>1907</v>
       </c>
-      <c r="B113" s="5">
-        <v>9</v>
-      </c>
-      <c r="C113" s="5">
-        <v>2</v>
-      </c>
-      <c r="D113" s="5">
+      <c r="B113" s="4">
+        <v>9</v>
+      </c>
+      <c r="C113" s="4">
+        <v>2</v>
+      </c>
+      <c r="D113" s="4">
         <v>7</v>
       </c>
-      <c r="E113" s="5" t="s">
+      <c r="E113" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="F113" s="6">
+      <c r="F113" s="5">
         <v>46261</v>
       </c>
-      <c r="G113" s="5" t="s">
+      <c r="G113" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="114" ht="13.5" customHeight="1">
-      <c r="A114" s="4">
+      <c r="A114" s="3">
         <v>1908</v>
       </c>
-      <c r="B114" s="5">
-        <v>9</v>
-      </c>
-      <c r="C114" s="5">
-        <v>2</v>
-      </c>
-      <c r="D114" s="5">
+      <c r="B114" s="4">
+        <v>9</v>
+      </c>
+      <c r="C114" s="4">
+        <v>2</v>
+      </c>
+      <c r="D114" s="4">
         <v>7</v>
       </c>
-      <c r="E114" s="5" t="s">
+      <c r="E114" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="F114" s="6">
+      <c r="F114" s="5">
         <v>46261</v>
       </c>
-      <c r="G114" s="5" t="s">
+      <c r="G114" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="115" ht="13.5" customHeight="1">
-      <c r="A115" s="4">
+      <c r="A115" s="3">
         <v>1909</v>
       </c>
-      <c r="B115" s="5">
-        <v>9</v>
-      </c>
-      <c r="C115" s="5">
-        <v>2</v>
-      </c>
-      <c r="D115" s="5">
+      <c r="B115" s="4">
+        <v>9</v>
+      </c>
+      <c r="C115" s="4">
+        <v>2</v>
+      </c>
+      <c r="D115" s="4">
         <v>7</v>
       </c>
-      <c r="E115" s="5" t="s">
+      <c r="E115" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="F115" s="6">
+      <c r="F115" s="5">
         <v>46261</v>
       </c>
-      <c r="G115" s="5" t="s">
+      <c r="G115" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="116" ht="13.5" customHeight="1">
-      <c r="A116" s="4">
+      <c r="A116" s="3">
         <v>1910</v>
       </c>
-      <c r="B116" s="5">
-        <v>9</v>
-      </c>
-      <c r="C116" s="5">
-        <v>2</v>
-      </c>
-      <c r="D116" s="5">
+      <c r="B116" s="4">
+        <v>9</v>
+      </c>
+      <c r="C116" s="4">
+        <v>2</v>
+      </c>
+      <c r="D116" s="4">
         <v>6</v>
       </c>
-      <c r="E116" s="5" t="s">
+      <c r="E116" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="F116" s="6">
+      <c r="F116" s="5">
         <v>46276</v>
       </c>
-      <c r="G116" s="5" t="s">
+      <c r="G116" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="117" ht="13.5" customHeight="1">
-      <c r="A117" s="4">
+      <c r="A117" s="3">
         <v>1911</v>
       </c>
-      <c r="B117" s="5">
-        <v>9</v>
-      </c>
-      <c r="C117" s="5">
-        <v>2</v>
-      </c>
-      <c r="D117" s="5">
+      <c r="B117" s="4">
+        <v>9</v>
+      </c>
+      <c r="C117" s="4">
+        <v>2</v>
+      </c>
+      <c r="D117" s="4">
         <v>7</v>
       </c>
-      <c r="E117" s="5" t="s">
+      <c r="E117" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="F117" s="6">
+      <c r="F117" s="5">
         <v>46261</v>
       </c>
-      <c r="G117" s="5" t="s">
+      <c r="G117" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="118" ht="13.5" customHeight="1">
-      <c r="A118" s="4">
+      <c r="A118" s="3">
         <v>1912</v>
       </c>
-      <c r="B118" s="5">
-        <v>9</v>
-      </c>
-      <c r="C118" s="5">
-        <v>2</v>
-      </c>
-      <c r="D118" s="5">
+      <c r="B118" s="4">
+        <v>9</v>
+      </c>
+      <c r="C118" s="4">
+        <v>2</v>
+      </c>
+      <c r="D118" s="4">
         <v>7</v>
       </c>
-      <c r="E118" s="5" t="s">
+      <c r="E118" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="F118" s="6">
+      <c r="F118" s="5">
         <v>46261</v>
       </c>
-      <c r="G118" s="5" t="s">
+      <c r="G118" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="119" ht="13.5" customHeight="1">
-      <c r="A119" s="4">
+      <c r="A119" s="3">
         <v>1913</v>
       </c>
-      <c r="B119" s="5">
-        <v>9</v>
-      </c>
-      <c r="C119" s="5">
-        <v>2</v>
-      </c>
-      <c r="D119" s="5">
+      <c r="B119" s="4">
+        <v>9</v>
+      </c>
+      <c r="C119" s="4">
+        <v>2</v>
+      </c>
+      <c r="D119" s="4">
         <v>7</v>
       </c>
-      <c r="E119" s="5" t="s">
+      <c r="E119" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="F119" s="6">
+      <c r="F119" s="5">
         <v>46261</v>
       </c>
-      <c r="G119" s="5" t="s">
+      <c r="G119" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="120" ht="13.5" customHeight="1">
-      <c r="A120" s="4">
+      <c r="A120" s="3">
         <v>1914</v>
       </c>
-      <c r="B120" s="5">
-        <v>9</v>
-      </c>
-      <c r="C120" s="5">
-        <v>2</v>
-      </c>
-      <c r="D120" s="5">
+      <c r="B120" s="4">
+        <v>9</v>
+      </c>
+      <c r="C120" s="4">
+        <v>2</v>
+      </c>
+      <c r="D120" s="4">
         <v>7</v>
       </c>
-      <c r="E120" s="5" t="s">
+      <c r="E120" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="F120" s="6">
+      <c r="F120" s="5">
         <v>46261</v>
       </c>
-      <c r="G120" s="5" t="s">
+      <c r="G120" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="121" ht="13.5" customHeight="1">
-      <c r="A121" s="4">
+      <c r="A121" s="3">
         <v>1915</v>
       </c>
-      <c r="B121" s="5">
-        <v>9</v>
-      </c>
-      <c r="C121" s="5">
-        <v>2</v>
-      </c>
-      <c r="D121" s="5">
+      <c r="B121" s="4">
+        <v>9</v>
+      </c>
+      <c r="C121" s="4">
+        <v>2</v>
+      </c>
+      <c r="D121" s="4">
         <v>6</v>
       </c>
-      <c r="E121" s="5" t="s">
+      <c r="E121" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="F121" s="6">
+      <c r="F121" s="5">
         <v>46261</v>
       </c>
-      <c r="G121" s="5" t="s">
+      <c r="G121" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="122" ht="13.5" customHeight="1">
-      <c r="A122" s="4">
+      <c r="A122" s="3">
         <v>1916</v>
       </c>
-      <c r="B122" s="5">
-        <v>9</v>
-      </c>
-      <c r="C122" s="5">
-        <v>2</v>
-      </c>
-      <c r="D122" s="5">
+      <c r="B122" s="4">
+        <v>9</v>
+      </c>
+      <c r="C122" s="4">
+        <v>2</v>
+      </c>
+      <c r="D122" s="4">
         <v>6</v>
       </c>
-      <c r="E122" s="5" t="s">
+      <c r="E122" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="F122" s="6">
+      <c r="F122" s="5">
         <v>46261</v>
       </c>
-      <c r="G122" s="5" t="s">
+      <c r="G122" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="123" ht="13.5" customHeight="1">
-      <c r="A123" s="4">
+      <c r="A123" s="3">
         <v>1917</v>
       </c>
-      <c r="B123" s="5">
-        <v>9</v>
-      </c>
-      <c r="C123" s="5">
-        <v>2</v>
-      </c>
-      <c r="D123" s="5">
+      <c r="B123" s="4">
+        <v>9</v>
+      </c>
+      <c r="C123" s="4">
+        <v>2</v>
+      </c>
+      <c r="D123" s="4">
         <v>6</v>
       </c>
-      <c r="E123" s="5" t="s">
+      <c r="E123" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="F123" s="6">
+      <c r="F123" s="5">
         <v>46261</v>
       </c>
-      <c r="G123" s="5" t="s">
+      <c r="G123" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="124" ht="13.5" customHeight="1">
-      <c r="A124" s="4">
+      <c r="A124" s="3">
         <v>1918</v>
       </c>
-      <c r="B124" s="5">
-        <v>9</v>
-      </c>
-      <c r="C124" s="5">
-        <v>2</v>
-      </c>
-      <c r="D124" s="5">
+      <c r="B124" s="4">
+        <v>9</v>
+      </c>
+      <c r="C124" s="4">
+        <v>2</v>
+      </c>
+      <c r="D124" s="4">
         <v>6</v>
       </c>
-      <c r="E124" s="5" t="s">
+      <c r="E124" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="F124" s="6">
+      <c r="F124" s="5">
         <v>46261</v>
       </c>
-      <c r="G124" s="5" t="s">
+      <c r="G124" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="125" ht="13.5" customHeight="1">
-      <c r="A125" s="4">
+      <c r="A125" s="3">
         <v>1919</v>
       </c>
-      <c r="B125" s="5">
-        <v>9</v>
-      </c>
-      <c r="C125" s="5">
-        <v>2</v>
-      </c>
-      <c r="D125" s="5">
+      <c r="B125" s="4">
+        <v>9</v>
+      </c>
+      <c r="C125" s="4">
+        <v>2</v>
+      </c>
+      <c r="D125" s="4">
         <v>6</v>
       </c>
-      <c r="E125" s="5" t="s">
+      <c r="E125" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="F125" s="6">
+      <c r="F125" s="5">
         <v>46261</v>
       </c>
-      <c r="G125" s="5" t="s">
+      <c r="G125" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="126" ht="13.5" customHeight="1">
-      <c r="A126" s="4">
+      <c r="A126" s="3">
         <v>1920</v>
       </c>
-      <c r="B126" s="5">
-        <v>9</v>
-      </c>
-      <c r="C126" s="5">
-        <v>2</v>
-      </c>
-      <c r="D126" s="5">
+      <c r="B126" s="4">
+        <v>9</v>
+      </c>
+      <c r="C126" s="4">
+        <v>2</v>
+      </c>
+      <c r="D126" s="4">
         <v>6</v>
       </c>
-      <c r="E126" s="5" t="s">
+      <c r="E126" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="F126" s="6">
+      <c r="F126" s="5">
         <v>46261</v>
       </c>
-      <c r="G126" s="5" t="s">
+      <c r="G126" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="127" ht="13.5" customHeight="1">
-      <c r="A127" s="4">
+      <c r="A127" s="3">
         <v>1921</v>
       </c>
-      <c r="B127" s="5">
-        <v>9</v>
-      </c>
-      <c r="C127" s="5">
-        <v>2</v>
-      </c>
-      <c r="D127" s="5">
+      <c r="B127" s="4">
+        <v>9</v>
+      </c>
+      <c r="C127" s="4">
+        <v>2</v>
+      </c>
+      <c r="D127" s="4">
         <v>6</v>
       </c>
-      <c r="E127" s="5" t="s">
+      <c r="E127" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="F127" s="6">
+      <c r="F127" s="5">
         <v>46261</v>
       </c>
-      <c r="G127" s="5" t="s">
+      <c r="G127" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="128" ht="13.5" customHeight="1">
-      <c r="A128" s="4">
+      <c r="A128" s="3">
         <v>2010</v>
       </c>
-      <c r="B128" s="5">
-        <v>9</v>
-      </c>
-      <c r="C128" s="5">
-        <v>2</v>
-      </c>
-      <c r="D128" s="5">
+      <c r="B128" s="4">
+        <v>9</v>
+      </c>
+      <c r="C128" s="4">
+        <v>2</v>
+      </c>
+      <c r="D128" s="4">
         <v>6</v>
       </c>
-      <c r="E128" s="5" t="s">
+      <c r="E128" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="F128" s="6">
+      <c r="F128" s="5">
         <v>46275</v>
       </c>
-      <c r="G128" s="5" t="s">
+      <c r="G128" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="129" ht="13.5" customHeight="1">
-      <c r="A129" s="4">
+      <c r="A129" s="3">
         <v>1923</v>
       </c>
-      <c r="B129" s="5">
-        <v>9</v>
-      </c>
-      <c r="C129" s="5">
-        <v>1</v>
-      </c>
-      <c r="D129" s="5">
+      <c r="B129" s="4">
+        <v>9</v>
+      </c>
+      <c r="C129" s="4">
+        <v>1</v>
+      </c>
+      <c r="D129" s="4">
         <v>5</v>
       </c>
-      <c r="E129" s="5" t="s">
+      <c r="E129" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="F129" s="6">
+      <c r="F129" s="5">
         <v>46262</v>
       </c>
-      <c r="G129" s="5" t="s">
+      <c r="G129" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="130" ht="13.5" customHeight="1">
-      <c r="A130" s="4">
+      <c r="A130" s="3">
         <v>1924</v>
       </c>
-      <c r="B130" s="5">
-        <v>9</v>
-      </c>
-      <c r="C130" s="5">
-        <v>1</v>
-      </c>
-      <c r="D130" s="5">
+      <c r="B130" s="4">
+        <v>9</v>
+      </c>
+      <c r="C130" s="4">
+        <v>1</v>
+      </c>
+      <c r="D130" s="4">
         <v>5</v>
       </c>
-      <c r="E130" s="5" t="s">
+      <c r="E130" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="F130" s="6">
+      <c r="F130" s="5">
         <v>46262</v>
       </c>
-      <c r="G130" s="5" t="s">
+      <c r="G130" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="131" ht="13.5" customHeight="1">
-      <c r="A131" s="4">
+      <c r="A131" s="3">
         <v>1925</v>
       </c>
-      <c r="B131" s="5">
-        <v>9</v>
-      </c>
-      <c r="C131" s="5">
-        <v>1</v>
-      </c>
-      <c r="D131" s="5">
+      <c r="B131" s="4">
+        <v>9</v>
+      </c>
+      <c r="C131" s="4">
+        <v>1</v>
+      </c>
+      <c r="D131" s="4">
         <v>5</v>
       </c>
-      <c r="E131" s="5" t="s">
+      <c r="E131" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="F131" s="6">
+      <c r="F131" s="5">
         <v>46262</v>
       </c>
-      <c r="G131" s="5" t="s">
+      <c r="G131" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="132" ht="13.5" customHeight="1">
-      <c r="A132" s="4">
+      <c r="A132" s="3">
         <v>1926</v>
       </c>
-      <c r="B132" s="5">
-        <v>9</v>
-      </c>
-      <c r="C132" s="5">
-        <v>1</v>
-      </c>
-      <c r="D132" s="5">
+      <c r="B132" s="4">
+        <v>9</v>
+      </c>
+      <c r="C132" s="4">
+        <v>1</v>
+      </c>
+      <c r="D132" s="4">
         <v>5</v>
       </c>
-      <c r="E132" s="5" t="s">
+      <c r="E132" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="F132" s="6">
+      <c r="F132" s="5">
         <v>46262</v>
       </c>
-      <c r="G132" s="5" t="s">
+      <c r="G132" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="133" ht="13.5" customHeight="1">
-      <c r="A133" s="4">
+      <c r="A133" s="3">
         <v>1927</v>
       </c>
-      <c r="B133" s="5">
-        <v>9</v>
-      </c>
-      <c r="C133" s="5">
-        <v>1</v>
-      </c>
-      <c r="D133" s="5">
+      <c r="B133" s="4">
+        <v>9</v>
+      </c>
+      <c r="C133" s="4">
+        <v>1</v>
+      </c>
+      <c r="D133" s="4">
         <v>5</v>
       </c>
-      <c r="E133" s="5" t="s">
+      <c r="E133" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="F133" s="6">
+      <c r="F133" s="5">
         <v>46262</v>
       </c>
-      <c r="G133" s="5" t="s">
+      <c r="G133" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="134" ht="13.5" customHeight="1">
-      <c r="A134" s="4">
+      <c r="A134" s="3">
         <v>1928</v>
       </c>
-      <c r="B134" s="5">
-        <v>9</v>
-      </c>
-      <c r="C134" s="5">
-        <v>1</v>
-      </c>
-      <c r="D134" s="5">
+      <c r="B134" s="4">
+        <v>9</v>
+      </c>
+      <c r="C134" s="4">
+        <v>1</v>
+      </c>
+      <c r="D134" s="4">
         <v>4</v>
       </c>
-      <c r="E134" s="5" t="s">
+      <c r="E134" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="F134" s="6">
+      <c r="F134" s="5">
         <v>46274</v>
       </c>
-      <c r="G134" s="5" t="s">
+      <c r="G134" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="135" ht="13.5" customHeight="1">
-      <c r="A135" s="4">
+      <c r="A135" s="3">
         <v>1929</v>
       </c>
-      <c r="B135" s="5">
-        <v>9</v>
-      </c>
-      <c r="C135" s="5">
-        <v>1</v>
-      </c>
-      <c r="D135" s="5">
+      <c r="B135" s="4">
+        <v>9</v>
+      </c>
+      <c r="C135" s="4">
+        <v>1</v>
+      </c>
+      <c r="D135" s="4">
         <v>4</v>
       </c>
-      <c r="E135" s="5" t="s">
+      <c r="E135" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="F135" s="6">
+      <c r="F135" s="5">
         <v>46262</v>
       </c>
-      <c r="G135" s="5" t="s">
+      <c r="G135" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="136" ht="13.5" customHeight="1">
-      <c r="A136" s="4">
+      <c r="A136" s="3">
         <v>1930</v>
       </c>
-      <c r="B136" s="5">
-        <v>9</v>
-      </c>
-      <c r="C136" s="5">
-        <v>1</v>
-      </c>
-      <c r="D136" s="5">
+      <c r="B136" s="4">
+        <v>9</v>
+      </c>
+      <c r="C136" s="4">
+        <v>1</v>
+      </c>
+      <c r="D136" s="4">
         <v>5</v>
       </c>
-      <c r="E136" s="5" t="s">
+      <c r="E136" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="F136" s="6">
+      <c r="F136" s="5">
         <v>46262</v>
       </c>
-      <c r="G136" s="5" t="s">
+      <c r="G136" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="137" ht="13.5" customHeight="1">
-      <c r="A137" s="4">
+      <c r="A137" s="3">
         <v>1931</v>
       </c>
-      <c r="B137" s="5">
-        <v>9</v>
-      </c>
-      <c r="C137" s="5">
-        <v>2</v>
-      </c>
-      <c r="D137" s="5">
+      <c r="B137" s="4">
+        <v>9</v>
+      </c>
+      <c r="C137" s="4">
+        <v>2</v>
+      </c>
+      <c r="D137" s="4">
         <v>6</v>
       </c>
-      <c r="E137" s="5" t="s">
+      <c r="E137" s="4" t="s">
         <v>142</v>
       </c>
-      <c r="F137" s="6">
+      <c r="F137" s="5">
         <v>46262</v>
       </c>
-      <c r="G137" s="5" t="s">
+      <c r="G137" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="138" ht="13.5" customHeight="1">
-      <c r="A138" s="4">
+      <c r="A138" s="3">
         <v>1932</v>
       </c>
-      <c r="B138" s="5">
-        <v>9</v>
-      </c>
-      <c r="C138" s="5">
-        <v>1</v>
-      </c>
-      <c r="D138" s="5">
+      <c r="B138" s="4">
+        <v>9</v>
+      </c>
+      <c r="C138" s="4">
+        <v>1</v>
+      </c>
+      <c r="D138" s="4">
         <v>3</v>
       </c>
-      <c r="E138" s="5" t="s">
+      <c r="E138" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="F138" s="6">
+      <c r="F138" s="5">
         <v>46263</v>
       </c>
-      <c r="G138" s="5" t="s">
+      <c r="G138" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="139" ht="13.5" customHeight="1">
-      <c r="A139" s="4">
+      <c r="A139" s="3">
         <v>1933</v>
       </c>
-      <c r="B139" s="5">
-        <v>9</v>
-      </c>
-      <c r="C139" s="5">
+      <c r="B139" s="4">
+        <v>9</v>
+      </c>
+      <c r="C139" s="4">
         <v>3</v>
       </c>
-      <c r="D139" s="5">
+      <c r="D139" s="4">
         <v>12</v>
       </c>
-      <c r="E139" s="5" t="s">
+      <c r="E139" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="F139" s="6">
+      <c r="F139" s="5">
         <v>46265</v>
       </c>
-      <c r="G139" s="5" t="s">
+      <c r="G139" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="140" ht="13.5" customHeight="1">
-      <c r="A140" s="4">
+      <c r="A140" s="3">
         <v>1934</v>
       </c>
-      <c r="B140" s="5">
-        <v>9</v>
-      </c>
-      <c r="C140" s="5">
-        <v>1</v>
-      </c>
-      <c r="D140" s="5">
+      <c r="B140" s="4">
+        <v>9</v>
+      </c>
+      <c r="C140" s="4">
+        <v>1</v>
+      </c>
+      <c r="D140" s="4">
         <v>5</v>
       </c>
-      <c r="E140" s="5" t="s">
+      <c r="E140" s="4" t="s">
         <v>145</v>
       </c>
-      <c r="F140" s="6">
+      <c r="F140" s="5">
         <v>46265</v>
       </c>
-      <c r="G140" s="5" t="s">
+      <c r="G140" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="141" ht="13.5" customHeight="1">
-      <c r="A141" s="4">
+      <c r="A141" s="3">
         <v>1935</v>
       </c>
-      <c r="B141" s="5">
-        <v>9</v>
-      </c>
-      <c r="C141" s="5">
-        <v>2</v>
-      </c>
-      <c r="D141" s="5">
-        <v>9</v>
-      </c>
-      <c r="E141" s="5" t="s">
+      <c r="B141" s="4">
+        <v>9</v>
+      </c>
+      <c r="C141" s="4">
+        <v>2</v>
+      </c>
+      <c r="D141" s="4">
+        <v>9</v>
+      </c>
+      <c r="E141" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="F141" s="6">
+      <c r="F141" s="5">
         <v>46265</v>
       </c>
-      <c r="G141" s="5" t="s">
+      <c r="G141" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="142" ht="13.5" customHeight="1">
-      <c r="A142" s="4">
+      <c r="A142" s="3">
         <v>1936</v>
       </c>
-      <c r="B142" s="5">
-        <v>9</v>
-      </c>
-      <c r="C142" s="5">
+      <c r="B142" s="4">
+        <v>9</v>
+      </c>
+      <c r="C142" s="4">
         <v>3</v>
       </c>
-      <c r="D142" s="5">
+      <c r="D142" s="4">
         <v>11</v>
       </c>
-      <c r="E142" s="5" t="s">
+      <c r="E142" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="F142" s="6">
+      <c r="F142" s="5">
         <v>46265</v>
       </c>
-      <c r="G142" s="5" t="s">
+      <c r="G142" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="143" ht="13.5" customHeight="1">
-      <c r="A143" s="4">
+      <c r="A143" s="3">
         <v>1937</v>
       </c>
-      <c r="B143" s="5">
-        <v>9</v>
-      </c>
-      <c r="C143" s="5">
-        <v>1</v>
-      </c>
-      <c r="D143" s="5">
+      <c r="B143" s="4">
+        <v>9</v>
+      </c>
+      <c r="C143" s="4">
+        <v>1</v>
+      </c>
+      <c r="D143" s="4">
         <v>5</v>
       </c>
-      <c r="E143" s="5" t="s">
+      <c r="E143" s="4" t="s">
         <v>148</v>
       </c>
-      <c r="F143" s="6">
+      <c r="F143" s="5">
         <v>46265</v>
       </c>
-      <c r="G143" s="5" t="s">
+      <c r="G143" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="144" ht="13.5" customHeight="1">
-      <c r="A144" s="4">
+      <c r="A144" s="3">
         <v>1938</v>
       </c>
-      <c r="B144" s="5">
-        <v>9</v>
-      </c>
-      <c r="C144" s="5">
-        <v>1</v>
-      </c>
-      <c r="D144" s="5">
+      <c r="B144" s="4">
+        <v>9</v>
+      </c>
+      <c r="C144" s="4">
+        <v>1</v>
+      </c>
+      <c r="D144" s="4">
         <v>5</v>
       </c>
-      <c r="E144" s="5" t="s">
+      <c r="E144" s="4" t="s">
         <v>149</v>
       </c>
-      <c r="F144" s="6">
+      <c r="F144" s="5">
         <v>46266</v>
       </c>
-      <c r="G144" s="5" t="s">
+      <c r="G144" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="145" ht="13.5" customHeight="1">
-      <c r="A145" s="4">
+      <c r="A145" s="3">
         <v>1939</v>
       </c>
-      <c r="B145" s="5">
-        <v>9</v>
-      </c>
-      <c r="C145" s="5">
-        <v>2</v>
-      </c>
-      <c r="D145" s="5">
+      <c r="B145" s="4">
+        <v>9</v>
+      </c>
+      <c r="C145" s="4">
+        <v>2</v>
+      </c>
+      <c r="D145" s="4">
         <v>6</v>
       </c>
-      <c r="E145" s="5" t="s">
+      <c r="E145" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="F145" s="6">
+      <c r="F145" s="5">
         <v>46266</v>
       </c>
-      <c r="G145" s="5" t="s">
+      <c r="G145" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="146" ht="13.5" customHeight="1">
-      <c r="A146" s="4">
+      <c r="A146" s="3">
         <v>1940</v>
       </c>
-      <c r="B146" s="5">
-        <v>9</v>
-      </c>
-      <c r="C146" s="5">
-        <v>1</v>
-      </c>
-      <c r="D146" s="5">
+      <c r="B146" s="4">
+        <v>9</v>
+      </c>
+      <c r="C146" s="4">
+        <v>1</v>
+      </c>
+      <c r="D146" s="4">
         <v>4</v>
       </c>
-      <c r="E146" s="5" t="s">
+      <c r="E146" s="4" t="s">
         <v>151</v>
       </c>
-      <c r="F146" s="6">
+      <c r="F146" s="5">
         <v>46267</v>
       </c>
-      <c r="G146" s="5" t="s">
+      <c r="G146" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="147" ht="13.5" customHeight="1">
-      <c r="A147" s="4">
+      <c r="A147" s="3">
         <v>1941</v>
       </c>
-      <c r="B147" s="5">
-        <v>9</v>
-      </c>
-      <c r="C147" s="5">
-        <v>2</v>
-      </c>
-      <c r="D147" s="5">
+      <c r="B147" s="4">
+        <v>9</v>
+      </c>
+      <c r="C147" s="4">
+        <v>2</v>
+      </c>
+      <c r="D147" s="4">
         <v>6</v>
       </c>
-      <c r="E147" s="5" t="s">
+      <c r="E147" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="F147" s="6">
+      <c r="F147" s="5">
         <v>46267</v>
       </c>
-      <c r="G147" s="5" t="s">
+      <c r="G147" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="148" ht="13.5" customHeight="1">
-      <c r="A148" s="4">
+      <c r="A148" s="3">
         <v>1942</v>
       </c>
-      <c r="B148" s="5">
-        <v>9</v>
-      </c>
-      <c r="C148" s="5">
-        <v>1</v>
-      </c>
-      <c r="D148" s="5">
+      <c r="B148" s="4">
+        <v>9</v>
+      </c>
+      <c r="C148" s="4">
+        <v>1</v>
+      </c>
+      <c r="D148" s="4">
         <v>3</v>
       </c>
-      <c r="E148" s="5" t="s">
+      <c r="E148" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="F148" s="6">
+      <c r="F148" s="5">
         <v>46267</v>
       </c>
-      <c r="G148" s="5" t="s">
+      <c r="G148" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="149" ht="13.5" customHeight="1">
-      <c r="A149" s="4">
+      <c r="A149" s="3">
         <v>1943</v>
       </c>
-      <c r="B149" s="5">
-        <v>9</v>
-      </c>
-      <c r="C149" s="5">
-        <v>1</v>
-      </c>
-      <c r="D149" s="5">
+      <c r="B149" s="4">
+        <v>9</v>
+      </c>
+      <c r="C149" s="4">
+        <v>1</v>
+      </c>
+      <c r="D149" s="4">
         <v>3</v>
       </c>
-      <c r="E149" s="5" t="s">
+      <c r="E149" s="4" t="s">
         <v>154</v>
       </c>
-      <c r="F149" s="6">
+      <c r="F149" s="5">
         <v>46267</v>
       </c>
-      <c r="G149" s="5" t="s">
+      <c r="G149" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="150" ht="13.5" customHeight="1">
-      <c r="A150" s="4">
+      <c r="A150" s="3">
         <v>1944</v>
       </c>
-      <c r="B150" s="5">
-        <v>9</v>
-      </c>
-      <c r="C150" s="5">
-        <v>1</v>
-      </c>
-      <c r="D150" s="5">
+      <c r="B150" s="4">
+        <v>9</v>
+      </c>
+      <c r="C150" s="4">
+        <v>1</v>
+      </c>
+      <c r="D150" s="4">
         <v>3</v>
       </c>
-      <c r="E150" s="5" t="s">
+      <c r="E150" s="4" t="s">
         <v>155</v>
       </c>
-      <c r="F150" s="6">
+      <c r="F150" s="5">
         <v>46267</v>
       </c>
-      <c r="G150" s="5" t="s">
+      <c r="G150" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="151" ht="13.5" customHeight="1">
-      <c r="A151" s="4">
+      <c r="A151" s="3">
         <v>1945</v>
       </c>
-      <c r="B151" s="5">
-        <v>9</v>
-      </c>
-      <c r="C151" s="5">
-        <v>2</v>
-      </c>
-      <c r="D151" s="5">
-        <v>9</v>
-      </c>
-      <c r="E151" s="5" t="s">
+      <c r="B151" s="4">
+        <v>9</v>
+      </c>
+      <c r="C151" s="4">
+        <v>2</v>
+      </c>
+      <c r="D151" s="4">
+        <v>9</v>
+      </c>
+      <c r="E151" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="F151" s="6">
+      <c r="F151" s="5">
         <v>46273</v>
       </c>
-      <c r="G151" s="5" t="s">
+      <c r="G151" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="152" ht="13.5" customHeight="1">
-      <c r="A152" s="4">
+      <c r="A152" s="3">
         <v>1946</v>
       </c>
-      <c r="B152" s="5">
-        <v>9</v>
-      </c>
-      <c r="C152" s="5">
-        <v>2</v>
-      </c>
-      <c r="D152" s="5">
+      <c r="B152" s="4">
+        <v>9</v>
+      </c>
+      <c r="C152" s="4">
+        <v>2</v>
+      </c>
+      <c r="D152" s="4">
         <v>7</v>
       </c>
-      <c r="E152" s="5" t="s">
+      <c r="E152" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="F152" s="6">
+      <c r="F152" s="5">
         <v>46267</v>
       </c>
-      <c r="G152" s="5" t="s">
+      <c r="G152" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="153" ht="13.5" customHeight="1">
-      <c r="A153" s="4">
+      <c r="A153" s="3">
         <v>1947</v>
       </c>
-      <c r="B153" s="5">
-        <v>9</v>
-      </c>
-      <c r="C153" s="5">
-        <v>1</v>
-      </c>
-      <c r="D153" s="5">
+      <c r="B153" s="4">
+        <v>9</v>
+      </c>
+      <c r="C153" s="4">
+        <v>1</v>
+      </c>
+      <c r="D153" s="4">
         <v>3</v>
       </c>
-      <c r="E153" s="5" t="s">
+      <c r="E153" s="4" t="s">
         <v>158</v>
       </c>
-      <c r="F153" s="6">
+      <c r="F153" s="5">
         <v>46267</v>
       </c>
-      <c r="G153" s="5" t="s">
+      <c r="G153" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="154" ht="13.5" customHeight="1">
-      <c r="A154" s="4">
+      <c r="A154" s="3">
         <v>1948</v>
       </c>
-      <c r="B154" s="5">
-        <v>9</v>
-      </c>
-      <c r="C154" s="5">
-        <v>1</v>
-      </c>
-      <c r="D154" s="5">
+      <c r="B154" s="4">
+        <v>9</v>
+      </c>
+      <c r="C154" s="4">
+        <v>1</v>
+      </c>
+      <c r="D154" s="4">
         <v>3</v>
       </c>
-      <c r="E154" s="5" t="s">
+      <c r="E154" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="F154" s="6">
+      <c r="F154" s="5">
         <v>46267</v>
       </c>
-      <c r="G154" s="5" t="s">
+      <c r="G154" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="155" ht="13.5" customHeight="1">
-      <c r="A155" s="4">
+      <c r="A155" s="3">
         <v>1949</v>
       </c>
-      <c r="B155" s="5">
-        <v>9</v>
-      </c>
-      <c r="C155" s="5">
-        <v>2</v>
-      </c>
-      <c r="D155" s="5">
+      <c r="B155" s="4">
+        <v>9</v>
+      </c>
+      <c r="C155" s="4">
+        <v>2</v>
+      </c>
+      <c r="D155" s="4">
         <v>6</v>
       </c>
-      <c r="E155" s="5" t="s">
+      <c r="E155" s="4" t="s">
         <v>160</v>
       </c>
-      <c r="F155" s="6">
+      <c r="F155" s="5">
         <v>46267</v>
       </c>
-      <c r="G155" s="5" t="s">
+      <c r="G155" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="156" ht="13.5" customHeight="1">
-      <c r="A156" s="4">
+      <c r="A156" s="3">
         <v>1950</v>
       </c>
-      <c r="B156" s="5">
-        <v>9</v>
-      </c>
-      <c r="C156" s="5">
-        <v>1</v>
-      </c>
-      <c r="D156" s="5">
-        <v>2</v>
-      </c>
-      <c r="E156" s="5" t="s">
+      <c r="B156" s="4">
+        <v>9</v>
+      </c>
+      <c r="C156" s="4">
+        <v>1</v>
+      </c>
+      <c r="D156" s="4">
+        <v>2</v>
+      </c>
+      <c r="E156" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="F156" s="6">
+      <c r="F156" s="5">
         <v>46267</v>
       </c>
-      <c r="G156" s="5" t="s">
+      <c r="G156" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="157" ht="13.5" customHeight="1">
-      <c r="A157" s="4">
+      <c r="A157" s="3">
         <v>1951</v>
       </c>
-      <c r="B157" s="5">
-        <v>9</v>
-      </c>
-      <c r="C157" s="5">
-        <v>1</v>
-      </c>
-      <c r="D157" s="5">
+      <c r="B157" s="4">
+        <v>9</v>
+      </c>
+      <c r="C157" s="4">
+        <v>1</v>
+      </c>
+      <c r="D157" s="4">
         <v>4</v>
       </c>
-      <c r="E157" s="5" t="s">
+      <c r="E157" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="F157" s="6">
+      <c r="F157" s="5">
         <v>46268</v>
       </c>
-      <c r="G157" s="5" t="s">
+      <c r="G157" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="158" ht="13.5" customHeight="1">
-      <c r="A158" s="4">
+      <c r="A158" s="3">
         <v>1952</v>
       </c>
-      <c r="B158" s="5">
-        <v>9</v>
-      </c>
-      <c r="C158" s="5">
-        <v>2</v>
-      </c>
-      <c r="D158" s="5">
-        <v>9</v>
-      </c>
-      <c r="E158" s="5" t="s">
+      <c r="B158" s="4">
+        <v>9</v>
+      </c>
+      <c r="C158" s="4">
+        <v>2</v>
+      </c>
+      <c r="D158" s="4">
+        <v>9</v>
+      </c>
+      <c r="E158" s="4" t="s">
         <v>163</v>
       </c>
-      <c r="F158" s="6">
+      <c r="F158" s="5">
         <v>46269</v>
       </c>
-      <c r="G158" s="5" t="s">
+      <c r="G158" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="159" ht="13.5" customHeight="1">
-      <c r="A159" s="4">
+      <c r="A159" s="3">
         <v>1953</v>
       </c>
-      <c r="B159" s="5">
-        <v>9</v>
-      </c>
-      <c r="C159" s="5">
+      <c r="B159" s="4">
+        <v>9</v>
+      </c>
+      <c r="C159" s="4">
         <v>3</v>
       </c>
-      <c r="D159" s="5">
+      <c r="D159" s="4">
         <v>11</v>
       </c>
-      <c r="E159" s="5" t="s">
+      <c r="E159" s="4" t="s">
         <v>164</v>
       </c>
-      <c r="F159" s="6">
+      <c r="F159" s="5">
         <v>46269</v>
       </c>
-      <c r="G159" s="5" t="s">
+      <c r="G159" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="160" ht="13.5" customHeight="1">
-      <c r="A160" s="4">
+      <c r="A160" s="3">
         <v>1954</v>
       </c>
-      <c r="B160" s="5">
-        <v>9</v>
-      </c>
-      <c r="C160" s="5">
-        <v>2</v>
-      </c>
-      <c r="D160" s="5">
-        <v>8</v>
-      </c>
-      <c r="E160" s="5" t="s">
+      <c r="B160" s="4">
+        <v>9</v>
+      </c>
+      <c r="C160" s="4">
+        <v>2</v>
+      </c>
+      <c r="D160" s="4">
+        <v>8</v>
+      </c>
+      <c r="E160" s="4" t="s">
         <v>165</v>
       </c>
-      <c r="F160" s="6">
+      <c r="F160" s="5">
         <v>46269</v>
       </c>
-      <c r="G160" s="5" t="s">
+      <c r="G160" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="161" ht="13.5" customHeight="1">
-      <c r="A161" s="4">
+      <c r="A161" s="3">
         <v>1955</v>
       </c>
-      <c r="B161" s="5">
-        <v>9</v>
-      </c>
-      <c r="C161" s="5">
+      <c r="B161" s="4">
+        <v>9</v>
+      </c>
+      <c r="C161" s="4">
         <v>3</v>
       </c>
-      <c r="D161" s="5">
+      <c r="D161" s="4">
         <v>11</v>
       </c>
-      <c r="E161" s="5" t="s">
+      <c r="E161" s="4" t="s">
         <v>166</v>
       </c>
-      <c r="F161" s="6">
+      <c r="F161" s="5">
         <v>46269</v>
       </c>
-      <c r="G161" s="5" t="s">
+      <c r="G161" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="162" ht="13.5" customHeight="1">
-      <c r="A162" s="4">
+      <c r="A162" s="3">
         <v>1956</v>
       </c>
-      <c r="B162" s="5">
-        <v>9</v>
-      </c>
-      <c r="C162" s="5">
-        <v>1</v>
-      </c>
-      <c r="D162" s="5">
+      <c r="B162" s="4">
+        <v>9</v>
+      </c>
+      <c r="C162" s="4">
+        <v>1</v>
+      </c>
+      <c r="D162" s="4">
         <v>3</v>
       </c>
-      <c r="E162" s="5" t="s">
+      <c r="E162" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="F162" s="6">
+      <c r="F162" s="5">
         <v>46269</v>
       </c>
-      <c r="G162" s="5" t="s">
+      <c r="G162" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="163" ht="13.5" customHeight="1">
-      <c r="A163" s="4">
+      <c r="A163" s="3">
         <v>1957</v>
       </c>
-      <c r="B163" s="5">
-        <v>9</v>
-      </c>
-      <c r="C163" s="5">
-        <v>2</v>
-      </c>
-      <c r="D163" s="5">
-        <v>8</v>
-      </c>
-      <c r="E163" s="5" t="s">
+      <c r="B163" s="4">
+        <v>9</v>
+      </c>
+      <c r="C163" s="4">
+        <v>2</v>
+      </c>
+      <c r="D163" s="4">
+        <v>8</v>
+      </c>
+      <c r="E163" s="4" t="s">
         <v>168</v>
       </c>
-      <c r="F163" s="6">
+      <c r="F163" s="5">
         <v>46269</v>
       </c>
-      <c r="G163" s="5" t="s">
+      <c r="G163" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="164" ht="13.5" customHeight="1">
-      <c r="A164" s="4">
+      <c r="A164" s="3">
         <v>1958</v>
       </c>
-      <c r="B164" s="5">
-        <v>9</v>
-      </c>
-      <c r="C164" s="5">
-        <v>2</v>
-      </c>
-      <c r="D164" s="5">
+      <c r="B164" s="4">
+        <v>9</v>
+      </c>
+      <c r="C164" s="4">
+        <v>2</v>
+      </c>
+      <c r="D164" s="4">
         <v>7</v>
       </c>
-      <c r="E164" s="5" t="s">
+      <c r="E164" s="4" t="s">
         <v>168</v>
       </c>
-      <c r="F164" s="6">
+      <c r="F164" s="5">
         <v>46269</v>
       </c>
-      <c r="G164" s="5" t="s">
+      <c r="G164" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="165" ht="13.5" customHeight="1">
-      <c r="A165" s="4">
+      <c r="A165" s="3">
         <v>1959</v>
       </c>
-      <c r="B165" s="5">
-        <v>9</v>
-      </c>
-      <c r="C165" s="5">
-        <v>1</v>
-      </c>
-      <c r="D165" s="5">
+      <c r="B165" s="4">
+        <v>9</v>
+      </c>
+      <c r="C165" s="4">
+        <v>1</v>
+      </c>
+      <c r="D165" s="4">
         <v>3</v>
       </c>
-      <c r="E165" s="5" t="s">
+      <c r="E165" s="4" t="s">
         <v>169</v>
       </c>
-      <c r="F165" s="6">
+      <c r="F165" s="5">
         <v>46269</v>
       </c>
-      <c r="G165" s="5" t="s">
+      <c r="G165" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="166" ht="13.5" customHeight="1">
-      <c r="A166" s="4">
+      <c r="A166" s="3">
         <v>1960</v>
       </c>
-      <c r="B166" s="5">
-        <v>9</v>
-      </c>
-      <c r="C166" s="5">
-        <v>1</v>
-      </c>
-      <c r="D166" s="5">
-        <v>2</v>
-      </c>
-      <c r="E166" s="5" t="s">
+      <c r="B166" s="4">
+        <v>9</v>
+      </c>
+      <c r="C166" s="4">
+        <v>1</v>
+      </c>
+      <c r="D166" s="4">
+        <v>2</v>
+      </c>
+      <c r="E166" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="F166" s="6">
+      <c r="F166" s="5">
         <v>46269</v>
       </c>
-      <c r="G166" s="5" t="s">
+      <c r="G166" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="167" ht="13.5" customHeight="1">
-      <c r="A167" s="4">
+      <c r="A167" s="3">
         <v>1961</v>
       </c>
-      <c r="B167" s="5">
-        <v>9</v>
-      </c>
-      <c r="C167" s="5">
-        <v>2</v>
-      </c>
-      <c r="D167" s="5">
-        <v>9</v>
-      </c>
-      <c r="E167" s="5" t="s">
+      <c r="B167" s="4">
+        <v>9</v>
+      </c>
+      <c r="C167" s="4">
+        <v>2</v>
+      </c>
+      <c r="D167" s="4">
+        <v>9</v>
+      </c>
+      <c r="E167" s="4" t="s">
         <v>171</v>
       </c>
-      <c r="F167" s="6">
+      <c r="F167" s="5">
         <v>46269</v>
       </c>
-      <c r="G167" s="5" t="s">
+      <c r="G167" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="168" ht="13.5" customHeight="1">
-      <c r="A168" s="4">
+      <c r="A168" s="3">
         <v>1962</v>
       </c>
-      <c r="B168" s="5">
-        <v>9</v>
-      </c>
-      <c r="C168" s="5">
-        <v>1</v>
-      </c>
-      <c r="D168" s="5">
-        <v>2</v>
-      </c>
-      <c r="E168" s="5" t="s">
+      <c r="B168" s="4">
+        <v>9</v>
+      </c>
+      <c r="C168" s="4">
+        <v>1</v>
+      </c>
+      <c r="D168" s="4">
+        <v>2</v>
+      </c>
+      <c r="E168" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="F168" s="6">
+      <c r="F168" s="5">
         <v>46269</v>
       </c>
-      <c r="G168" s="5" t="s">
+      <c r="G168" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="169" ht="13.5" customHeight="1">
-      <c r="A169" s="4">
+      <c r="A169" s="3">
         <v>1963</v>
       </c>
-      <c r="B169" s="5">
-        <v>9</v>
-      </c>
-      <c r="C169" s="5">
-        <v>1</v>
-      </c>
-      <c r="D169" s="5">
-        <v>2</v>
-      </c>
-      <c r="E169" s="5" t="s">
+      <c r="B169" s="4">
+        <v>9</v>
+      </c>
+      <c r="C169" s="4">
+        <v>1</v>
+      </c>
+      <c r="D169" s="4">
+        <v>2</v>
+      </c>
+      <c r="E169" s="4" t="s">
         <v>173</v>
       </c>
-      <c r="F169" s="6">
+      <c r="F169" s="5">
         <v>46269</v>
       </c>
-      <c r="G169" s="5" t="s">
+      <c r="G169" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="170" ht="13.5" customHeight="1">
-      <c r="A170" s="4">
+      <c r="A170" s="3">
         <v>1964</v>
       </c>
-      <c r="B170" s="5">
-        <v>9</v>
-      </c>
-      <c r="C170" s="5">
-        <v>2</v>
-      </c>
-      <c r="D170" s="5">
-        <v>9</v>
-      </c>
-      <c r="E170" s="5" t="s">
+      <c r="B170" s="4">
+        <v>9</v>
+      </c>
+      <c r="C170" s="4">
+        <v>2</v>
+      </c>
+      <c r="D170" s="4">
+        <v>9</v>
+      </c>
+      <c r="E170" s="4" t="s">
         <v>174</v>
       </c>
-      <c r="F170" s="6">
+      <c r="F170" s="5">
         <v>46274</v>
       </c>
-      <c r="G170" s="5" t="s">
+      <c r="G170" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="171" ht="13.5" customHeight="1">
-      <c r="A171" s="4">
+      <c r="A171" s="3">
         <v>1965</v>
       </c>
-      <c r="B171" s="5">
-        <v>9</v>
-      </c>
-      <c r="C171" s="5">
-        <v>2</v>
-      </c>
-      <c r="D171" s="5">
-        <v>9</v>
-      </c>
-      <c r="E171" s="5" t="s">
+      <c r="B171" s="4">
+        <v>9</v>
+      </c>
+      <c r="C171" s="4">
+        <v>2</v>
+      </c>
+      <c r="D171" s="4">
+        <v>9</v>
+      </c>
+      <c r="E171" s="4" t="s">
         <v>175</v>
       </c>
-      <c r="F171" s="6">
+      <c r="F171" s="5">
         <v>46270</v>
       </c>
-      <c r="G171" s="5" t="s">
+      <c r="G171" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="172" ht="13.5" customHeight="1">
-      <c r="A172" s="4">
+      <c r="A172" s="3">
         <v>1966</v>
       </c>
-      <c r="B172" s="5">
-        <v>9</v>
-      </c>
-      <c r="C172" s="5">
-        <v>1</v>
-      </c>
-      <c r="D172" s="5">
+      <c r="B172" s="4">
+        <v>9</v>
+      </c>
+      <c r="C172" s="4">
+        <v>1</v>
+      </c>
+      <c r="D172" s="4">
         <v>4</v>
       </c>
-      <c r="E172" s="5" t="s">
+      <c r="E172" s="4" t="s">
         <v>176</v>
       </c>
-      <c r="F172" s="6">
+      <c r="F172" s="5">
         <v>46270</v>
       </c>
-      <c r="G172" s="5" t="s">
+      <c r="G172" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="173" ht="13.5" customHeight="1">
-      <c r="A173" s="4">
+      <c r="A173" s="3">
         <v>1967</v>
       </c>
-      <c r="B173" s="5">
-        <v>9</v>
-      </c>
-      <c r="C173" s="5">
-        <v>1</v>
-      </c>
-      <c r="D173" s="5">
-        <v>2</v>
-      </c>
-      <c r="E173" s="5" t="s">
+      <c r="B173" s="4">
+        <v>9</v>
+      </c>
+      <c r="C173" s="4">
+        <v>1</v>
+      </c>
+      <c r="D173" s="4">
+        <v>2</v>
+      </c>
+      <c r="E173" s="4" t="s">
         <v>177</v>
       </c>
-      <c r="F173" s="6">
+      <c r="F173" s="5">
         <v>46270</v>
       </c>
-      <c r="G173" s="5" t="s">
+      <c r="G173" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="174" ht="13.5" customHeight="1">
-      <c r="A174" s="4">
+      <c r="A174" s="3">
         <v>1968</v>
       </c>
-      <c r="B174" s="5">
-        <v>9</v>
-      </c>
-      <c r="C174" s="5">
-        <v>1</v>
-      </c>
-      <c r="D174" s="5">
-        <v>1</v>
-      </c>
-      <c r="E174" s="5" t="s">
+      <c r="B174" s="4">
+        <v>9</v>
+      </c>
+      <c r="C174" s="4">
+        <v>1</v>
+      </c>
+      <c r="D174" s="4">
+        <v>1</v>
+      </c>
+      <c r="E174" s="4" t="s">
         <v>178</v>
       </c>
-      <c r="F174" s="6">
+      <c r="F174" s="5">
         <v>46270</v>
       </c>
-      <c r="G174" s="5" t="s">
+      <c r="G174" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="175" ht="13.5" customHeight="1">
-      <c r="A175" s="4">
+      <c r="A175" s="3">
         <v>1969</v>
       </c>
-      <c r="B175" s="5">
-        <v>9</v>
-      </c>
-      <c r="C175" s="5">
-        <v>1</v>
-      </c>
-      <c r="D175" s="5">
-        <v>2</v>
-      </c>
-      <c r="E175" s="5" t="s">
+      <c r="B175" s="4">
+        <v>9</v>
+      </c>
+      <c r="C175" s="4">
+        <v>1</v>
+      </c>
+      <c r="D175" s="4">
+        <v>2</v>
+      </c>
+      <c r="E175" s="4" t="s">
         <v>178</v>
       </c>
-      <c r="F175" s="6">
+      <c r="F175" s="5">
         <v>46270</v>
       </c>
-      <c r="G175" s="5" t="s">
+      <c r="G175" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="176" ht="13.5" customHeight="1">
-      <c r="A176" s="4">
+      <c r="A176" s="3">
         <v>1970</v>
       </c>
-      <c r="B176" s="5">
-        <v>9</v>
-      </c>
-      <c r="C176" s="5">
-        <v>1</v>
-      </c>
-      <c r="D176" s="5">
+      <c r="B176" s="4">
+        <v>9</v>
+      </c>
+      <c r="C176" s="4">
+        <v>1</v>
+      </c>
+      <c r="D176" s="4">
         <v>3</v>
       </c>
-      <c r="E176" s="5" t="s">
+      <c r="E176" s="4" t="s">
         <v>179</v>
       </c>
-      <c r="F176" s="6">
+      <c r="F176" s="5">
         <v>46272</v>
       </c>
-      <c r="G176" s="5" t="s">
+      <c r="G176" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="177" ht="13.5" customHeight="1">
-      <c r="A177" s="4">
+      <c r="A177" s="3">
         <v>1971</v>
       </c>
-      <c r="B177" s="5">
-        <v>9</v>
-      </c>
-      <c r="C177" s="5">
-        <v>2</v>
-      </c>
-      <c r="D177" s="5">
+      <c r="B177" s="4">
+        <v>9</v>
+      </c>
+      <c r="C177" s="4">
+        <v>2</v>
+      </c>
+      <c r="D177" s="4">
         <v>6</v>
       </c>
-      <c r="E177" s="5" t="s">
+      <c r="E177" s="4" t="s">
         <v>180</v>
       </c>
-      <c r="F177" s="6">
+      <c r="F177" s="5">
         <v>46273</v>
       </c>
-      <c r="G177" s="5" t="s">
+      <c r="G177" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="178" ht="13.5" customHeight="1">
-      <c r="A178" s="4">
+      <c r="A178" s="3">
         <v>1972</v>
       </c>
-      <c r="B178" s="5">
-        <v>9</v>
-      </c>
-      <c r="C178" s="5">
+      <c r="B178" s="4">
+        <v>9</v>
+      </c>
+      <c r="C178" s="4">
         <v>3</v>
       </c>
-      <c r="D178" s="5">
+      <c r="D178" s="4">
         <v>11</v>
       </c>
-      <c r="E178" s="5" t="s">
+      <c r="E178" s="4" t="s">
         <v>181</v>
       </c>
-      <c r="F178" s="6">
+      <c r="F178" s="5">
         <v>46273</v>
       </c>
-      <c r="G178" s="5" t="s">
+      <c r="G178" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="179" ht="13.5" customHeight="1">
-      <c r="A179" s="4">
+      <c r="A179" s="3">
         <v>1973</v>
       </c>
-      <c r="B179" s="5">
-        <v>9</v>
-      </c>
-      <c r="C179" s="5">
-        <v>1</v>
-      </c>
-      <c r="D179" s="5">
+      <c r="B179" s="4">
+        <v>9</v>
+      </c>
+      <c r="C179" s="4">
+        <v>1</v>
+      </c>
+      <c r="D179" s="4">
         <v>3</v>
       </c>
-      <c r="E179" s="5" t="s">
+      <c r="E179" s="4" t="s">
         <v>182</v>
       </c>
-      <c r="F179" s="6">
+      <c r="F179" s="5">
         <v>46274</v>
       </c>
-      <c r="G179" s="5" t="s">
+      <c r="G179" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="180" ht="13.5" customHeight="1">
-      <c r="A180" s="4">
+      <c r="A180" s="3">
         <v>1974</v>
       </c>
-      <c r="B180" s="5">
-        <v>9</v>
-      </c>
-      <c r="C180" s="5">
-        <v>1</v>
-      </c>
-      <c r="D180" s="5">
+      <c r="B180" s="4">
+        <v>9</v>
+      </c>
+      <c r="C180" s="4">
+        <v>1</v>
+      </c>
+      <c r="D180" s="4">
         <v>4</v>
       </c>
-      <c r="E180" s="5" t="s">
+      <c r="E180" s="4" t="s">
         <v>183</v>
       </c>
-      <c r="F180" s="6">
+      <c r="F180" s="5">
         <v>46273</v>
       </c>
-      <c r="G180" s="5" t="s">
+      <c r="G180" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="181" ht="13.5" customHeight="1">
-      <c r="A181" s="4">
+      <c r="A181" s="3">
         <v>1975</v>
       </c>
-      <c r="B181" s="5">
-        <v>9</v>
-      </c>
-      <c r="C181" s="5">
-        <v>1</v>
-      </c>
-      <c r="D181" s="5">
+      <c r="B181" s="4">
+        <v>9</v>
+      </c>
+      <c r="C181" s="4">
+        <v>1</v>
+      </c>
+      <c r="D181" s="4">
         <v>4</v>
       </c>
-      <c r="E181" s="5" t="s">
+      <c r="E181" s="4" t="s">
         <v>184</v>
       </c>
-      <c r="F181" s="6">
+      <c r="F181" s="5">
         <v>46273</v>
       </c>
-      <c r="G181" s="5" t="s">
+      <c r="G181" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="182" ht="13.5" customHeight="1">
-      <c r="A182" s="4">
+      <c r="A182" s="3">
         <v>1976</v>
       </c>
-      <c r="B182" s="5">
-        <v>9</v>
-      </c>
-      <c r="C182" s="5">
-        <v>1</v>
-      </c>
-      <c r="D182" s="5">
+      <c r="B182" s="4">
+        <v>9</v>
+      </c>
+      <c r="C182" s="4">
+        <v>1</v>
+      </c>
+      <c r="D182" s="4">
         <v>5</v>
       </c>
-      <c r="E182" s="5" t="s">
+      <c r="E182" s="4" t="s">
         <v>185</v>
       </c>
-      <c r="F182" s="6">
+      <c r="F182" s="5">
         <v>46273</v>
       </c>
-      <c r="G182" s="5" t="s">
+      <c r="G182" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="183" ht="13.5" customHeight="1">
-      <c r="A183" s="4">
+      <c r="A183" s="3">
         <v>1977</v>
       </c>
-      <c r="B183" s="5">
-        <v>9</v>
-      </c>
-      <c r="C183" s="5">
-        <v>1</v>
-      </c>
-      <c r="D183" s="5">
-        <v>2</v>
-      </c>
-      <c r="E183" s="5" t="s">
+      <c r="B183" s="4">
+        <v>9</v>
+      </c>
+      <c r="C183" s="4">
+        <v>1</v>
+      </c>
+      <c r="D183" s="4">
+        <v>2</v>
+      </c>
+      <c r="E183" s="4" t="s">
         <v>186</v>
       </c>
-      <c r="F183" s="6">
+      <c r="F183" s="5">
         <v>46273</v>
       </c>
-      <c r="G183" s="5" t="s">
+      <c r="G183" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="184" ht="13.5" customHeight="1">
-      <c r="A184" s="4">
+      <c r="A184" s="3">
         <v>1978</v>
       </c>
-      <c r="B184" s="5">
-        <v>9</v>
-      </c>
-      <c r="C184" s="5">
-        <v>1</v>
-      </c>
-      <c r="D184" s="5">
+      <c r="B184" s="4">
+        <v>9</v>
+      </c>
+      <c r="C184" s="4">
+        <v>1</v>
+      </c>
+      <c r="D184" s="4">
         <v>4</v>
       </c>
-      <c r="E184" s="5" t="s">
+      <c r="E184" s="4" t="s">
         <v>187</v>
       </c>
-      <c r="F184" s="6">
+      <c r="F184" s="5">
         <v>46274</v>
       </c>
-      <c r="G184" s="5" t="s">
+      <c r="G184" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="185" ht="13.5" customHeight="1">
-      <c r="A185" s="4">
+      <c r="A185" s="3">
         <v>1979</v>
       </c>
-      <c r="B185" s="5">
-        <v>9</v>
-      </c>
-      <c r="C185" s="5">
-        <v>2</v>
-      </c>
-      <c r="D185" s="5">
-        <v>9</v>
-      </c>
-      <c r="E185" s="5" t="s">
+      <c r="B185" s="4">
+        <v>9</v>
+      </c>
+      <c r="C185" s="4">
+        <v>2</v>
+      </c>
+      <c r="D185" s="4">
+        <v>9</v>
+      </c>
+      <c r="E185" s="4" t="s">
         <v>188</v>
       </c>
-      <c r="F185" s="6">
+      <c r="F185" s="5">
         <v>46274</v>
       </c>
-      <c r="G185" s="5" t="s">
+      <c r="G185" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="186" ht="13.5" customHeight="1">
-      <c r="A186" s="4">
+      <c r="A186" s="3">
         <v>1980</v>
       </c>
-      <c r="B186" s="5">
-        <v>9</v>
-      </c>
-      <c r="C186" s="5">
+      <c r="B186" s="4">
+        <v>9</v>
+      </c>
+      <c r="C186" s="4">
         <v>3</v>
       </c>
-      <c r="D186" s="5">
+      <c r="D186" s="4">
         <v>12</v>
       </c>
-      <c r="E186" s="5" t="s">
+      <c r="E186" s="4" t="s">
         <v>189</v>
       </c>
-      <c r="F186" s="6">
+      <c r="F186" s="5">
         <v>46274</v>
       </c>
-      <c r="G186" s="5" t="s">
+      <c r="G186" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="187" ht="13.5" customHeight="1">
-      <c r="A187" s="4">
+      <c r="A187" s="3">
         <v>1981</v>
       </c>
-      <c r="B187" s="5">
-        <v>9</v>
-      </c>
-      <c r="C187" s="5">
+      <c r="B187" s="4">
+        <v>9</v>
+      </c>
+      <c r="C187" s="4">
         <v>3</v>
       </c>
-      <c r="D187" s="5">
+      <c r="D187" s="4">
         <v>14</v>
       </c>
-      <c r="E187" s="5" t="s">
+      <c r="E187" s="4" t="s">
         <v>190</v>
       </c>
-      <c r="F187" s="6">
+      <c r="F187" s="5">
         <v>46274</v>
       </c>
-      <c r="G187" s="5" t="s">
+      <c r="G187" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="188" ht="13.5" customHeight="1">
-      <c r="A188" s="4">
+      <c r="A188" s="3">
         <v>1982</v>
       </c>
-      <c r="B188" s="5">
-        <v>9</v>
-      </c>
-      <c r="C188" s="5">
-        <v>2</v>
-      </c>
-      <c r="D188" s="5">
+      <c r="B188" s="4">
+        <v>9</v>
+      </c>
+      <c r="C188" s="4">
+        <v>2</v>
+      </c>
+      <c r="D188" s="4">
         <v>6</v>
       </c>
-      <c r="E188" s="5" t="s">
+      <c r="E188" s="4" t="s">
         <v>191</v>
       </c>
-      <c r="F188" s="6">
+      <c r="F188" s="5">
         <v>46274</v>
       </c>
-      <c r="G188" s="5" t="s">
+      <c r="G188" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="189" ht="13.5" customHeight="1">
-      <c r="A189" s="4">
+      <c r="A189" s="3">
         <v>1983</v>
       </c>
-      <c r="B189" s="5">
-        <v>9</v>
-      </c>
-      <c r="C189" s="5">
-        <v>2</v>
-      </c>
-      <c r="D189" s="5">
+      <c r="B189" s="4">
+        <v>9</v>
+      </c>
+      <c r="C189" s="4">
+        <v>2</v>
+      </c>
+      <c r="D189" s="4">
         <v>7</v>
       </c>
-      <c r="E189" s="5" t="s">
+      <c r="E189" s="4" t="s">
         <v>191</v>
       </c>
-      <c r="F189" s="6">
+      <c r="F189" s="5">
         <v>46275</v>
       </c>
-      <c r="G189" s="5" t="s">
+      <c r="G189" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="190" ht="13.5" customHeight="1">
-      <c r="A190" s="4">
+      <c r="A190" s="3">
         <v>1984</v>
       </c>
-      <c r="B190" s="5">
-        <v>9</v>
-      </c>
-      <c r="C190" s="5">
-        <v>1</v>
-      </c>
-      <c r="D190" s="5">
+      <c r="B190" s="4">
+        <v>9</v>
+      </c>
+      <c r="C190" s="4">
+        <v>1</v>
+      </c>
+      <c r="D190" s="4">
         <v>5</v>
       </c>
-      <c r="E190" s="5" t="s">
+      <c r="E190" s="4" t="s">
         <v>192</v>
       </c>
-      <c r="F190" s="6">
+      <c r="F190" s="5">
         <v>46274</v>
       </c>
-      <c r="G190" s="5" t="s">
+      <c r="G190" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="191" ht="13.5" customHeight="1">
-      <c r="A191" s="4">
+      <c r="A191" s="3">
         <v>1985</v>
       </c>
-      <c r="B191" s="5">
-        <v>9</v>
-      </c>
-      <c r="C191" s="5">
-        <v>2</v>
-      </c>
-      <c r="D191" s="5">
+      <c r="B191" s="4">
+        <v>9</v>
+      </c>
+      <c r="C191" s="4">
+        <v>2</v>
+      </c>
+      <c r="D191" s="4">
         <v>6</v>
       </c>
-      <c r="E191" s="5" t="s">
+      <c r="E191" s="4" t="s">
         <v>192</v>
       </c>
-      <c r="F191" s="6">
+      <c r="F191" s="5">
         <v>46274</v>
       </c>
-      <c r="G191" s="5" t="s">
+      <c r="G191" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="192" ht="13.5" customHeight="1">
-      <c r="A192" s="4">
+      <c r="A192" s="3">
         <v>1986</v>
       </c>
-      <c r="B192" s="5">
-        <v>9</v>
-      </c>
-      <c r="C192" s="5">
-        <v>1</v>
-      </c>
-      <c r="D192" s="5">
+      <c r="B192" s="4">
+        <v>9</v>
+      </c>
+      <c r="C192" s="4">
+        <v>1</v>
+      </c>
+      <c r="D192" s="4">
         <v>3</v>
       </c>
-      <c r="E192" s="5" t="s">
+      <c r="E192" s="4" t="s">
         <v>193</v>
       </c>
-      <c r="F192" s="6">
+      <c r="F192" s="5">
         <v>46274</v>
       </c>
-      <c r="G192" s="5" t="s">
+      <c r="G192" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="193" ht="13.5" customHeight="1">
-      <c r="A193" s="4">
+      <c r="A193" s="3">
         <v>1987</v>
       </c>
-      <c r="B193" s="5">
-        <v>9</v>
-      </c>
-      <c r="C193" s="5">
-        <v>1</v>
-      </c>
-      <c r="D193" s="5">
+      <c r="B193" s="4">
+        <v>9</v>
+      </c>
+      <c r="C193" s="4">
+        <v>1</v>
+      </c>
+      <c r="D193" s="4">
         <v>4</v>
       </c>
-      <c r="E193" s="5" t="s">
+      <c r="E193" s="4" t="s">
         <v>193</v>
       </c>
-      <c r="F193" s="6">
+      <c r="F193" s="5">
         <v>46274</v>
       </c>
-      <c r="G193" s="5" t="s">
+      <c r="G193" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="194" ht="13.5" customHeight="1">
-      <c r="A194" s="4">
+      <c r="A194" s="3">
         <v>1988</v>
       </c>
-      <c r="B194" s="5">
-        <v>9</v>
-      </c>
-      <c r="C194" s="5">
-        <v>1</v>
-      </c>
-      <c r="D194" s="5">
-        <v>2</v>
-      </c>
-      <c r="E194" s="5" t="s">
+      <c r="B194" s="4">
+        <v>9</v>
+      </c>
+      <c r="C194" s="4">
+        <v>1</v>
+      </c>
+      <c r="D194" s="4">
+        <v>2</v>
+      </c>
+      <c r="E194" s="4" t="s">
         <v>194</v>
       </c>
-      <c r="F194" s="6">
+      <c r="F194" s="5">
         <v>46274</v>
       </c>
-      <c r="G194" s="5" t="s">
+      <c r="G194" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="195" ht="13.5" customHeight="1">
-      <c r="A195" s="4">
+      <c r="A195" s="3">
         <v>1989</v>
       </c>
-      <c r="B195" s="5">
-        <v>9</v>
-      </c>
-      <c r="C195" s="5">
-        <v>1</v>
-      </c>
-      <c r="D195" s="5">
+      <c r="B195" s="4">
+        <v>9</v>
+      </c>
+      <c r="C195" s="4">
+        <v>1</v>
+      </c>
+      <c r="D195" s="4">
         <v>4</v>
       </c>
-      <c r="E195" s="5" t="s">
+      <c r="E195" s="4" t="s">
         <v>195</v>
       </c>
-      <c r="F195" s="6">
+      <c r="F195" s="5">
         <v>46274</v>
       </c>
-      <c r="G195" s="5" t="s">
+      <c r="G195" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="196" ht="13.5" customHeight="1">
-      <c r="A196" s="4">
+      <c r="A196" s="3">
         <v>1990</v>
       </c>
-      <c r="B196" s="5">
-        <v>9</v>
-      </c>
-      <c r="C196" s="5">
-        <v>1</v>
-      </c>
-      <c r="D196" s="5">
+      <c r="B196" s="4">
+        <v>9</v>
+      </c>
+      <c r="C196" s="4">
+        <v>1</v>
+      </c>
+      <c r="D196" s="4">
         <v>3</v>
       </c>
-      <c r="E196" s="5" t="s">
+      <c r="E196" s="4" t="s">
         <v>196</v>
       </c>
-      <c r="F196" s="6">
+      <c r="F196" s="5">
         <v>46275</v>
       </c>
-      <c r="G196" s="5" t="s">
+      <c r="G196" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="197" ht="13.5" customHeight="1">
-      <c r="A197" s="4">
+      <c r="A197" s="3">
         <v>1991</v>
       </c>
-      <c r="B197" s="5">
-        <v>9</v>
-      </c>
-      <c r="C197" s="5">
-        <v>1</v>
-      </c>
-      <c r="D197" s="5">
+      <c r="B197" s="4">
+        <v>9</v>
+      </c>
+      <c r="C197" s="4">
+        <v>1</v>
+      </c>
+      <c r="D197" s="4">
         <v>3</v>
       </c>
-      <c r="E197" s="5" t="s">
+      <c r="E197" s="4" t="s">
         <v>197</v>
       </c>
-      <c r="F197" s="6">
+      <c r="F197" s="5">
         <v>46275</v>
       </c>
-      <c r="G197" s="5" t="s">
+      <c r="G197" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="198" ht="13.5" customHeight="1">
-      <c r="A198" s="4">
+      <c r="A198" s="3">
         <v>1992</v>
       </c>
-      <c r="B198" s="5">
-        <v>9</v>
-      </c>
-      <c r="C198" s="5">
-        <v>1</v>
-      </c>
-      <c r="D198" s="5">
+      <c r="B198" s="4">
+        <v>9</v>
+      </c>
+      <c r="C198" s="4">
+        <v>1</v>
+      </c>
+      <c r="D198" s="4">
         <v>3</v>
       </c>
-      <c r="E198" s="5" t="s">
+      <c r="E198" s="4" t="s">
         <v>198</v>
       </c>
-      <c r="F198" s="6">
+      <c r="F198" s="5">
         <v>46275</v>
       </c>
-      <c r="G198" s="5" t="s">
+      <c r="G198" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="199" ht="13.5" customHeight="1">
-      <c r="A199" s="4">
+      <c r="A199" s="3">
         <v>1993</v>
       </c>
-      <c r="B199" s="5">
-        <v>9</v>
-      </c>
-      <c r="C199" s="5">
-        <v>1</v>
-      </c>
-      <c r="D199" s="5">
+      <c r="B199" s="4">
+        <v>9</v>
+      </c>
+      <c r="C199" s="4">
+        <v>1</v>
+      </c>
+      <c r="D199" s="4">
         <v>3</v>
       </c>
-      <c r="E199" s="5" t="s">
+      <c r="E199" s="4" t="s">
         <v>199</v>
       </c>
-      <c r="F199" s="6">
+      <c r="F199" s="5">
         <v>46275</v>
       </c>
-      <c r="G199" s="5" t="s">
+      <c r="G199" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="200" ht="13.5" customHeight="1">
-      <c r="A200" s="4">
+      <c r="A200" s="3">
         <v>1994</v>
       </c>
-      <c r="B200" s="5">
-        <v>9</v>
-      </c>
-      <c r="C200" s="5">
-        <v>1</v>
-      </c>
-      <c r="D200" s="5">
+      <c r="B200" s="4">
+        <v>9</v>
+      </c>
+      <c r="C200" s="4">
+        <v>1</v>
+      </c>
+      <c r="D200" s="4">
         <v>3</v>
       </c>
-      <c r="E200" s="5" t="s">
+      <c r="E200" s="4" t="s">
         <v>200</v>
       </c>
-      <c r="F200" s="6">
+      <c r="F200" s="5">
         <v>46275</v>
       </c>
-      <c r="G200" s="5" t="s">
+      <c r="G200" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="201" ht="13.5" customHeight="1">
-      <c r="A201" s="4">
+      <c r="A201" s="3">
         <v>1995</v>
       </c>
-      <c r="B201" s="5">
-        <v>9</v>
-      </c>
-      <c r="C201" s="5">
-        <v>1</v>
-      </c>
-      <c r="D201" s="5">
+      <c r="B201" s="4">
+        <v>9</v>
+      </c>
+      <c r="C201" s="4">
+        <v>1</v>
+      </c>
+      <c r="D201" s="4">
         <v>3</v>
       </c>
-      <c r="E201" s="5" t="s">
+      <c r="E201" s="4" t="s">
         <v>201</v>
       </c>
-      <c r="F201" s="6">
+      <c r="F201" s="5">
         <v>46275</v>
       </c>
-      <c r="G201" s="5" t="s">
+      <c r="G201" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="202" ht="13.5" customHeight="1">
-      <c r="A202" s="4">
+      <c r="A202" s="3">
         <v>1996</v>
       </c>
-      <c r="B202" s="5">
-        <v>9</v>
-      </c>
-      <c r="C202" s="5">
-        <v>1</v>
-      </c>
-      <c r="D202" s="5">
+      <c r="B202" s="4">
+        <v>9</v>
+      </c>
+      <c r="C202" s="4">
+        <v>1</v>
+      </c>
+      <c r="D202" s="4">
         <v>3</v>
       </c>
-      <c r="E202" s="5" t="s">
+      <c r="E202" s="4" t="s">
         <v>202</v>
       </c>
-      <c r="F202" s="6">
+      <c r="F202" s="5">
         <v>46275</v>
       </c>
-      <c r="G202" s="5" t="s">
+      <c r="G202" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="203" ht="13.5" customHeight="1">
-      <c r="A203" s="4">
+      <c r="A203" s="3">
         <v>1997</v>
       </c>
-      <c r="B203" s="5">
-        <v>9</v>
-      </c>
-      <c r="C203" s="5">
-        <v>1</v>
-      </c>
-      <c r="D203" s="5">
+      <c r="B203" s="4">
+        <v>9</v>
+      </c>
+      <c r="C203" s="4">
+        <v>1</v>
+      </c>
+      <c r="D203" s="4">
         <v>3</v>
       </c>
-      <c r="E203" s="5" t="s">
+      <c r="E203" s="4" t="s">
         <v>203</v>
       </c>
-      <c r="F203" s="6">
+      <c r="F203" s="5">
         <v>46275</v>
       </c>
-      <c r="G203" s="5" t="s">
+      <c r="G203" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="204" ht="13.5" customHeight="1">
-      <c r="A204" s="4">
+      <c r="A204" s="3">
         <v>1998</v>
       </c>
-      <c r="B204" s="5">
-        <v>9</v>
-      </c>
-      <c r="C204" s="5">
-        <v>1</v>
-      </c>
-      <c r="D204" s="5">
+      <c r="B204" s="4">
+        <v>9</v>
+      </c>
+      <c r="C204" s="4">
+        <v>1</v>
+      </c>
+      <c r="D204" s="4">
         <v>4</v>
       </c>
-      <c r="E204" s="5" t="s">
+      <c r="E204" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="F204" s="6">
+      <c r="F204" s="5">
         <v>46275</v>
       </c>
-      <c r="G204" s="5" t="s">
+      <c r="G204" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="205" ht="13.5" customHeight="1">
-      <c r="A205" s="4">
+      <c r="A205" s="3">
         <v>1999</v>
       </c>
-      <c r="B205" s="5">
-        <v>9</v>
-      </c>
-      <c r="C205" s="5">
-        <v>1</v>
-      </c>
-      <c r="D205" s="5">
+      <c r="B205" s="4">
+        <v>9</v>
+      </c>
+      <c r="C205" s="4">
+        <v>1</v>
+      </c>
+      <c r="D205" s="4">
         <v>4</v>
       </c>
-      <c r="E205" s="5" t="s">
+      <c r="E205" s="4" t="s">
         <v>204</v>
       </c>
-      <c r="F205" s="6">
+      <c r="F205" s="5">
         <v>46275</v>
       </c>
-      <c r="G205" s="5" t="s">
+      <c r="G205" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="206" ht="13.5" customHeight="1">
-      <c r="A206" s="4">
+      <c r="A206" s="3">
         <v>2000</v>
       </c>
-      <c r="B206" s="5">
-        <v>9</v>
-      </c>
-      <c r="C206" s="5">
-        <v>1</v>
-      </c>
-      <c r="D206" s="5">
+      <c r="B206" s="4">
+        <v>9</v>
+      </c>
+      <c r="C206" s="4">
+        <v>1</v>
+      </c>
+      <c r="D206" s="4">
         <v>4</v>
       </c>
-      <c r="E206" s="5" t="s">
+      <c r="E206" s="4" t="s">
         <v>205</v>
       </c>
-      <c r="F206" s="6">
+      <c r="F206" s="5">
         <v>46275</v>
       </c>
-      <c r="G206" s="5" t="s">
+      <c r="G206" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="207" ht="13.5" customHeight="1">
-      <c r="A207" s="4">
+      <c r="A207" s="3">
         <v>2001</v>
       </c>
-      <c r="B207" s="5">
-        <v>9</v>
-      </c>
-      <c r="C207" s="5">
-        <v>1</v>
-      </c>
-      <c r="D207" s="5">
+      <c r="B207" s="4">
+        <v>9</v>
+      </c>
+      <c r="C207" s="4">
+        <v>1</v>
+      </c>
+      <c r="D207" s="4">
         <v>4</v>
       </c>
-      <c r="E207" s="5" t="s">
+      <c r="E207" s="4" t="s">
         <v>206</v>
       </c>
-      <c r="F207" s="6">
+      <c r="F207" s="5">
         <v>46275</v>
       </c>
-      <c r="G207" s="5" t="s">
+      <c r="G207" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="208" ht="13.5" customHeight="1">
-      <c r="A208" s="4">
+      <c r="A208" s="3">
         <v>2002</v>
       </c>
-      <c r="B208" s="5">
-        <v>9</v>
-      </c>
-      <c r="C208" s="5">
-        <v>1</v>
-      </c>
-      <c r="D208" s="5">
+      <c r="B208" s="4">
+        <v>9</v>
+      </c>
+      <c r="C208" s="4">
+        <v>1</v>
+      </c>
+      <c r="D208" s="4">
         <v>4</v>
       </c>
-      <c r="E208" s="5" t="s">
+      <c r="E208" s="4" t="s">
         <v>207</v>
       </c>
-      <c r="F208" s="6">
+      <c r="F208" s="5">
         <v>46275</v>
       </c>
-      <c r="G208" s="5" t="s">
+      <c r="G208" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="209" ht="13.5" customHeight="1">
-      <c r="A209" s="4">
+      <c r="A209" s="3">
         <v>2003</v>
       </c>
-      <c r="B209" s="5">
-        <v>9</v>
-      </c>
-      <c r="C209" s="5">
-        <v>1</v>
-      </c>
-      <c r="D209" s="5">
+      <c r="B209" s="4">
+        <v>9</v>
+      </c>
+      <c r="C209" s="4">
+        <v>1</v>
+      </c>
+      <c r="D209" s="4">
         <v>5</v>
       </c>
-      <c r="E209" s="5" t="s">
+      <c r="E209" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="F209" s="6">
+      <c r="F209" s="5">
         <v>46275</v>
       </c>
-      <c r="G209" s="5" t="s">
+      <c r="G209" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="210" ht="13.5" customHeight="1">
-      <c r="A210" s="4">
+      <c r="A210" s="3">
         <v>2004</v>
       </c>
-      <c r="B210" s="5">
-        <v>9</v>
-      </c>
-      <c r="C210" s="5">
-        <v>1</v>
-      </c>
-      <c r="D210" s="5">
+      <c r="B210" s="4">
+        <v>9</v>
+      </c>
+      <c r="C210" s="4">
+        <v>1</v>
+      </c>
+      <c r="D210" s="4">
         <v>5</v>
       </c>
-      <c r="E210" s="5" t="s">
+      <c r="E210" s="4" t="s">
         <v>208</v>
       </c>
-      <c r="F210" s="6">
+      <c r="F210" s="5">
         <v>46275</v>
       </c>
-      <c r="G210" s="5" t="s">
+      <c r="G210" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="211" ht="13.5" customHeight="1">
-      <c r="A211" s="4">
+      <c r="A211" s="3">
         <v>2005</v>
       </c>
-      <c r="B211" s="5">
-        <v>9</v>
-      </c>
-      <c r="C211" s="5">
-        <v>1</v>
-      </c>
-      <c r="D211" s="5">
+      <c r="B211" s="4">
+        <v>9</v>
+      </c>
+      <c r="C211" s="4">
+        <v>1</v>
+      </c>
+      <c r="D211" s="4">
         <v>5</v>
       </c>
-      <c r="E211" s="5" t="s">
+      <c r="E211" s="4" t="s">
         <v>209</v>
       </c>
-      <c r="F211" s="6">
+      <c r="F211" s="5">
         <v>46275</v>
       </c>
-      <c r="G211" s="5" t="s">
+      <c r="G211" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="212" ht="13.5" customHeight="1">
-      <c r="A212" s="4">
+      <c r="A212" s="3">
         <v>2006</v>
       </c>
-      <c r="B212" s="5">
-        <v>9</v>
-      </c>
-      <c r="C212" s="5">
-        <v>1</v>
-      </c>
-      <c r="D212" s="5">
+      <c r="B212" s="4">
+        <v>9</v>
+      </c>
+      <c r="C212" s="4">
+        <v>1</v>
+      </c>
+      <c r="D212" s="4">
         <v>5</v>
       </c>
-      <c r="E212" s="5" t="s">
+      <c r="E212" s="4" t="s">
         <v>210</v>
       </c>
-      <c r="F212" s="6">
+      <c r="F212" s="5">
         <v>46275</v>
       </c>
-      <c r="G212" s="5" t="s">
+      <c r="G212" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="213" ht="13.5" customHeight="1">
-      <c r="A213" s="4">
+      <c r="A213" s="3">
         <v>2007</v>
       </c>
-      <c r="B213" s="5">
-        <v>9</v>
-      </c>
-      <c r="C213" s="5">
-        <v>1</v>
-      </c>
-      <c r="D213" s="5">
+      <c r="B213" s="4">
+        <v>9</v>
+      </c>
+      <c r="C213" s="4">
+        <v>1</v>
+      </c>
+      <c r="D213" s="4">
         <v>5</v>
       </c>
-      <c r="E213" s="5" t="s">
+      <c r="E213" s="4" t="s">
         <v>211</v>
       </c>
-      <c r="F213" s="6">
+      <c r="F213" s="5">
         <v>46275</v>
       </c>
-      <c r="G213" s="5" t="s">
+      <c r="G213" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="214" ht="13.5" customHeight="1">
-      <c r="A214" s="4">
+      <c r="A214" s="3">
         <v>2008</v>
       </c>
-      <c r="B214" s="5">
-        <v>9</v>
-      </c>
-      <c r="C214" s="5">
-        <v>1</v>
-      </c>
-      <c r="D214" s="5">
+      <c r="B214" s="4">
+        <v>9</v>
+      </c>
+      <c r="C214" s="4">
+        <v>1</v>
+      </c>
+      <c r="D214" s="4">
         <v>5</v>
       </c>
-      <c r="E214" s="5" t="s">
+      <c r="E214" s="4" t="s">
         <v>212</v>
       </c>
-      <c r="F214" s="6">
+      <c r="F214" s="5">
         <v>46275</v>
       </c>
-      <c r="G214" s="5" t="s">
+      <c r="G214" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="215" ht="13.5" customHeight="1">
-      <c r="A215" s="4">
+      <c r="A215" s="3">
         <v>2009</v>
       </c>
-      <c r="B215" s="5">
-        <v>9</v>
-      </c>
-      <c r="C215" s="5">
-        <v>2</v>
-      </c>
-      <c r="D215" s="5">
+      <c r="B215" s="4">
+        <v>9</v>
+      </c>
+      <c r="C215" s="4">
+        <v>2</v>
+      </c>
+      <c r="D215" s="4">
         <v>6</v>
       </c>
-      <c r="E215" s="5" t="s">
+      <c r="E215" s="4" t="s">
         <v>213</v>
       </c>
-      <c r="F215" s="6">
+      <c r="F215" s="5">
         <v>46275</v>
       </c>
-      <c r="G215" s="5" t="s">
+      <c r="G215" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="216" ht="13.5" customHeight="1">
-      <c r="A216" s="4">
+      <c r="A216" s="3">
         <v>2011</v>
       </c>
-      <c r="B216" s="5">
-        <v>9</v>
-      </c>
-      <c r="C216" s="5">
-        <v>2</v>
-      </c>
-      <c r="D216" s="5">
+      <c r="B216" s="4">
+        <v>9</v>
+      </c>
+      <c r="C216" s="4">
+        <v>2</v>
+      </c>
+      <c r="D216" s="4">
         <v>6</v>
       </c>
-      <c r="E216" s="5" t="s">
+      <c r="E216" s="4" t="s">
         <v>214</v>
       </c>
-      <c r="F216" s="6">
+      <c r="F216" s="5">
         <v>46275</v>
       </c>
-      <c r="G216" s="5" t="s">
+      <c r="G216" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="217" ht="13.5" customHeight="1">
-      <c r="A217" s="4">
+      <c r="A217" s="3">
         <v>2012</v>
       </c>
-      <c r="B217" s="5">
-        <v>9</v>
-      </c>
-      <c r="C217" s="5">
-        <v>2</v>
-      </c>
-      <c r="D217" s="5">
+      <c r="B217" s="4">
+        <v>9</v>
+      </c>
+      <c r="C217" s="4">
+        <v>2</v>
+      </c>
+      <c r="D217" s="4">
         <v>6</v>
       </c>
-      <c r="E217" s="5" t="s">
+      <c r="E217" s="4" t="s">
         <v>215</v>
       </c>
-      <c r="F217" s="6">
+      <c r="F217" s="5">
         <v>46275</v>
       </c>
-      <c r="G217" s="5" t="s">
+      <c r="G217" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="218" ht="13.5" customHeight="1">
-      <c r="A218" s="4">
+      <c r="A218" s="3">
         <v>2013</v>
       </c>
-      <c r="B218" s="5">
-        <v>9</v>
-      </c>
-      <c r="C218" s="5">
-        <v>2</v>
-      </c>
-      <c r="D218" s="5">
+      <c r="B218" s="4">
+        <v>9</v>
+      </c>
+      <c r="C218" s="4">
+        <v>2</v>
+      </c>
+      <c r="D218" s="4">
         <v>6</v>
       </c>
-      <c r="E218" s="5" t="s">
+      <c r="E218" s="4" t="s">
         <v>216</v>
       </c>
-      <c r="F218" s="6">
+      <c r="F218" s="5">
         <v>46275</v>
       </c>
-      <c r="G218" s="5" t="s">
+      <c r="G218" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="219" ht="13.5" customHeight="1">
-      <c r="A219" s="4">
+      <c r="A219" s="3">
         <v>2014</v>
       </c>
-      <c r="B219" s="5">
-        <v>9</v>
-      </c>
-      <c r="C219" s="5">
-        <v>2</v>
-      </c>
-      <c r="D219" s="5">
+      <c r="B219" s="4">
+        <v>9</v>
+      </c>
+      <c r="C219" s="4">
+        <v>2</v>
+      </c>
+      <c r="D219" s="4">
         <v>6</v>
       </c>
-      <c r="E219" s="5" t="s">
+      <c r="E219" s="4" t="s">
         <v>217</v>
       </c>
-      <c r="F219" s="6">
+      <c r="F219" s="5">
         <v>46275</v>
       </c>
-      <c r="G219" s="5" t="s">
+      <c r="G219" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="220" ht="13.5" customHeight="1">
-      <c r="A220" s="4">
+      <c r="A220" s="3">
         <v>2015</v>
       </c>
-      <c r="B220" s="5">
-        <v>9</v>
-      </c>
-      <c r="C220" s="5">
-        <v>2</v>
-      </c>
-      <c r="D220" s="5">
+      <c r="B220" s="4">
+        <v>9</v>
+      </c>
+      <c r="C220" s="4">
+        <v>2</v>
+      </c>
+      <c r="D220" s="4">
         <v>7</v>
       </c>
-      <c r="E220" s="5" t="s">
+      <c r="E220" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="F220" s="6">
+      <c r="F220" s="5">
         <v>46275</v>
       </c>
-      <c r="G220" s="5" t="s">
+      <c r="G220" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="221" ht="13.5" customHeight="1">
-      <c r="A221" s="4">
+      <c r="A221" s="3">
         <v>2016</v>
       </c>
-      <c r="B221" s="5">
-        <v>9</v>
-      </c>
-      <c r="C221" s="5">
-        <v>2</v>
-      </c>
-      <c r="D221" s="5">
+      <c r="B221" s="4">
+        <v>9</v>
+      </c>
+      <c r="C221" s="4">
+        <v>2</v>
+      </c>
+      <c r="D221" s="4">
         <v>7</v>
       </c>
-      <c r="E221" s="5" t="s">
+      <c r="E221" s="4" t="s">
         <v>218</v>
       </c>
-      <c r="F221" s="6">
+      <c r="F221" s="5">
         <v>46275</v>
       </c>
-      <c r="G221" s="5" t="s">
+      <c r="G221" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="222" ht="13.5" customHeight="1">
-      <c r="A222" s="4">
+      <c r="A222" s="3">
         <v>2017</v>
       </c>
-      <c r="B222" s="5">
-        <v>9</v>
-      </c>
-      <c r="C222" s="5">
-        <v>2</v>
-      </c>
-      <c r="D222" s="5">
-        <v>8</v>
-      </c>
-      <c r="E222" s="5" t="s">
+      <c r="B222" s="4">
+        <v>9</v>
+      </c>
+      <c r="C222" s="4">
+        <v>2</v>
+      </c>
+      <c r="D222" s="4">
+        <v>8</v>
+      </c>
+      <c r="E222" s="4" t="s">
         <v>219</v>
       </c>
-      <c r="F222" s="6">
+      <c r="F222" s="5">
         <v>46275</v>
       </c>
-      <c r="G222" s="5" t="s">
+      <c r="G222" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="223" ht="13.5" customHeight="1">
-      <c r="A223" s="4">
+      <c r="A223" s="3">
         <v>2018</v>
       </c>
-      <c r="B223" s="5">
-        <v>9</v>
-      </c>
-      <c r="C223" s="5">
-        <v>2</v>
-      </c>
-      <c r="D223" s="5">
-        <v>8</v>
-      </c>
-      <c r="E223" s="5" t="s">
+      <c r="B223" s="4">
+        <v>9</v>
+      </c>
+      <c r="C223" s="4">
+        <v>2</v>
+      </c>
+      <c r="D223" s="4">
+        <v>8</v>
+      </c>
+      <c r="E223" s="4" t="s">
         <v>220</v>
       </c>
-      <c r="F223" s="6">
+      <c r="F223" s="5">
         <v>46275</v>
       </c>
-      <c r="G223" s="5" t="s">
+      <c r="G223" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="224" ht="13.5" customHeight="1">
-      <c r="A224" s="4">
+      <c r="A224" s="3">
         <v>2019</v>
       </c>
-      <c r="B224" s="5">
-        <v>9</v>
-      </c>
-      <c r="C224" s="5">
-        <v>2</v>
-      </c>
-      <c r="D224" s="5">
-        <v>8</v>
-      </c>
-      <c r="E224" s="5" t="s">
+      <c r="B224" s="4">
+        <v>9</v>
+      </c>
+      <c r="C224" s="4">
+        <v>2</v>
+      </c>
+      <c r="D224" s="4">
+        <v>8</v>
+      </c>
+      <c r="E224" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="F224" s="6">
+      <c r="F224" s="5">
         <v>46275</v>
       </c>
-      <c r="G224" s="5" t="s">
+      <c r="G224" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="225" ht="13.5" customHeight="1">
-      <c r="A225" s="4">
+      <c r="A225" s="3">
         <v>2020</v>
       </c>
-      <c r="B225" s="5">
-        <v>9</v>
-      </c>
-      <c r="C225" s="5">
-        <v>2</v>
-      </c>
-      <c r="D225" s="5">
-        <v>8</v>
-      </c>
-      <c r="E225" s="5" t="s">
+      <c r="B225" s="4">
+        <v>9</v>
+      </c>
+      <c r="C225" s="4">
+        <v>2</v>
+      </c>
+      <c r="D225" s="4">
+        <v>8</v>
+      </c>
+      <c r="E225" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="F225" s="6">
+      <c r="F225" s="5">
         <v>46275</v>
       </c>
-      <c r="G225" s="5" t="s">
+      <c r="G225" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="226" ht="13.5" customHeight="1">
-      <c r="A226" s="4">
+      <c r="A226" s="3">
         <v>2021</v>
       </c>
-      <c r="B226" s="5">
-        <v>9</v>
-      </c>
-      <c r="C226" s="5">
-        <v>2</v>
-      </c>
-      <c r="D226" s="5">
-        <v>8</v>
-      </c>
-      <c r="E226" s="5" t="s">
+      <c r="B226" s="4">
+        <v>9</v>
+      </c>
+      <c r="C226" s="4">
+        <v>2</v>
+      </c>
+      <c r="D226" s="4">
+        <v>8</v>
+      </c>
+      <c r="E226" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="F226" s="6">
+      <c r="F226" s="5">
         <v>46275</v>
       </c>
-      <c r="G226" s="5" t="s">
+      <c r="G226" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="227" ht="13.5" customHeight="1">
-      <c r="A227" s="4">
+      <c r="A227" s="3">
         <v>2022</v>
       </c>
-      <c r="B227" s="5">
-        <v>9</v>
-      </c>
-      <c r="C227" s="5">
-        <v>2</v>
-      </c>
-      <c r="D227" s="5">
-        <v>8</v>
-      </c>
-      <c r="E227" s="5" t="s">
+      <c r="B227" s="4">
+        <v>9</v>
+      </c>
+      <c r="C227" s="4">
+        <v>2</v>
+      </c>
+      <c r="D227" s="4">
+        <v>8</v>
+      </c>
+      <c r="E227" s="4" t="s">
         <v>224</v>
       </c>
-      <c r="F227" s="6">
+      <c r="F227" s="5">
         <v>46275</v>
       </c>
-      <c r="G227" s="5" t="s">
+      <c r="G227" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="228" ht="13.5" customHeight="1">
-      <c r="A228" s="4">
+      <c r="A228" s="3">
         <v>2023</v>
       </c>
-      <c r="B228" s="5">
-        <v>9</v>
-      </c>
-      <c r="C228" s="5">
-        <v>2</v>
-      </c>
-      <c r="D228" s="5">
-        <v>8</v>
-      </c>
-      <c r="E228" s="5" t="s">
+      <c r="B228" s="4">
+        <v>9</v>
+      </c>
+      <c r="C228" s="4">
+        <v>2</v>
+      </c>
+      <c r="D228" s="4">
+        <v>8</v>
+      </c>
+      <c r="E228" s="4" t="s">
         <v>225</v>
       </c>
-      <c r="F228" s="6">
+      <c r="F228" s="5">
         <v>46275</v>
       </c>
-      <c r="G228" s="5" t="s">
+      <c r="G228" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="229" ht="13.5" customHeight="1">
-      <c r="A229" s="4">
+      <c r="A229" s="3">
         <v>2024</v>
       </c>
-      <c r="B229" s="5">
-        <v>9</v>
-      </c>
-      <c r="C229" s="5">
-        <v>1</v>
-      </c>
-      <c r="D229" s="5">
+      <c r="B229" s="4">
+        <v>9</v>
+      </c>
+      <c r="C229" s="4">
+        <v>1</v>
+      </c>
+      <c r="D229" s="4">
         <v>4</v>
       </c>
-      <c r="E229" s="5" t="s">
+      <c r="E229" s="4" t="s">
         <v>226</v>
       </c>
-      <c r="F229" s="6">
+      <c r="F229" s="5">
         <v>46276</v>
       </c>
-      <c r="G229" s="5" t="s">
+      <c r="G229" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="230" ht="13.5" customHeight="1">
-      <c r="A230" s="4">
+      <c r="A230" s="3">
         <v>2025</v>
       </c>
-      <c r="B230" s="5">
-        <v>9</v>
-      </c>
-      <c r="C230" s="5">
-        <v>2</v>
-      </c>
-      <c r="D230" s="5">
+      <c r="B230" s="4">
+        <v>9</v>
+      </c>
+      <c r="C230" s="4">
+        <v>2</v>
+      </c>
+      <c r="D230" s="4">
         <v>6</v>
       </c>
-      <c r="E230" s="5" t="s">
+      <c r="E230" s="4" t="s">
         <v>227</v>
       </c>
-      <c r="F230" s="6">
+      <c r="F230" s="5">
         <v>46276</v>
       </c>
-      <c r="G230" s="5" t="s">
+      <c r="G230" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="231" ht="13.5" customHeight="1">
-      <c r="A231" s="4">
+      <c r="A231" s="3">
         <v>2026</v>
       </c>
-      <c r="B231" s="5">
-        <v>9</v>
-      </c>
-      <c r="C231" s="5">
-        <v>1</v>
-      </c>
-      <c r="D231" s="5">
-        <v>1</v>
-      </c>
-      <c r="E231" s="5" t="s">
+      <c r="B231" s="4">
+        <v>9</v>
+      </c>
+      <c r="C231" s="4">
+        <v>1</v>
+      </c>
+      <c r="D231" s="4">
+        <v>1</v>
+      </c>
+      <c r="E231" s="4" t="s">
         <v>228</v>
       </c>
-      <c r="F231" s="6">
+      <c r="F231" s="5">
         <v>46276</v>
       </c>
-      <c r="G231" s="5" t="s">
+      <c r="G231" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="232" ht="13.5" customHeight="1">
-      <c r="A232" s="4">
+      <c r="A232" s="3">
         <v>2027</v>
       </c>
-      <c r="B232" s="5">
-        <v>9</v>
-      </c>
-      <c r="C232" s="5">
-        <v>1</v>
-      </c>
-      <c r="D232" s="5">
+      <c r="B232" s="4">
+        <v>9</v>
+      </c>
+      <c r="C232" s="4">
+        <v>1</v>
+      </c>
+      <c r="D232" s="4">
         <v>5</v>
       </c>
-      <c r="E232" s="5" t="s">
+      <c r="E232" s="4" t="s">
         <v>229</v>
       </c>
-      <c r="F232" s="6">
+      <c r="F232" s="5">
         <v>46276</v>
       </c>
-      <c r="G232" s="5" t="s">
+      <c r="G232" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="233" ht="13.5" customHeight="1">
-      <c r="A233" s="4">
+      <c r="A233" s="3">
         <v>2029</v>
       </c>
-      <c r="B233" s="5">
-        <v>9</v>
-      </c>
-      <c r="C233" s="5">
+      <c r="B233" s="4">
+        <v>9</v>
+      </c>
+      <c r="C233" s="4">
         <v>3</v>
       </c>
-      <c r="D233" s="5">
+      <c r="D233" s="4">
         <v>12</v>
       </c>
-      <c r="E233" s="5" t="s">
+      <c r="E233" s="4" t="s">
         <v>230</v>
       </c>
-      <c r="F233" s="6">
+      <c r="F233" s="5">
         <v>46276</v>
       </c>
-      <c r="G233" s="5" t="s">
+      <c r="G233" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="234" ht="13.5" customHeight="1">
-      <c r="A234" s="4">
+      <c r="A234" s="3">
         <v>2030</v>
       </c>
-      <c r="B234" s="5">
-        <v>9</v>
-      </c>
-      <c r="C234" s="5">
-        <v>1</v>
-      </c>
-      <c r="D234" s="5">
-        <v>2</v>
-      </c>
-      <c r="E234" s="5" t="s">
+      <c r="B234" s="4">
+        <v>9</v>
+      </c>
+      <c r="C234" s="4">
+        <v>1</v>
+      </c>
+      <c r="D234" s="4">
+        <v>2</v>
+      </c>
+      <c r="E234" s="4" t="s">
         <v>231</v>
       </c>
-      <c r="F234" s="6">
+      <c r="F234" s="5">
         <v>46276</v>
       </c>
-      <c r="G234" s="5" t="s">
+      <c r="G234" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="235" ht="13.5" customHeight="1">
-      <c r="A235" s="4">
+      <c r="A235" s="3">
         <v>2031</v>
       </c>
-      <c r="B235" s="5">
-        <v>9</v>
-      </c>
-      <c r="C235" s="5">
-        <v>2</v>
-      </c>
-      <c r="D235" s="5">
+      <c r="B235" s="4">
+        <v>9</v>
+      </c>
+      <c r="C235" s="4">
+        <v>2</v>
+      </c>
+      <c r="D235" s="4">
         <v>7</v>
       </c>
-      <c r="E235" s="5" t="s">
+      <c r="E235" s="4" t="s">
         <v>232</v>
       </c>
-      <c r="F235" s="6">
+      <c r="F235" s="5">
         <v>46280</v>
       </c>
-      <c r="G235" s="5" t="s">
+      <c r="G235" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="236" ht="13.5" customHeight="1">
-      <c r="A236" s="4">
+      <c r="A236" s="3">
         <v>2032</v>
       </c>
-      <c r="B236" s="5">
-        <v>9</v>
-      </c>
-      <c r="C236" s="5">
+      <c r="B236" s="4">
+        <v>9</v>
+      </c>
+      <c r="C236" s="4">
         <v>3</v>
       </c>
-      <c r="D236" s="5">
+      <c r="D236" s="4">
         <v>12</v>
       </c>
-      <c r="E236" s="5" t="s">
+      <c r="E236" s="4" t="s">
         <v>233</v>
       </c>
-      <c r="F236" s="6">
+      <c r="F236" s="5">
         <v>46280</v>
       </c>
-      <c r="G236" s="5" t="s">
+      <c r="G236" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="237" ht="13.5" customHeight="1">
-      <c r="A237" s="4">
+      <c r="A237" s="3">
         <v>2033</v>
       </c>
-      <c r="B237" s="5">
-        <v>9</v>
-      </c>
-      <c r="C237" s="5">
+      <c r="B237" s="4">
+        <v>9</v>
+      </c>
+      <c r="C237" s="4">
         <v>3</v>
       </c>
-      <c r="D237" s="5">
+      <c r="D237" s="4">
         <v>14</v>
       </c>
-      <c r="E237" s="5" t="s">
+      <c r="E237" s="4" t="s">
         <v>234</v>
       </c>
-      <c r="F237" s="6">
+      <c r="F237" s="5">
         <v>46280</v>
       </c>
-      <c r="G237" s="5" t="s">
+      <c r="G237" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="238" ht="13.5" customHeight="1">
-      <c r="A238" s="4">
+      <c r="A238" s="3">
         <v>2034</v>
       </c>
-      <c r="B238" s="5">
-        <v>9</v>
-      </c>
-      <c r="C238" s="5">
-        <v>1</v>
-      </c>
-      <c r="D238" s="5">
+      <c r="B238" s="4">
+        <v>9</v>
+      </c>
+      <c r="C238" s="4">
+        <v>1</v>
+      </c>
+      <c r="D238" s="4">
         <v>5</v>
       </c>
-      <c r="E238" s="5" t="s">
+      <c r="E238" s="4" t="s">
         <v>235</v>
       </c>
-      <c r="F238" s="6">
+      <c r="F238" s="5">
         <v>46280</v>
       </c>
-      <c r="G238" s="5" t="s">
+      <c r="G238" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="239" ht="13.5" customHeight="1">
-      <c r="A239" s="4">
+      <c r="A239" s="3">
         <v>2035</v>
       </c>
-      <c r="B239" s="5">
-        <v>9</v>
-      </c>
-      <c r="C239" s="5">
-        <v>2</v>
-      </c>
-      <c r="D239" s="5">
+      <c r="B239" s="4">
+        <v>9</v>
+      </c>
+      <c r="C239" s="4">
+        <v>2</v>
+      </c>
+      <c r="D239" s="4">
         <v>6</v>
       </c>
-      <c r="E239" s="5" t="s">
+      <c r="E239" s="4" t="s">
         <v>236</v>
       </c>
-      <c r="F239" s="6">
+      <c r="F239" s="5">
         <v>46280</v>
       </c>
-      <c r="G239" s="5" t="s">
+      <c r="G239" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="240" ht="13.5" customHeight="1">
-      <c r="A240" s="4">
+      <c r="A240" s="3">
         <v>2036</v>
       </c>
-      <c r="B240" s="5">
-        <v>9</v>
-      </c>
-      <c r="C240" s="5">
-        <v>1</v>
-      </c>
-      <c r="D240" s="5">
+      <c r="B240" s="4">
+        <v>9</v>
+      </c>
+      <c r="C240" s="4">
+        <v>1</v>
+      </c>
+      <c r="D240" s="4">
         <v>5</v>
       </c>
-      <c r="E240" s="5" t="s">
+      <c r="E240" s="4" t="s">
         <v>237</v>
       </c>
-      <c r="F240" s="6">
+      <c r="F240" s="5">
         <v>46280</v>
       </c>
-      <c r="G240" s="5" t="s">
+      <c r="G240" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="241" ht="13.5" customHeight="1">
-      <c r="A241" s="4">
+      <c r="A241" s="3">
         <v>2037</v>
       </c>
-      <c r="B241" s="5">
-        <v>9</v>
-      </c>
-      <c r="C241" s="5">
-        <v>2</v>
-      </c>
-      <c r="D241" s="5">
-        <v>8</v>
-      </c>
-      <c r="E241" s="5" t="s">
+      <c r="B241" s="4">
+        <v>9</v>
+      </c>
+      <c r="C241" s="4">
+        <v>2</v>
+      </c>
+      <c r="D241" s="4">
+        <v>8</v>
+      </c>
+      <c r="E241" s="4" t="s">
         <v>238</v>
       </c>
-      <c r="F241" s="6">
+      <c r="F241" s="5">
         <v>46280</v>
       </c>
-      <c r="G241" s="5" t="s">
+      <c r="G241" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="242" ht="13.5" customHeight="1">
-      <c r="A242" s="4">
+      <c r="A242" s="3">
         <v>2038</v>
       </c>
-      <c r="B242" s="5">
-        <v>9</v>
-      </c>
-      <c r="C242" s="5">
-        <v>2</v>
-      </c>
-      <c r="D242" s="5">
-        <v>9</v>
-      </c>
-      <c r="E242" s="5" t="s">
+      <c r="B242" s="4">
+        <v>9</v>
+      </c>
+      <c r="C242" s="4">
+        <v>2</v>
+      </c>
+      <c r="D242" s="4">
+        <v>9</v>
+      </c>
+      <c r="E242" s="4" t="s">
         <v>239</v>
       </c>
-      <c r="F242" s="6">
+      <c r="F242" s="5">
         <v>46280</v>
       </c>
-      <c r="G242" s="5" t="s">
+      <c r="G242" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="243" ht="13.5" customHeight="1">
-      <c r="A243" s="4">
+      <c r="A243" s="3">
         <v>2039</v>
       </c>
-      <c r="B243" s="5">
-        <v>9</v>
-      </c>
-      <c r="C243" s="5">
+      <c r="B243" s="4">
+        <v>9</v>
+      </c>
+      <c r="C243" s="4">
         <v>3</v>
       </c>
-      <c r="D243" s="5">
+      <c r="D243" s="4">
         <v>12</v>
       </c>
-      <c r="E243" s="5" t="s">
+      <c r="E243" s="4" t="s">
         <v>240</v>
       </c>
-      <c r="F243" s="6">
+      <c r="F243" s="5">
         <v>46280</v>
       </c>
-      <c r="G243" s="5" t="s">
+      <c r="G243" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="244" ht="13.5" customHeight="1">
-      <c r="A244" s="4">
+      <c r="A244" s="3">
         <v>2040</v>
       </c>
-      <c r="B244" s="5">
-        <v>9</v>
-      </c>
-      <c r="C244" s="5">
-        <v>1</v>
-      </c>
-      <c r="D244" s="5">
+      <c r="B244" s="4">
+        <v>9</v>
+      </c>
+      <c r="C244" s="4">
+        <v>1</v>
+      </c>
+      <c r="D244" s="4">
         <v>4</v>
       </c>
-      <c r="E244" s="5" t="s">
+      <c r="E244" s="4" t="s">
         <v>241</v>
       </c>
-      <c r="F244" s="6">
+      <c r="F244" s="5">
         <v>46280</v>
       </c>
-      <c r="G244" s="5" t="s">
+      <c r="G244" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="245" ht="13.5" customHeight="1">
-      <c r="A245" s="4">
+      <c r="A245" s="3">
         <v>2041</v>
       </c>
-      <c r="B245" s="5">
-        <v>9</v>
-      </c>
-      <c r="C245" s="5">
-        <v>2</v>
-      </c>
-      <c r="D245" s="5">
+      <c r="B245" s="4">
+        <v>9</v>
+      </c>
+      <c r="C245" s="4">
+        <v>2</v>
+      </c>
+      <c r="D245" s="4">
         <v>10</v>
       </c>
-      <c r="E245" s="5" t="s">
+      <c r="E245" s="4" t="s">
         <v>242</v>
       </c>
-      <c r="F245" s="6">
+      <c r="F245" s="5">
         <v>46280</v>
       </c>
-      <c r="G245" s="5" t="s">
+      <c r="G245" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="246" ht="13.5" customHeight="1">
-      <c r="A246" s="4">
+      <c r="A246" s="3">
         <v>2042</v>
       </c>
-      <c r="B246" s="5">
-        <v>9</v>
-      </c>
-      <c r="C246" s="5">
-        <v>1</v>
-      </c>
-      <c r="D246" s="5">
+      <c r="B246" s="4">
+        <v>9</v>
+      </c>
+      <c r="C246" s="4">
+        <v>1</v>
+      </c>
+      <c r="D246" s="4">
         <v>4</v>
       </c>
-      <c r="E246" s="5" t="s">
+      <c r="E246" s="4" t="s">
         <v>243</v>
       </c>
-      <c r="F246" s="6">
+      <c r="F246" s="5">
         <v>46280</v>
       </c>
-      <c r="G246" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="247" ht="15" customHeight="1">
-      <c r="B247" s="5"/>
-      <c r="C247"/>
-      <c r="D247" s="5"/>
-      <c r="E247"/>
-    </row>
-    <row r="248" ht="15" customHeight="1">
-      <c r="B248" s="5"/>
-      <c r="C248"/>
-      <c r="D248" s="5"/>
-      <c r="E248"/>
-    </row>
-    <row r="249" ht="15" customHeight="1">
-      <c r="D249" s="5"/>
-      <c r="E249"/>
-    </row>
-    <row r="250" ht="15" customHeight="1">
-      <c r="D250" s="5"/>
-      <c r="E250"/>
-    </row>
-    <row r="251" ht="15" customHeight="1">
-      <c r="D251" s="5"/>
-      <c r="E251"/>
-    </row>
-    <row r="252" ht="15" customHeight="1">
-      <c r="D252" s="5"/>
-      <c r="E252"/>
-    </row>
-    <row r="253" ht="15" customHeight="1">
-      <c r="D253" s="5"/>
-      <c r="E253"/>
-    </row>
-    <row r="254" ht="15" customHeight="1">
-      <c r="D254" s="5"/>
-      <c r="E254"/>
-    </row>
-    <row r="255" ht="15" customHeight="1">
-      <c r="D255" s="5"/>
-      <c r="E255"/>
+      <c r="G246" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="247" ht="13.5" customHeight="1">
+      <c r="A247" s="8"/>
+      <c r="B247" s="4"/>
+      <c r="C247" s="9"/>
+      <c r="D247" s="4"/>
+      <c r="E247" s="9"/>
+      <c r="F247" s="10"/>
+      <c r="G247" s="9"/>
+    </row>
+    <row r="248" ht="13.5" customHeight="1">
+      <c r="A248" s="8"/>
+      <c r="B248" s="4"/>
+      <c r="C248" s="9"/>
+      <c r="D248" s="4"/>
+      <c r="E248" s="9"/>
+      <c r="F248" s="10"/>
+      <c r="G248" s="9"/>
+    </row>
+    <row r="249" ht="13.5" customHeight="1">
+      <c r="A249" s="8"/>
+      <c r="B249" s="4"/>
+      <c r="C249" s="9"/>
+      <c r="D249" s="4"/>
+      <c r="E249" s="9"/>
+      <c r="F249" s="10"/>
+      <c r="G249" s="9"/>
+    </row>
+    <row r="250" ht="13.5" customHeight="1">
+      <c r="A250" s="8"/>
+      <c r="B250" s="4"/>
+      <c r="C250" s="9"/>
+      <c r="D250" s="4"/>
+      <c r="E250" s="9"/>
+      <c r="F250" s="10"/>
+      <c r="G250" s="9"/>
+    </row>
+    <row r="251" ht="13.5" customHeight="1">
+      <c r="A251" s="8"/>
+      <c r="B251" s="4"/>
+      <c r="C251" s="9"/>
+      <c r="D251" s="4"/>
+      <c r="E251" s="9"/>
+      <c r="F251" s="10"/>
+      <c r="G251" s="9"/>
+    </row>
+    <row r="252" ht="13.5" customHeight="1">
+      <c r="A252" s="8"/>
+      <c r="B252" s="4"/>
+      <c r="C252" s="9"/>
+      <c r="D252" s="4"/>
+      <c r="E252" s="9"/>
+      <c r="F252" s="10"/>
+      <c r="G252" s="9"/>
+    </row>
+    <row r="253" ht="13.5" customHeight="1">
+      <c r="A253" s="8"/>
+      <c r="B253" s="4"/>
+      <c r="C253" s="9"/>
+      <c r="D253" s="4"/>
+      <c r="E253" s="9"/>
+      <c r="F253" s="10"/>
+      <c r="G253" s="9"/>
+    </row>
+    <row r="254" ht="13.5" customHeight="1">
+      <c r="A254" s="8"/>
+      <c r="B254" s="4"/>
+      <c r="C254" s="9"/>
+      <c r="D254" s="4"/>
+      <c r="E254" s="9"/>
+      <c r="F254" s="10"/>
+      <c r="G254" s="9"/>
+    </row>
+    <row r="255" ht="13.5" customHeight="1">
+      <c r="A255" s="8"/>
+      <c r="B255" s="4"/>
+      <c r="C255" s="9"/>
+      <c r="D255" s="4"/>
+      <c r="E255" s="9"/>
+      <c r="F255" s="10"/>
+      <c r="G255" s="9"/>
+    </row>
+    <row r="256" ht="15" customHeight="1">
+      <c r="B256" s="4"/>
+      <c r="C256"/>
+      <c r="D256" s="4"/>
+      <c r="E256"/>
+    </row>
+    <row r="257" ht="15" customHeight="1">
+      <c r="B257" s="4"/>
+      <c r="C257"/>
+      <c r="D257" s="4"/>
+      <c r="E257"/>
+    </row>
+    <row r="258" ht="15" customHeight="1">
+      <c r="D258" s="4"/>
+      <c r="E258"/>
+    </row>
+    <row r="259" ht="15" customHeight="1">
+      <c r="D259" s="4"/>
+      <c r="E259"/>
+    </row>
+    <row r="260" ht="15" customHeight="1">
+      <c r="D260" s="4"/>
+      <c r="E260"/>
+    </row>
+    <row r="261" ht="15" customHeight="1">
+      <c r="D261" s="4"/>
+      <c r="E261"/>
+    </row>
+    <row r="262" ht="15" customHeight="1">
+      <c r="D262" s="4"/>
+      <c r="E262"/>
+    </row>
+    <row r="263" ht="15" customHeight="1">
+      <c r="D263" s="4"/>
+      <c r="E263"/>
+    </row>
+    <row r="264" ht="15" customHeight="1">
+      <c r="D264" s="4"/>
+      <c r="E264"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:G246"/>

--- a/imports/Inscription.xlsx
+++ b/imports/Inscription.xlsx
@@ -787,7 +787,7 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="8">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
@@ -807,15 +807,6 @@
     </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1371,7 +1362,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" ht="13.5" customHeight="1">
+    <row r="3" ht="13.5" hidden="1" customHeight="1">
       <c r="A3" s="3">
         <v>1787</v>
       </c>
@@ -1394,7 +1385,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" ht="13.5" customHeight="1">
+    <row r="4" ht="13.5" hidden="1" customHeight="1">
       <c r="A4" s="3">
         <v>1707</v>
       </c>
@@ -1417,7 +1408,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" ht="13.5" customHeight="1">
+    <row r="5" ht="13.5" hidden="1" customHeight="1">
       <c r="A5" s="3">
         <v>1726</v>
       </c>
@@ -1440,7 +1431,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" ht="13.5" customHeight="1">
+    <row r="6" ht="13.5" hidden="1" customHeight="1">
       <c r="A6" s="3">
         <v>1727</v>
       </c>
@@ -1463,7 +1454,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" ht="13.5" customHeight="1">
+    <row r="7" ht="13.5" hidden="1" customHeight="1">
       <c r="A7" s="3">
         <v>1733</v>
       </c>
@@ -1486,7 +1477,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" ht="13.5" customHeight="1">
+    <row r="8" ht="13.5" hidden="1" customHeight="1">
       <c r="A8" s="3">
         <v>1739</v>
       </c>
@@ -1509,7 +1500,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" ht="13.5" customHeight="1">
+    <row r="9" ht="13.5" hidden="1" customHeight="1">
       <c r="A9" s="3">
         <v>1741</v>
       </c>
@@ -1532,7 +1523,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" ht="13.5" customHeight="1">
+    <row r="10" ht="13.5" hidden="1" customHeight="1">
       <c r="A10" s="3">
         <v>1773</v>
       </c>
@@ -1555,7 +1546,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" ht="13.5" customHeight="1">
+    <row r="11" ht="13.5" hidden="1" customHeight="1">
       <c r="A11" s="3">
         <v>1785</v>
       </c>
@@ -1578,7 +1569,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="12" ht="13.5" customHeight="1">
+    <row r="12" ht="13.5" hidden="1" customHeight="1">
       <c r="A12" s="3">
         <v>1796</v>
       </c>
@@ -1601,7 +1592,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="13" ht="13.5" customHeight="1">
+    <row r="13" ht="13.5" hidden="1" customHeight="1">
       <c r="A13" s="3">
         <v>1806</v>
       </c>
@@ -1624,7 +1615,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="14" ht="13.5" customHeight="1">
+    <row r="14" ht="13.5" hidden="1" customHeight="1">
       <c r="A14" s="3">
         <v>1807</v>
       </c>
@@ -1647,7 +1638,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" ht="13.5" customHeight="1">
+    <row r="15" ht="13.5" hidden="1" customHeight="1">
       <c r="A15" s="3">
         <v>1808</v>
       </c>
@@ -1670,7 +1661,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" ht="13.5" customHeight="1">
+    <row r="16" ht="13.5" hidden="1" customHeight="1">
       <c r="A16" s="3">
         <v>1809</v>
       </c>
@@ -1693,7 +1684,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="17" ht="13.5" customHeight="1">
+    <row r="17" ht="13.5" hidden="1" customHeight="1">
       <c r="A17" s="3">
         <v>1810</v>
       </c>
@@ -1716,7 +1707,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="18" ht="13.5" customHeight="1">
+    <row r="18" ht="13.5" hidden="1" customHeight="1">
       <c r="A18" s="3">
         <v>1811</v>
       </c>
@@ -1739,7 +1730,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="19" ht="13.5" customHeight="1">
+    <row r="19" ht="13.5" hidden="1" customHeight="1">
       <c r="A19" s="3">
         <v>1812</v>
       </c>
@@ -1762,7 +1753,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="20" ht="13.5" customHeight="1">
+    <row r="20" ht="13.5" hidden="1" customHeight="1">
       <c r="A20" s="6">
         <v>1813</v>
       </c>
@@ -1785,7 +1776,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="21" ht="13.5" customHeight="1">
+    <row r="21" ht="13.5" hidden="1" customHeight="1">
       <c r="A21" s="3">
         <v>1814</v>
       </c>
@@ -1808,7 +1799,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="22" ht="13.5" customHeight="1">
+    <row r="22" ht="13.5" hidden="1" customHeight="1">
       <c r="A22" s="3">
         <v>1815</v>
       </c>
@@ -1831,7 +1822,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="23" ht="13.5" customHeight="1">
+    <row r="23" ht="13.5" hidden="1" customHeight="1">
       <c r="A23" s="3">
         <v>1816</v>
       </c>
@@ -1854,7 +1845,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="24" ht="13.5" customHeight="1">
+    <row r="24" ht="13.5" hidden="1" customHeight="1">
       <c r="A24" s="3">
         <v>1817</v>
       </c>
@@ -1877,7 +1868,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="25" ht="13.5" customHeight="1">
+    <row r="25" ht="13.5" hidden="1" customHeight="1">
       <c r="A25" s="3">
         <v>1818</v>
       </c>
@@ -1900,7 +1891,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="26" ht="13.5" customHeight="1">
+    <row r="26" ht="13.5" hidden="1" customHeight="1">
       <c r="A26" s="3">
         <v>1819</v>
       </c>
@@ -1923,7 +1914,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="27" ht="13.5" customHeight="1">
+    <row r="27" ht="13.5" hidden="1" customHeight="1">
       <c r="A27" s="3">
         <v>1820</v>
       </c>
@@ -1946,7 +1937,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="28" ht="13.5" customHeight="1">
+    <row r="28" ht="13.5" hidden="1" customHeight="1">
       <c r="A28" s="3">
         <v>1821</v>
       </c>
@@ -1969,7 +1960,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="29" ht="13.5" customHeight="1">
+    <row r="29" ht="13.5" hidden="1" customHeight="1">
       <c r="A29" s="3">
         <v>1822</v>
       </c>
@@ -1992,7 +1983,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="30" ht="13.5" customHeight="1">
+    <row r="30" ht="13.5" hidden="1" customHeight="1">
       <c r="A30" s="3">
         <v>1823</v>
       </c>
@@ -2015,7 +2006,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="31" ht="13.5" customHeight="1">
+    <row r="31" ht="13.5" hidden="1" customHeight="1">
       <c r="A31" s="3">
         <v>1824</v>
       </c>
@@ -2038,7 +2029,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="32" ht="13.5" customHeight="1">
+    <row r="32" ht="13.5" hidden="1" customHeight="1">
       <c r="A32" s="3">
         <v>1825</v>
       </c>
@@ -2061,7 +2052,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="33" ht="13.5" customHeight="1">
+    <row r="33" ht="13.5" hidden="1" customHeight="1">
       <c r="A33" s="3">
         <v>1826</v>
       </c>
@@ -2084,7 +2075,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="34" ht="13.5" customHeight="1">
+    <row r="34" ht="13.5" hidden="1" customHeight="1">
       <c r="A34" s="3">
         <v>1827</v>
       </c>
@@ -2107,7 +2098,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="35" ht="13.5" customHeight="1">
+    <row r="35" ht="13.5" hidden="1" customHeight="1">
       <c r="A35" s="3">
         <v>1828</v>
       </c>
@@ -2130,7 +2121,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="36" ht="13.5" customHeight="1">
+    <row r="36" ht="13.5" hidden="1" customHeight="1">
       <c r="A36" s="3">
         <v>1829</v>
       </c>
@@ -2153,7 +2144,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="37" ht="13.5" customHeight="1">
+    <row r="37" ht="13.5" hidden="1" customHeight="1">
       <c r="A37" s="3">
         <v>1830</v>
       </c>
@@ -2176,7 +2167,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="38" ht="13.5" customHeight="1">
+    <row r="38" ht="13.5" hidden="1" customHeight="1">
       <c r="A38" s="3">
         <v>1831</v>
       </c>
@@ -2199,7 +2190,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="39" ht="13.5" customHeight="1">
+    <row r="39" ht="13.5" hidden="1" customHeight="1">
       <c r="A39" s="3">
         <v>1832</v>
       </c>
@@ -2222,7 +2213,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="40" ht="13.5" customHeight="1">
+    <row r="40" ht="13.5" hidden="1" customHeight="1">
       <c r="A40" s="3">
         <v>1833</v>
       </c>
@@ -2245,7 +2236,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="41" ht="13.5" customHeight="1">
+    <row r="41" ht="13.5" hidden="1" customHeight="1">
       <c r="A41" s="3">
         <v>1834</v>
       </c>
@@ -2268,7 +2259,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="42" ht="13.5" customHeight="1">
+    <row r="42" ht="13.5" hidden="1" customHeight="1">
       <c r="A42" s="3">
         <v>1835</v>
       </c>
@@ -2291,7 +2282,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="43" ht="13.5" customHeight="1">
+    <row r="43" ht="13.5" hidden="1" customHeight="1">
       <c r="A43" s="3">
         <v>1836</v>
       </c>
@@ -2314,7 +2305,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="44" ht="13.5" customHeight="1">
+    <row r="44" ht="13.5" hidden="1" customHeight="1">
       <c r="A44" s="3">
         <v>1837</v>
       </c>
@@ -2337,7 +2328,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="45" ht="13.5" customHeight="1">
+    <row r="45" ht="13.5" hidden="1" customHeight="1">
       <c r="A45" s="3">
         <v>1838</v>
       </c>
@@ -2360,7 +2351,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="46" ht="13.5" customHeight="1">
+    <row r="46" ht="13.5" hidden="1" customHeight="1">
       <c r="A46" s="3">
         <v>1839</v>
       </c>
@@ -2383,7 +2374,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="47" ht="13.5" customHeight="1">
+    <row r="47" ht="13.5" hidden="1" customHeight="1">
       <c r="A47" s="3">
         <v>1840</v>
       </c>
@@ -2406,7 +2397,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="48" ht="13.5" customHeight="1">
+    <row r="48" ht="13.5" hidden="1" customHeight="1">
       <c r="A48" s="3">
         <v>1841</v>
       </c>
@@ -2429,7 +2420,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="49" ht="13.5" customHeight="1">
+    <row r="49" ht="13.5" hidden="1" customHeight="1">
       <c r="A49" s="3">
         <v>1842</v>
       </c>
@@ -2452,7 +2443,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="50" ht="13.5" customHeight="1">
+    <row r="50" ht="13.5" hidden="1" customHeight="1">
       <c r="A50" s="3">
         <v>1843</v>
       </c>
@@ -2475,7 +2466,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="51" ht="13.5" customHeight="1">
+    <row r="51" ht="13.5" hidden="1" customHeight="1">
       <c r="A51" s="3">
         <v>1844</v>
       </c>
@@ -2498,7 +2489,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="52" ht="13.5" customHeight="1">
+    <row r="52" ht="13.5" hidden="1" customHeight="1">
       <c r="A52" s="3">
         <v>1845</v>
       </c>
@@ -2521,7 +2512,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="53" ht="13.5" customHeight="1">
+    <row r="53" ht="13.5" hidden="1" customHeight="1">
       <c r="A53" s="3">
         <v>1846</v>
       </c>
@@ -2544,7 +2535,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="54" ht="13.5" customHeight="1">
+    <row r="54" ht="13.5" hidden="1" customHeight="1">
       <c r="A54" s="3">
         <v>1847</v>
       </c>
@@ -2567,7 +2558,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="55" ht="13.5" customHeight="1">
+    <row r="55" ht="13.5" hidden="1" customHeight="1">
       <c r="A55" s="3">
         <v>1848</v>
       </c>
@@ -2590,7 +2581,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="56" ht="13.5" customHeight="1">
+    <row r="56" ht="13.5" hidden="1" customHeight="1">
       <c r="A56" s="3">
         <v>1849</v>
       </c>
@@ -2613,7 +2604,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="57" ht="13.5" customHeight="1">
+    <row r="57" ht="13.5" hidden="1" customHeight="1">
       <c r="A57" s="3">
         <v>1850</v>
       </c>
@@ -2636,7 +2627,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="58" ht="13.5" customHeight="1">
+    <row r="58" ht="13.5" hidden="1" customHeight="1">
       <c r="A58" s="3">
         <v>1851</v>
       </c>
@@ -2659,7 +2650,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="59" ht="13.5" customHeight="1">
+    <row r="59" ht="13.5" hidden="1" customHeight="1">
       <c r="A59" s="3">
         <v>1852</v>
       </c>
@@ -2682,7 +2673,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="60" ht="13.5" customHeight="1">
+    <row r="60" ht="13.5" hidden="1" customHeight="1">
       <c r="A60" s="3">
         <v>1853</v>
       </c>
@@ -2705,7 +2696,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="61" ht="13.5" customHeight="1">
+    <row r="61" ht="13.5" hidden="1" customHeight="1">
       <c r="A61" s="3">
         <v>1854</v>
       </c>
@@ -2728,7 +2719,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="62" ht="13.5" customHeight="1">
+    <row r="62" ht="13.5" hidden="1" customHeight="1">
       <c r="A62" s="3">
         <v>1855</v>
       </c>
@@ -2751,7 +2742,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="63" ht="13.5" customHeight="1">
+    <row r="63" ht="13.5" hidden="1" customHeight="1">
       <c r="A63" s="3">
         <v>1856</v>
       </c>
@@ -2774,7 +2765,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="64" ht="13.5" customHeight="1">
+    <row r="64" ht="13.5" hidden="1" customHeight="1">
       <c r="A64" s="3">
         <v>1857</v>
       </c>
@@ -2797,7 +2788,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="65" ht="13.5" customHeight="1">
+    <row r="65" ht="13.5" hidden="1" customHeight="1">
       <c r="A65" s="3">
         <v>1858</v>
       </c>
@@ -2820,7 +2811,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="66" ht="13.5" customHeight="1">
+    <row r="66" ht="13.5" hidden="1" customHeight="1">
       <c r="A66" s="3">
         <v>1859</v>
       </c>
@@ -2843,7 +2834,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="67" ht="13.5" customHeight="1">
+    <row r="67" ht="13.5" hidden="1" customHeight="1">
       <c r="A67" s="3">
         <v>1860</v>
       </c>
@@ -2866,7 +2857,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="68" ht="13.5" customHeight="1">
+    <row r="68" ht="13.5" hidden="1" customHeight="1">
       <c r="A68" s="3">
         <v>1861</v>
       </c>
@@ -2889,7 +2880,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="69" ht="13.5" customHeight="1">
+    <row r="69" ht="13.5" hidden="1" customHeight="1">
       <c r="A69" s="3">
         <v>1862</v>
       </c>
@@ -2912,7 +2903,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="70" ht="13.5" customHeight="1">
+    <row r="70" ht="13.5" hidden="1" customHeight="1">
       <c r="A70" s="3">
         <v>1863</v>
       </c>
@@ -2935,7 +2926,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="71" ht="13.5" customHeight="1">
+    <row r="71" ht="13.5" hidden="1" customHeight="1">
       <c r="A71" s="3">
         <v>1864</v>
       </c>
@@ -2958,7 +2949,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="72" ht="13.5" customHeight="1">
+    <row r="72" ht="13.5" hidden="1" customHeight="1">
       <c r="A72" s="3">
         <v>1865</v>
       </c>
@@ -2981,7 +2972,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="73" ht="13.5" customHeight="1">
+    <row r="73" ht="13.5" hidden="1" customHeight="1">
       <c r="A73" s="3">
         <v>2028</v>
       </c>
@@ -3004,7 +2995,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="74" ht="13.5" customHeight="1">
+    <row r="74" ht="13.5" hidden="1" customHeight="1">
       <c r="A74" s="3">
         <v>1867</v>
       </c>
@@ -3027,7 +3018,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="75" ht="13.5" customHeight="1">
+    <row r="75" ht="13.5" hidden="1" customHeight="1">
       <c r="A75" s="3">
         <v>1868</v>
       </c>
@@ -3050,7 +3041,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="76" ht="13.5" customHeight="1">
+    <row r="76" ht="13.5" hidden="1" customHeight="1">
       <c r="A76" s="3">
         <v>1869</v>
       </c>
@@ -3073,7 +3064,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="77" ht="13.5" customHeight="1">
+    <row r="77" ht="13.5" hidden="1" customHeight="1">
       <c r="A77" s="3">
         <v>1870</v>
       </c>
@@ -3096,7 +3087,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="78" ht="13.5" customHeight="1">
+    <row r="78" ht="13.5" hidden="1" customHeight="1">
       <c r="A78" s="3">
         <v>1871</v>
       </c>
@@ -3119,7 +3110,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="79" ht="13.5" customHeight="1">
+    <row r="79" ht="13.5" hidden="1" customHeight="1">
       <c r="A79" s="3">
         <v>1872</v>
       </c>
@@ -3142,7 +3133,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="80" ht="13.5" customHeight="1">
+    <row r="80" ht="13.5" hidden="1" customHeight="1">
       <c r="A80" s="3">
         <v>1873</v>
       </c>
@@ -3165,7 +3156,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="81" ht="13.5" customHeight="1">
+    <row r="81" ht="13.5" hidden="1" customHeight="1">
       <c r="A81" s="3">
         <v>1874</v>
       </c>
@@ -3188,7 +3179,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="82" ht="13.5" customHeight="1">
+    <row r="82" ht="13.5" hidden="1" customHeight="1">
       <c r="A82" s="3">
         <v>1875</v>
       </c>
@@ -3211,7 +3202,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="83" ht="13.5" customHeight="1">
+    <row r="83" ht="13.5" hidden="1" customHeight="1">
       <c r="A83" s="3">
         <v>1877</v>
       </c>
@@ -3234,7 +3225,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="84" ht="13.5" customHeight="1">
+    <row r="84" ht="13.5" hidden="1" customHeight="1">
       <c r="A84" s="3">
         <v>1878</v>
       </c>
@@ -3257,7 +3248,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="85" ht="13.5" customHeight="1">
+    <row r="85" ht="13.5" hidden="1" customHeight="1">
       <c r="A85" s="3">
         <v>1879</v>
       </c>
@@ -3280,7 +3271,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="86" ht="13.5" customHeight="1">
+    <row r="86" ht="13.5" hidden="1" customHeight="1">
       <c r="A86" s="3">
         <v>1880</v>
       </c>
@@ -3303,7 +3294,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="87" ht="13.5" customHeight="1">
+    <row r="87" ht="13.5" hidden="1" customHeight="1">
       <c r="A87" s="3">
         <v>1881</v>
       </c>
@@ -3326,7 +3317,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="88" ht="13.5" customHeight="1">
+    <row r="88" ht="13.5" hidden="1" customHeight="1">
       <c r="A88" s="3">
         <v>1882</v>
       </c>
@@ -3349,7 +3340,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="89" ht="13.5" customHeight="1">
+    <row r="89" ht="13.5" hidden="1" customHeight="1">
       <c r="A89" s="3">
         <v>1883</v>
       </c>
@@ -3372,7 +3363,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="90" ht="13.5" customHeight="1">
+    <row r="90" ht="13.5" hidden="1" customHeight="1">
       <c r="A90" s="3">
         <v>1884</v>
       </c>
@@ -3395,7 +3386,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="91" ht="13.5" customHeight="1">
+    <row r="91" ht="13.5" hidden="1" customHeight="1">
       <c r="A91" s="3">
         <v>1885</v>
       </c>
@@ -3418,7 +3409,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="92" ht="13.5" customHeight="1">
+    <row r="92" ht="13.5" hidden="1" customHeight="1">
       <c r="A92" s="3">
         <v>1886</v>
       </c>
@@ -3441,7 +3432,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="93" ht="13.5" customHeight="1">
+    <row r="93" ht="13.5" hidden="1" customHeight="1">
       <c r="A93" s="3">
         <v>1887</v>
       </c>
@@ -3464,7 +3455,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="94" ht="13.5" customHeight="1">
+    <row r="94" ht="13.5" hidden="1" customHeight="1">
       <c r="A94" s="3">
         <v>1888</v>
       </c>
@@ -3487,7 +3478,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="95" ht="13.5" customHeight="1">
+    <row r="95" ht="13.5" hidden="1" customHeight="1">
       <c r="A95" s="3">
         <v>1889</v>
       </c>
@@ -3510,7 +3501,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="96" ht="13.5" customHeight="1">
+    <row r="96" ht="13.5" hidden="1" customHeight="1">
       <c r="A96" s="3">
         <v>1890</v>
       </c>
@@ -3533,7 +3524,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="97" ht="13.5" customHeight="1">
+    <row r="97" ht="13.5" hidden="1" customHeight="1">
       <c r="A97" s="3">
         <v>1891</v>
       </c>
@@ -3556,7 +3547,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="98" ht="13.5" customHeight="1">
+    <row r="98" ht="13.5" hidden="1" customHeight="1">
       <c r="A98" s="3">
         <v>1892</v>
       </c>
@@ -3579,7 +3570,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="99" ht="13.5" customHeight="1">
+    <row r="99" ht="13.5" hidden="1" customHeight="1">
       <c r="A99" s="3">
         <v>1893</v>
       </c>
@@ -3602,7 +3593,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="100" ht="13.5" customHeight="1">
+    <row r="100" ht="13.5" hidden="1" customHeight="1">
       <c r="A100" s="3">
         <v>1894</v>
       </c>
@@ -3625,7 +3616,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="101" ht="13.5" customHeight="1">
+    <row r="101" ht="13.5" hidden="1" customHeight="1">
       <c r="A101" s="3">
         <v>1895</v>
       </c>
@@ -3648,7 +3639,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="102" ht="13.5" customHeight="1">
+    <row r="102" ht="13.5" hidden="1" customHeight="1">
       <c r="A102" s="3">
         <v>1896</v>
       </c>
@@ -3671,7 +3662,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="103" ht="13.5" customHeight="1">
+    <row r="103" ht="13.5" hidden="1" customHeight="1">
       <c r="A103" s="3">
         <v>1897</v>
       </c>
@@ -3694,7 +3685,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="104" ht="13.5" customHeight="1">
+    <row r="104" ht="13.5" hidden="1" customHeight="1">
       <c r="A104" s="3">
         <v>1898</v>
       </c>
@@ -3717,7 +3708,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="105" ht="13.5" customHeight="1">
+    <row r="105" ht="13.5" hidden="1" customHeight="1">
       <c r="A105" s="3">
         <v>1899</v>
       </c>
@@ -3740,7 +3731,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="106" ht="13.5" customHeight="1">
+    <row r="106" ht="13.5" hidden="1" customHeight="1">
       <c r="A106" s="3">
         <v>1900</v>
       </c>
@@ -3763,7 +3754,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="107" ht="13.5" customHeight="1">
+    <row r="107" ht="13.5" hidden="1" customHeight="1">
       <c r="A107" s="3">
         <v>1901</v>
       </c>
@@ -3786,7 +3777,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="108" ht="13.5" customHeight="1">
+    <row r="108" ht="13.5" hidden="1" customHeight="1">
       <c r="A108" s="3">
         <v>1902</v>
       </c>
@@ -3809,7 +3800,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="109" ht="13.5" customHeight="1">
+    <row r="109" ht="13.5" hidden="1" customHeight="1">
       <c r="A109" s="3">
         <v>1903</v>
       </c>
@@ -3832,7 +3823,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="110" ht="13.5" customHeight="1">
+    <row r="110" ht="13.5" hidden="1" customHeight="1">
       <c r="A110" s="3">
         <v>1904</v>
       </c>
@@ -3855,7 +3846,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="111" ht="13.5" customHeight="1">
+    <row r="111" ht="13.5" hidden="1" customHeight="1">
       <c r="A111" s="3">
         <v>1905</v>
       </c>
@@ -3878,7 +3869,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="112" ht="13.5" customHeight="1">
+    <row r="112" ht="13.5" hidden="1" customHeight="1">
       <c r="A112" s="3">
         <v>1906</v>
       </c>
@@ -3901,7 +3892,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="113" ht="13.5" customHeight="1">
+    <row r="113" ht="13.5" hidden="1" customHeight="1">
       <c r="A113" s="3">
         <v>1907</v>
       </c>
@@ -3924,7 +3915,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="114" ht="13.5" customHeight="1">
+    <row r="114" ht="13.5" hidden="1" customHeight="1">
       <c r="A114" s="3">
         <v>1908</v>
       </c>
@@ -3947,7 +3938,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="115" ht="13.5" customHeight="1">
+    <row r="115" ht="13.5" hidden="1" customHeight="1">
       <c r="A115" s="3">
         <v>1909</v>
       </c>
@@ -3970,7 +3961,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="116" ht="13.5" customHeight="1">
+    <row r="116" ht="13.5" hidden="1" customHeight="1">
       <c r="A116" s="3">
         <v>1910</v>
       </c>
@@ -3993,7 +3984,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="117" ht="13.5" customHeight="1">
+    <row r="117" ht="13.5" hidden="1" customHeight="1">
       <c r="A117" s="3">
         <v>1911</v>
       </c>
@@ -4016,7 +4007,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="118" ht="13.5" customHeight="1">
+    <row r="118" ht="13.5" hidden="1" customHeight="1">
       <c r="A118" s="3">
         <v>1912</v>
       </c>
@@ -4039,7 +4030,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="119" ht="13.5" customHeight="1">
+    <row r="119" ht="13.5" hidden="1" customHeight="1">
       <c r="A119" s="3">
         <v>1913</v>
       </c>
@@ -4062,7 +4053,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="120" ht="13.5" customHeight="1">
+    <row r="120" ht="13.5" hidden="1" customHeight="1">
       <c r="A120" s="3">
         <v>1914</v>
       </c>
@@ -4085,7 +4076,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="121" ht="13.5" customHeight="1">
+    <row r="121" ht="13.5" hidden="1" customHeight="1">
       <c r="A121" s="3">
         <v>1915</v>
       </c>
@@ -4108,7 +4099,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="122" ht="13.5" customHeight="1">
+    <row r="122" ht="13.5" hidden="1" customHeight="1">
       <c r="A122" s="3">
         <v>1916</v>
       </c>
@@ -4131,7 +4122,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="123" ht="13.5" customHeight="1">
+    <row r="123" ht="13.5" hidden="1" customHeight="1">
       <c r="A123" s="3">
         <v>1917</v>
       </c>
@@ -4154,7 +4145,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="124" ht="13.5" customHeight="1">
+    <row r="124" ht="13.5" hidden="1" customHeight="1">
       <c r="A124" s="3">
         <v>1918</v>
       </c>
@@ -4177,7 +4168,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="125" ht="13.5" customHeight="1">
+    <row r="125" ht="13.5" hidden="1" customHeight="1">
       <c r="A125" s="3">
         <v>1919</v>
       </c>
@@ -4200,7 +4191,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="126" ht="13.5" customHeight="1">
+    <row r="126" ht="13.5" hidden="1" customHeight="1">
       <c r="A126" s="3">
         <v>1920</v>
       </c>
@@ -4223,7 +4214,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="127" ht="13.5" customHeight="1">
+    <row r="127" ht="13.5" hidden="1" customHeight="1">
       <c r="A127" s="3">
         <v>1921</v>
       </c>
@@ -4246,7 +4237,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="128" ht="13.5" customHeight="1">
+    <row r="128" ht="13.5" hidden="1" customHeight="1">
       <c r="A128" s="3">
         <v>2010</v>
       </c>
@@ -4269,7 +4260,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="129" ht="13.5" customHeight="1">
+    <row r="129" ht="13.5" hidden="1" customHeight="1">
       <c r="A129" s="3">
         <v>1923</v>
       </c>
@@ -4292,7 +4283,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="130" ht="13.5" customHeight="1">
+    <row r="130" ht="13.5" hidden="1" customHeight="1">
       <c r="A130" s="3">
         <v>1924</v>
       </c>
@@ -4315,7 +4306,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="131" ht="13.5" customHeight="1">
+    <row r="131" ht="13.5" hidden="1" customHeight="1">
       <c r="A131" s="3">
         <v>1925</v>
       </c>
@@ -4338,7 +4329,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="132" ht="13.5" customHeight="1">
+    <row r="132" ht="13.5" hidden="1" customHeight="1">
       <c r="A132" s="3">
         <v>1926</v>
       </c>
@@ -4361,7 +4352,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="133" ht="13.5" customHeight="1">
+    <row r="133" ht="13.5" hidden="1" customHeight="1">
       <c r="A133" s="3">
         <v>1927</v>
       </c>
@@ -4384,7 +4375,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="134" ht="13.5" customHeight="1">
+    <row r="134" ht="13.5" hidden="1" customHeight="1">
       <c r="A134" s="3">
         <v>1928</v>
       </c>
@@ -4407,7 +4398,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="135" ht="13.5" customHeight="1">
+    <row r="135" ht="13.5" hidden="1" customHeight="1">
       <c r="A135" s="3">
         <v>1929</v>
       </c>
@@ -4430,7 +4421,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="136" ht="13.5" customHeight="1">
+    <row r="136" ht="13.5" hidden="1" customHeight="1">
       <c r="A136" s="3">
         <v>1930</v>
       </c>
@@ -4453,7 +4444,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="137" ht="13.5" customHeight="1">
+    <row r="137" ht="13.5" hidden="1" customHeight="1">
       <c r="A137" s="3">
         <v>1931</v>
       </c>
@@ -4476,7 +4467,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="138" ht="13.5" customHeight="1">
+    <row r="138" ht="13.5" hidden="1" customHeight="1">
       <c r="A138" s="3">
         <v>1932</v>
       </c>
@@ -4499,7 +4490,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="139" ht="13.5" customHeight="1">
+    <row r="139" ht="13.5" hidden="1" customHeight="1">
       <c r="A139" s="3">
         <v>1933</v>
       </c>
@@ -4522,7 +4513,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="140" ht="13.5" customHeight="1">
+    <row r="140" ht="13.5" hidden="1" customHeight="1">
       <c r="A140" s="3">
         <v>1934</v>
       </c>
@@ -4545,7 +4536,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="141" ht="13.5" customHeight="1">
+    <row r="141" ht="13.5" hidden="1" customHeight="1">
       <c r="A141" s="3">
         <v>1935</v>
       </c>
@@ -4568,7 +4559,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="142" ht="13.5" customHeight="1">
+    <row r="142" ht="13.5" hidden="1" customHeight="1">
       <c r="A142" s="3">
         <v>1936</v>
       </c>
@@ -4591,7 +4582,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="143" ht="13.5" customHeight="1">
+    <row r="143" ht="13.5" hidden="1" customHeight="1">
       <c r="A143" s="3">
         <v>1937</v>
       </c>
@@ -4614,7 +4605,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="144" ht="13.5" customHeight="1">
+    <row r="144" ht="13.5" hidden="1" customHeight="1">
       <c r="A144" s="3">
         <v>1938</v>
       </c>
@@ -4637,7 +4628,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="145" ht="13.5" customHeight="1">
+    <row r="145" ht="13.5" hidden="1" customHeight="1">
       <c r="A145" s="3">
         <v>1939</v>
       </c>
@@ -4660,7 +4651,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="146" ht="13.5" customHeight="1">
+    <row r="146" ht="13.5" hidden="1" customHeight="1">
       <c r="A146" s="3">
         <v>1940</v>
       </c>
@@ -4683,7 +4674,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="147" ht="13.5" customHeight="1">
+    <row r="147" ht="13.5" hidden="1" customHeight="1">
       <c r="A147" s="3">
         <v>1941</v>
       </c>
@@ -4706,7 +4697,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="148" ht="13.5" customHeight="1">
+    <row r="148" ht="13.5" hidden="1" customHeight="1">
       <c r="A148" s="3">
         <v>1942</v>
       </c>
@@ -4729,7 +4720,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="149" ht="13.5" customHeight="1">
+    <row r="149" ht="13.5" hidden="1" customHeight="1">
       <c r="A149" s="3">
         <v>1943</v>
       </c>
@@ -4752,7 +4743,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="150" ht="13.5" customHeight="1">
+    <row r="150" ht="13.5" hidden="1" customHeight="1">
       <c r="A150" s="3">
         <v>1944</v>
       </c>
@@ -4775,7 +4766,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="151" ht="13.5" customHeight="1">
+    <row r="151" ht="13.5" hidden="1" customHeight="1">
       <c r="A151" s="3">
         <v>1945</v>
       </c>
@@ -4798,7 +4789,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="152" ht="13.5" customHeight="1">
+    <row r="152" ht="13.5" hidden="1" customHeight="1">
       <c r="A152" s="3">
         <v>1946</v>
       </c>
@@ -4821,7 +4812,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="153" ht="13.5" customHeight="1">
+    <row r="153" ht="13.5" hidden="1" customHeight="1">
       <c r="A153" s="3">
         <v>1947</v>
       </c>
@@ -4844,7 +4835,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="154" ht="13.5" customHeight="1">
+    <row r="154" ht="13.5" hidden="1" customHeight="1">
       <c r="A154" s="3">
         <v>1948</v>
       </c>
@@ -4867,7 +4858,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="155" ht="13.5" customHeight="1">
+    <row r="155" ht="13.5" hidden="1" customHeight="1">
       <c r="A155" s="3">
         <v>1949</v>
       </c>
@@ -4890,7 +4881,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="156" ht="13.5" customHeight="1">
+    <row r="156" ht="13.5" hidden="1" customHeight="1">
       <c r="A156" s="3">
         <v>1950</v>
       </c>
@@ -4913,7 +4904,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="157" ht="13.5" customHeight="1">
+    <row r="157" ht="13.5" hidden="1" customHeight="1">
       <c r="A157" s="3">
         <v>1951</v>
       </c>
@@ -4936,7 +4927,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="158" ht="13.5" customHeight="1">
+    <row r="158" ht="13.5" hidden="1" customHeight="1">
       <c r="A158" s="3">
         <v>1952</v>
       </c>
@@ -4959,7 +4950,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="159" ht="13.5" customHeight="1">
+    <row r="159" ht="13.5" hidden="1" customHeight="1">
       <c r="A159" s="3">
         <v>1953</v>
       </c>
@@ -4982,7 +4973,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="160" ht="13.5" customHeight="1">
+    <row r="160" ht="13.5" hidden="1" customHeight="1">
       <c r="A160" s="3">
         <v>1954</v>
       </c>
@@ -5005,7 +4996,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="161" ht="13.5" customHeight="1">
+    <row r="161" ht="13.5" hidden="1" customHeight="1">
       <c r="A161" s="3">
         <v>1955</v>
       </c>
@@ -5028,7 +5019,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="162" ht="13.5" customHeight="1">
+    <row r="162" ht="13.5" hidden="1" customHeight="1">
       <c r="A162" s="3">
         <v>1956</v>
       </c>
@@ -5051,7 +5042,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="163" ht="13.5" customHeight="1">
+    <row r="163" ht="13.5" hidden="1" customHeight="1">
       <c r="A163" s="3">
         <v>1957</v>
       </c>
@@ -5074,7 +5065,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="164" ht="13.5" customHeight="1">
+    <row r="164" ht="13.5" hidden="1" customHeight="1">
       <c r="A164" s="3">
         <v>1958</v>
       </c>
@@ -5097,7 +5088,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="165" ht="13.5" customHeight="1">
+    <row r="165" ht="13.5" hidden="1" customHeight="1">
       <c r="A165" s="3">
         <v>1959</v>
       </c>
@@ -5120,7 +5111,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="166" ht="13.5" customHeight="1">
+    <row r="166" ht="13.5" hidden="1" customHeight="1">
       <c r="A166" s="3">
         <v>1960</v>
       </c>
@@ -5143,7 +5134,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="167" ht="13.5" customHeight="1">
+    <row r="167" ht="13.5" hidden="1" customHeight="1">
       <c r="A167" s="3">
         <v>1961</v>
       </c>
@@ -5166,7 +5157,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="168" ht="13.5" customHeight="1">
+    <row r="168" ht="13.5" hidden="1" customHeight="1">
       <c r="A168" s="3">
         <v>1962</v>
       </c>
@@ -5189,7 +5180,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="169" ht="13.5" customHeight="1">
+    <row r="169" ht="13.5" hidden="1" customHeight="1">
       <c r="A169" s="3">
         <v>1963</v>
       </c>
@@ -5212,7 +5203,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="170" ht="13.5" customHeight="1">
+    <row r="170" ht="13.5" hidden="1" customHeight="1">
       <c r="A170" s="3">
         <v>1964</v>
       </c>
@@ -5235,7 +5226,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="171" ht="13.5" customHeight="1">
+    <row r="171" ht="13.5" hidden="1" customHeight="1">
       <c r="A171" s="3">
         <v>1965</v>
       </c>
@@ -5258,7 +5249,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="172" ht="13.5" customHeight="1">
+    <row r="172" ht="13.5" hidden="1" customHeight="1">
       <c r="A172" s="3">
         <v>1966</v>
       </c>
@@ -5281,7 +5272,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="173" ht="13.5" customHeight="1">
+    <row r="173" ht="13.5" hidden="1" customHeight="1">
       <c r="A173" s="3">
         <v>1967</v>
       </c>
@@ -5304,7 +5295,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="174" ht="13.5" customHeight="1">
+    <row r="174" ht="13.5" hidden="1" customHeight="1">
       <c r="A174" s="3">
         <v>1968</v>
       </c>
@@ -5327,7 +5318,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="175" ht="13.5" customHeight="1">
+    <row r="175" ht="13.5" hidden="1" customHeight="1">
       <c r="A175" s="3">
         <v>1969</v>
       </c>
@@ -5350,7 +5341,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="176" ht="13.5" customHeight="1">
+    <row r="176" ht="13.5" hidden="1" customHeight="1">
       <c r="A176" s="3">
         <v>1970</v>
       </c>
@@ -5373,7 +5364,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="177" ht="13.5" customHeight="1">
+    <row r="177" ht="13.5" hidden="1" customHeight="1">
       <c r="A177" s="3">
         <v>1971</v>
       </c>
@@ -5396,7 +5387,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="178" ht="13.5" customHeight="1">
+    <row r="178" ht="13.5" hidden="1" customHeight="1">
       <c r="A178" s="3">
         <v>1972</v>
       </c>
@@ -5419,7 +5410,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="179" ht="13.5" customHeight="1">
+    <row r="179" ht="13.5" hidden="1" customHeight="1">
       <c r="A179" s="3">
         <v>1973</v>
       </c>
@@ -5442,7 +5433,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="180" ht="13.5" customHeight="1">
+    <row r="180" ht="13.5" hidden="1" customHeight="1">
       <c r="A180" s="3">
         <v>1974</v>
       </c>
@@ -5465,7 +5456,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="181" ht="13.5" customHeight="1">
+    <row r="181" ht="13.5" hidden="1" customHeight="1">
       <c r="A181" s="3">
         <v>1975</v>
       </c>
@@ -5488,7 +5479,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="182" ht="13.5" customHeight="1">
+    <row r="182" ht="13.5" hidden="1" customHeight="1">
       <c r="A182" s="3">
         <v>1976</v>
       </c>
@@ -5511,7 +5502,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="183" ht="13.5" customHeight="1">
+    <row r="183" ht="13.5" hidden="1" customHeight="1">
       <c r="A183" s="3">
         <v>1977</v>
       </c>
@@ -5534,7 +5525,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="184" ht="13.5" customHeight="1">
+    <row r="184" ht="13.5" hidden="1" customHeight="1">
       <c r="A184" s="3">
         <v>1978</v>
       </c>
@@ -5557,7 +5548,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="185" ht="13.5" customHeight="1">
+    <row r="185" ht="13.5" hidden="1" customHeight="1">
       <c r="A185" s="3">
         <v>1979</v>
       </c>
@@ -5580,7 +5571,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="186" ht="13.5" customHeight="1">
+    <row r="186" ht="13.5" hidden="1" customHeight="1">
       <c r="A186" s="3">
         <v>1980</v>
       </c>
@@ -5603,7 +5594,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="187" ht="13.5" customHeight="1">
+    <row r="187" ht="13.5" hidden="1" customHeight="1">
       <c r="A187" s="3">
         <v>1981</v>
       </c>
@@ -5626,7 +5617,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="188" ht="13.5" customHeight="1">
+    <row r="188" ht="13.5" hidden="1" customHeight="1">
       <c r="A188" s="3">
         <v>1982</v>
       </c>
@@ -5649,7 +5640,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="189" ht="13.5" customHeight="1">
+    <row r="189" ht="13.5" hidden="1" customHeight="1">
       <c r="A189" s="3">
         <v>1983</v>
       </c>
@@ -5672,7 +5663,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="190" ht="13.5" customHeight="1">
+    <row r="190" ht="13.5" hidden="1" customHeight="1">
       <c r="A190" s="3">
         <v>1984</v>
       </c>
@@ -5695,7 +5686,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="191" ht="13.5" customHeight="1">
+    <row r="191" ht="13.5" hidden="1" customHeight="1">
       <c r="A191" s="3">
         <v>1985</v>
       </c>
@@ -5718,7 +5709,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="192" ht="13.5" customHeight="1">
+    <row r="192" ht="13.5" hidden="1" customHeight="1">
       <c r="A192" s="3">
         <v>1986</v>
       </c>
@@ -5741,7 +5732,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="193" ht="13.5" customHeight="1">
+    <row r="193" ht="13.5" hidden="1" customHeight="1">
       <c r="A193" s="3">
         <v>1987</v>
       </c>
@@ -5764,7 +5755,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="194" ht="13.5" customHeight="1">
+    <row r="194" ht="13.5" hidden="1" customHeight="1">
       <c r="A194" s="3">
         <v>1988</v>
       </c>
@@ -5787,7 +5778,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="195" ht="13.5" customHeight="1">
+    <row r="195" ht="13.5" hidden="1" customHeight="1">
       <c r="A195" s="3">
         <v>1989</v>
       </c>
@@ -5810,7 +5801,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="196" ht="13.5" customHeight="1">
+    <row r="196" ht="13.5" hidden="1" customHeight="1">
       <c r="A196" s="3">
         <v>1990</v>
       </c>
@@ -5833,7 +5824,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="197" ht="13.5" customHeight="1">
+    <row r="197" ht="13.5" hidden="1" customHeight="1">
       <c r="A197" s="3">
         <v>1991</v>
       </c>
@@ -5856,7 +5847,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="198" ht="13.5" customHeight="1">
+    <row r="198" ht="13.5" hidden="1" customHeight="1">
       <c r="A198" s="3">
         <v>1992</v>
       </c>
@@ -5879,7 +5870,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="199" ht="13.5" customHeight="1">
+    <row r="199" ht="13.5" hidden="1" customHeight="1">
       <c r="A199" s="3">
         <v>1993</v>
       </c>
@@ -5902,7 +5893,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="200" ht="13.5" customHeight="1">
+    <row r="200" ht="13.5" hidden="1" customHeight="1">
       <c r="A200" s="3">
         <v>1994</v>
       </c>
@@ -5925,7 +5916,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="201" ht="13.5" customHeight="1">
+    <row r="201" ht="13.5" hidden="1" customHeight="1">
       <c r="A201" s="3">
         <v>1995</v>
       </c>
@@ -5948,7 +5939,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="202" ht="13.5" customHeight="1">
+    <row r="202" ht="13.5" hidden="1" customHeight="1">
       <c r="A202" s="3">
         <v>1996</v>
       </c>
@@ -5971,7 +5962,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="203" ht="13.5" customHeight="1">
+    <row r="203" ht="13.5" hidden="1" customHeight="1">
       <c r="A203" s="3">
         <v>1997</v>
       </c>
@@ -5994,7 +5985,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="204" ht="13.5" customHeight="1">
+    <row r="204" ht="13.5" hidden="1" customHeight="1">
       <c r="A204" s="3">
         <v>1998</v>
       </c>
@@ -6017,7 +6008,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="205" ht="13.5" customHeight="1">
+    <row r="205" ht="13.5" hidden="1" customHeight="1">
       <c r="A205" s="3">
         <v>1999</v>
       </c>
@@ -6040,7 +6031,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="206" ht="13.5" customHeight="1">
+    <row r="206" ht="13.5" hidden="1" customHeight="1">
       <c r="A206" s="3">
         <v>2000</v>
       </c>
@@ -6063,7 +6054,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="207" ht="13.5" customHeight="1">
+    <row r="207" ht="13.5" hidden="1" customHeight="1">
       <c r="A207" s="3">
         <v>2001</v>
       </c>
@@ -6086,7 +6077,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="208" ht="13.5" customHeight="1">
+    <row r="208" ht="13.5" hidden="1" customHeight="1">
       <c r="A208" s="3">
         <v>2002</v>
       </c>
@@ -6109,7 +6100,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="209" ht="13.5" customHeight="1">
+    <row r="209" ht="13.5" hidden="1" customHeight="1">
       <c r="A209" s="3">
         <v>2003</v>
       </c>
@@ -6132,7 +6123,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="210" ht="13.5" customHeight="1">
+    <row r="210" ht="13.5" hidden="1" customHeight="1">
       <c r="A210" s="3">
         <v>2004</v>
       </c>
@@ -6155,7 +6146,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="211" ht="13.5" customHeight="1">
+    <row r="211" ht="13.5" hidden="1" customHeight="1">
       <c r="A211" s="3">
         <v>2005</v>
       </c>
@@ -6178,7 +6169,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="212" ht="13.5" customHeight="1">
+    <row r="212" ht="13.5" hidden="1" customHeight="1">
       <c r="A212" s="3">
         <v>2006</v>
       </c>
@@ -6201,7 +6192,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="213" ht="13.5" customHeight="1">
+    <row r="213" ht="13.5" hidden="1" customHeight="1">
       <c r="A213" s="3">
         <v>2007</v>
       </c>
@@ -6224,7 +6215,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="214" ht="13.5" customHeight="1">
+    <row r="214" ht="13.5" hidden="1" customHeight="1">
       <c r="A214" s="3">
         <v>2008</v>
       </c>
@@ -6247,7 +6238,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="215" ht="13.5" customHeight="1">
+    <row r="215" ht="13.5" hidden="1" customHeight="1">
       <c r="A215" s="3">
         <v>2009</v>
       </c>
@@ -6270,7 +6261,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="216" ht="13.5" customHeight="1">
+    <row r="216" ht="13.5" hidden="1" customHeight="1">
       <c r="A216" s="3">
         <v>2011</v>
       </c>
@@ -6293,7 +6284,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="217" ht="13.5" customHeight="1">
+    <row r="217" ht="13.5" hidden="1" customHeight="1">
       <c r="A217" s="3">
         <v>2012</v>
       </c>
@@ -6316,7 +6307,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="218" ht="13.5" customHeight="1">
+    <row r="218" ht="13.5" hidden="1" customHeight="1">
       <c r="A218" s="3">
         <v>2013</v>
       </c>
@@ -6339,7 +6330,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="219" ht="13.5" customHeight="1">
+    <row r="219" ht="13.5" hidden="1" customHeight="1">
       <c r="A219" s="3">
         <v>2014</v>
       </c>
@@ -6362,7 +6353,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="220" ht="13.5" customHeight="1">
+    <row r="220" ht="13.5" hidden="1" customHeight="1">
       <c r="A220" s="3">
         <v>2015</v>
       </c>
@@ -6385,7 +6376,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="221" ht="13.5" customHeight="1">
+    <row r="221" ht="13.5" hidden="1" customHeight="1">
       <c r="A221" s="3">
         <v>2016</v>
       </c>
@@ -6408,7 +6399,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="222" ht="13.5" customHeight="1">
+    <row r="222" ht="13.5" hidden="1" customHeight="1">
       <c r="A222" s="3">
         <v>2017</v>
       </c>
@@ -6431,7 +6422,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="223" ht="13.5" customHeight="1">
+    <row r="223" ht="13.5" hidden="1" customHeight="1">
       <c r="A223" s="3">
         <v>2018</v>
       </c>
@@ -6454,7 +6445,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="224" ht="13.5" customHeight="1">
+    <row r="224" ht="13.5" hidden="1" customHeight="1">
       <c r="A224" s="3">
         <v>2019</v>
       </c>
@@ -6477,7 +6468,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="225" ht="13.5" customHeight="1">
+    <row r="225" ht="13.5" hidden="1" customHeight="1">
       <c r="A225" s="3">
         <v>2020</v>
       </c>
@@ -6500,7 +6491,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="226" ht="13.5" customHeight="1">
+    <row r="226" ht="13.5" hidden="1" customHeight="1">
       <c r="A226" s="3">
         <v>2021</v>
       </c>
@@ -6523,7 +6514,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="227" ht="13.5" customHeight="1">
+    <row r="227" ht="13.5" hidden="1" customHeight="1">
       <c r="A227" s="3">
         <v>2022</v>
       </c>
@@ -6546,7 +6537,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="228" ht="13.5" customHeight="1">
+    <row r="228" ht="13.5" hidden="1" customHeight="1">
       <c r="A228" s="3">
         <v>2023</v>
       </c>
@@ -6569,7 +6560,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="229" ht="13.5" customHeight="1">
+    <row r="229" ht="13.5" hidden="1" customHeight="1">
       <c r="A229" s="3">
         <v>2024</v>
       </c>
@@ -6592,7 +6583,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="230" ht="13.5" customHeight="1">
+    <row r="230" ht="13.5" hidden="1" customHeight="1">
       <c r="A230" s="3">
         <v>2025</v>
       </c>
@@ -6615,7 +6606,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="231" ht="13.5" customHeight="1">
+    <row r="231" ht="13.5" hidden="1" customHeight="1">
       <c r="A231" s="3">
         <v>2026</v>
       </c>
@@ -6638,7 +6629,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="232" ht="13.5" customHeight="1">
+    <row r="232" ht="13.5" hidden="1" customHeight="1">
       <c r="A232" s="3">
         <v>2027</v>
       </c>
@@ -6661,7 +6652,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="233" ht="13.5" customHeight="1">
+    <row r="233" ht="13.5" hidden="1" customHeight="1">
       <c r="A233" s="3">
         <v>2029</v>
       </c>
@@ -6684,7 +6675,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="234" ht="13.5" customHeight="1">
+    <row r="234" ht="13.5" hidden="1" customHeight="1">
       <c r="A234" s="3">
         <v>2030</v>
       </c>
@@ -6707,7 +6698,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="235" ht="13.5" customHeight="1">
+    <row r="235" ht="13.5" hidden="1" customHeight="1">
       <c r="A235" s="3">
         <v>2031</v>
       </c>
@@ -6730,7 +6721,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="236" ht="13.5" customHeight="1">
+    <row r="236" ht="13.5" hidden="1" customHeight="1">
       <c r="A236" s="3">
         <v>2032</v>
       </c>
@@ -6753,7 +6744,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="237" ht="13.5" customHeight="1">
+    <row r="237" ht="13.5" hidden="1" customHeight="1">
       <c r="A237" s="3">
         <v>2033</v>
       </c>
@@ -6776,7 +6767,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="238" ht="13.5" customHeight="1">
+    <row r="238" ht="13.5" hidden="1" customHeight="1">
       <c r="A238" s="3">
         <v>2034</v>
       </c>
@@ -6799,7 +6790,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="239" ht="13.5" customHeight="1">
+    <row r="239" ht="13.5" hidden="1" customHeight="1">
       <c r="A239" s="3">
         <v>2035</v>
       </c>
@@ -6822,7 +6813,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="240" ht="13.5" customHeight="1">
+    <row r="240" ht="13.5" hidden="1" customHeight="1">
       <c r="A240" s="3">
         <v>2036</v>
       </c>
@@ -6845,7 +6836,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="241" ht="13.5" customHeight="1">
+    <row r="241" ht="13.5" hidden="1" customHeight="1">
       <c r="A241" s="3">
         <v>2037</v>
       </c>
@@ -6868,7 +6859,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="242" ht="13.5" customHeight="1">
+    <row r="242" ht="13.5" hidden="1" customHeight="1">
       <c r="A242" s="3">
         <v>2038</v>
       </c>
@@ -6891,7 +6882,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="243" ht="13.5" customHeight="1">
+    <row r="243" ht="13.5" hidden="1" customHeight="1">
       <c r="A243" s="3">
         <v>2039</v>
       </c>
@@ -6914,7 +6905,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="244" ht="13.5" customHeight="1">
+    <row r="244" ht="13.5" hidden="1" customHeight="1">
       <c r="A244" s="3">
         <v>2040</v>
       </c>
@@ -6937,7 +6928,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="245" ht="13.5" customHeight="1">
+    <row r="245" ht="13.5" hidden="1" customHeight="1">
       <c r="A245" s="3">
         <v>2041</v>
       </c>
@@ -6960,7 +6951,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="246" ht="13.5" customHeight="1">
+    <row r="246" ht="13.5" hidden="1" customHeight="1">
       <c r="A246" s="3">
         <v>2042</v>
       </c>
@@ -6984,85 +6975,85 @@
       </c>
     </row>
     <row r="247" ht="13.5" customHeight="1">
-      <c r="A247" s="8"/>
+      <c r="A247" s="3"/>
       <c r="B247" s="4"/>
-      <c r="C247" s="9"/>
+      <c r="C247" s="4"/>
       <c r="D247" s="4"/>
-      <c r="E247" s="9"/>
-      <c r="F247" s="10"/>
-      <c r="G247" s="9"/>
+      <c r="E247" s="4"/>
+      <c r="F247" s="5"/>
+      <c r="G247" s="4"/>
     </row>
     <row r="248" ht="13.5" customHeight="1">
-      <c r="A248" s="8"/>
+      <c r="A248" s="3"/>
       <c r="B248" s="4"/>
-      <c r="C248" s="9"/>
+      <c r="C248" s="4"/>
       <c r="D248" s="4"/>
-      <c r="E248" s="9"/>
-      <c r="F248" s="10"/>
-      <c r="G248" s="9"/>
+      <c r="E248" s="4"/>
+      <c r="F248" s="5"/>
+      <c r="G248" s="4"/>
     </row>
     <row r="249" ht="13.5" customHeight="1">
-      <c r="A249" s="8"/>
+      <c r="A249" s="3"/>
       <c r="B249" s="4"/>
-      <c r="C249" s="9"/>
+      <c r="C249" s="4"/>
       <c r="D249" s="4"/>
-      <c r="E249" s="9"/>
-      <c r="F249" s="10"/>
-      <c r="G249" s="9"/>
+      <c r="E249" s="4"/>
+      <c r="F249" s="5"/>
+      <c r="G249" s="4"/>
     </row>
     <row r="250" ht="13.5" customHeight="1">
-      <c r="A250" s="8"/>
+      <c r="A250" s="3"/>
       <c r="B250" s="4"/>
-      <c r="C250" s="9"/>
+      <c r="C250" s="4"/>
       <c r="D250" s="4"/>
-      <c r="E250" s="9"/>
-      <c r="F250" s="10"/>
-      <c r="G250" s="9"/>
+      <c r="E250" s="4"/>
+      <c r="F250" s="5"/>
+      <c r="G250" s="4"/>
     </row>
     <row r="251" ht="13.5" customHeight="1">
-      <c r="A251" s="8"/>
+      <c r="A251" s="3"/>
       <c r="B251" s="4"/>
-      <c r="C251" s="9"/>
+      <c r="C251" s="4"/>
       <c r="D251" s="4"/>
-      <c r="E251" s="9"/>
-      <c r="F251" s="10"/>
-      <c r="G251" s="9"/>
+      <c r="E251" s="4"/>
+      <c r="F251" s="5"/>
+      <c r="G251" s="4"/>
     </row>
     <row r="252" ht="13.5" customHeight="1">
-      <c r="A252" s="8"/>
+      <c r="A252" s="3"/>
       <c r="B252" s="4"/>
-      <c r="C252" s="9"/>
+      <c r="C252" s="4"/>
       <c r="D252" s="4"/>
-      <c r="E252" s="9"/>
-      <c r="F252" s="10"/>
-      <c r="G252" s="9"/>
+      <c r="E252" s="4"/>
+      <c r="F252" s="5"/>
+      <c r="G252" s="4"/>
     </row>
     <row r="253" ht="13.5" customHeight="1">
-      <c r="A253" s="8"/>
+      <c r="A253" s="3"/>
       <c r="B253" s="4"/>
-      <c r="C253" s="9"/>
+      <c r="C253" s="4"/>
       <c r="D253" s="4"/>
-      <c r="E253" s="9"/>
-      <c r="F253" s="10"/>
-      <c r="G253" s="9"/>
+      <c r="E253" s="4"/>
+      <c r="F253" s="5"/>
+      <c r="G253" s="4"/>
     </row>
     <row r="254" ht="13.5" customHeight="1">
-      <c r="A254" s="8"/>
+      <c r="A254" s="3"/>
       <c r="B254" s="4"/>
-      <c r="C254" s="9"/>
+      <c r="C254" s="4"/>
       <c r="D254" s="4"/>
-      <c r="E254" s="9"/>
-      <c r="F254" s="10"/>
-      <c r="G254" s="9"/>
+      <c r="E254" s="4"/>
+      <c r="F254" s="5"/>
+      <c r="G254" s="4"/>
     </row>
     <row r="255" ht="13.5" customHeight="1">
-      <c r="A255" s="8"/>
+      <c r="A255" s="3"/>
       <c r="B255" s="4"/>
-      <c r="C255" s="9"/>
+      <c r="C255" s="4"/>
       <c r="D255" s="4"/>
-      <c r="E255" s="9"/>
-      <c r="F255" s="10"/>
-      <c r="G255" s="9"/>
+      <c r="E255" s="4"/>
+      <c r="F255" s="5"/>
+      <c r="G255" s="4"/>
     </row>
     <row r="256" ht="15" customHeight="1">
       <c r="B256" s="4"/>
@@ -7105,7 +7096,13 @@
       <c r="E264"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G246"/>
+  <autoFilter ref="A1:G246">
+    <filterColumn colId="4">
+      <filters>
+        <filter val="25570"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
